--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E558"/>
+  <dimension ref="A1:E560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15494,6 +15494,60 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>6a1221dac0afe2057c5f8e0c</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Ochieng</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000ce</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>delantero</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>6a122197fd42ba053658e853</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Beitia</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000ce</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E621"/>
+  <dimension ref="A1:E622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>6689c4a399e2e504052caf27</t>
+          <t>65ff6b016f0f544f132ae71b</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Rosier</t>
+          <t>Gastón Valles</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520384b42e80d2950b000092</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>66ade7b9702b9203b99a16eb</t>
+          <t>6689c4a399e2e504052caf27</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Luka Sucic</t>
+          <t>Rosier</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,22 +9611,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>68679d128486ff33404f2eef</t>
+          <t>66ade7b9702b9203b99a16eb</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Davinchi</t>
+          <t>Luka Sucic</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -9638,17 +9638,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>68679d128486ff33404f2eef</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Davinchi</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9665,17 +9665,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>51c1fdeac7694f5f66000051</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>David López</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9692,17 +9692,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>599893cd0999c98e0c5fa382</t>
+          <t>51c1fdeac7694f5f66000051</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Berrocal</t>
+          <t>David López</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9719,22 +9719,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5b32c9ec3200b74d1d721549</t>
+          <t>599893cd0999c98e0c5fa382</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Lemar</t>
+          <t>Berrocal</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>5b32c9ec3200b74d1d721549</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Lemar</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,22 +9773,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5d134f035af255065129d598</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Nteka</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,22 +9800,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5f04e39ee9102e0410faa4fb</t>
+          <t>5d134f035af255065129d598</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Víctor García</t>
+          <t>Nteka</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,17 +9827,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5f04e39ee9102e0410faa4fb</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Víctor García</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9854,17 +9854,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9881,22 +9881,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>64a0a08ba58cb1732757ad81</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Reina</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -9908,17 +9908,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>657cccb79a154503e6fa2fa8</t>
+          <t>64a0a08ba58cb1732757ad81</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Rodri Mendoza</t>
+          <t>Reina</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6689c562e0157a03f87fbf0e</t>
+          <t>657cccb79a154503e6fa2fa8</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Morey</t>
+          <t>Rodri Mendoza</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>66b5ea2dc34e5603e02c025e</t>
+          <t>6689c562e0157a03f87fbf0e</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Marc Vidal</t>
+          <t>Morey</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,22 +9989,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>6795064560299f03fb5de648</t>
+          <t>66b5ea2dc34e5603e02c025e</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Ángel Ortiz</t>
+          <t>Marc Vidal</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10016,22 +10016,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>679e3ac197b9af042545f308</t>
+          <t>6795064560299f03fb5de648</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Sannadi</t>
+          <t>Ángel Ortiz</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>54026d04e8a4c9292a0001db</t>
+          <t>679e3ac197b9af042545f308</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Joan Jordan</t>
+          <t>Sannadi</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,12 +10070,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>54026d04e8a4c9292a0001db</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Joan Jordan</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10097,17 +10097,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5b58ada3c1287fe25740991c</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Benavídez</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10124,17 +10124,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5b58ada3c1287fe25740991c</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Benavídez</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5ce0070a94a66a03f197ee55</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Camello</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,17 +10178,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5d0236a3167d9e5eb611db9b</t>
+          <t>5ce0070a94a66a03f197ee55</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Rodrygo</t>
+          <t>Camello</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5d0236a3167d9e5eb611db9b</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Rodrygo</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,17 +10232,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5efa4e35ee5a640417710119</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Jon Pacheco</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10259,22 +10259,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5f36db010b759303ff680104</t>
+          <t>5efa4e35ee5a640417710119</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Martín </t>
+          <t>Jon Pacheco</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10286,22 +10286,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5fbe33c11fd5fa0e8491689f</t>
+          <t>5f36db010b759303ff680104</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mingueza</t>
+          <t xml:space="preserve">Iván Martín </t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -10313,22 +10313,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>5fbe33c11fd5fa0e8491689f</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Mingueza</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,22 +10421,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>630a8dadb3e9b206bc1bb9c4</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Carmona</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10448,22 +10448,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>630f3695b0b3fe076438ce57</t>
+          <t>630a8dadb3e9b206bc1bb9c4</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Yvan Neyou</t>
+          <t>Carmona</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10475,17 +10475,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>63fd2d48e13c195af1f7112f</t>
+          <t>630f3695b0b3fe076438ce57</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Terrats</t>
+          <t>Yvan Neyou</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10502,22 +10502,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>64d1243213c6a63ccc321949</t>
+          <t>63fd2d48e13c195af1f7112f</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Campos</t>
+          <t>Terrats</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -10529,22 +10529,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d1243213c6a63ccc321949</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Campos</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>6757ff71d2717703ca746142</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Cabanes</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,22 +10583,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>67771f89cdd220756cfabdb0</t>
+          <t>6757ff71d2717703ca746142</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Garcés</t>
+          <t>Cabanes</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -10610,22 +10610,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a67000601</t>
+          <t>67771f89cdd220756cfabdb0</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Juanmi</t>
+          <t>Garcés</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5895c85a1b85076162dab6ac</t>
+          <t>504f65184d8bec9a67000601</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Juanmi</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,17 +10664,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5c8bf51dc84b6a5140cdd554</t>
+          <t>5895c85a1b85076162dab6ac</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Guevara</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10691,22 +10691,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5d6c122c5501724f700d2f42</t>
+          <t>5c8bf51dc84b6a5140cdd554</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Riquelme</t>
+          <t>Guevara</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5d9a575c370ecd5c7486de5c</t>
+          <t>5d6c122c5501724f700d2f42</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Ronald Araújo</t>
+          <t>Riquelme</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,12 +10745,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>51b9d964e401a15f2c000174</t>
+          <t>5d9a575c370ecd5c7486de5c</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Ter Stegen</t>
+          <t>Ronald Araújo</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -10772,22 +10772,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>584521ee88569163361f22cc</t>
+          <t>51b9d964e401a15f2c000174</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Javi Galán</t>
+          <t>Ter Stegen</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>584521ee88569163361f22cc</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Javi Galán</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,17 +10826,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>58e1616852a7d14c54bb26d3</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Carles Aleñá</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10853,22 +10853,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6060aa1a7a64b003da0efc7d</t>
+          <t>58e1616852a7d14c54bb26d3</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Arnau Martínez</t>
+          <t>Carles Aleñá</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -10880,17 +10880,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>6060aa1a7a64b003da0efc7d</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Arnau Martínez</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10907,22 +10907,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>614cc15d3916210732959cc3</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Robert Navarro</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10934,22 +10934,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>631ca92becf9a206fe07abea</t>
+          <t>614cc15d3916210732959cc3</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Kike Salas</t>
+          <t>Robert Navarro</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10961,22 +10961,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>5b34abe685664b531d0b6277</t>
+          <t>631ca92becf9a206fe07abea</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Jorge De Frutos</t>
+          <t>Kike Salas</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -10988,22 +10988,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5b375e0567e86d14114d4601</t>
+          <t>5b34abe685664b531d0b6277</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Ionuț Radu</t>
+          <t>Jorge De Frutos</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -11015,12 +11015,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>635d3cab6b7e0c0865360f8d</t>
+          <t>5b375e0567e86d14114d4601</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Pablo Durán</t>
+          <t>Ionuț Radu</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -11042,22 +11042,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>635d3cab6b7e0c0865360f8d</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Pablo Durán</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -11069,17 +11069,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11096,17 +11096,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11123,22 +11123,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>61be5d8bd58cb63e086bb365</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Iván Romero</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -11150,22 +11150,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>61be5d8bd58cb63e086bb365</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Iván Romero</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -11177,17 +11177,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>66c11e2cdad1bc1a1cff9a81</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Gerard Martín</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11204,22 +11204,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>64a7487e94e9d33cda0d9840</t>
+          <t>66c11e2cdad1bc1a1cff9a81</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>S. Altimira</t>
+          <t>Gerard Martín</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -11231,22 +11231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>64a7487e94e9d33cda0d9840</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>S. Altimira</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11258,22 +11258,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -11285,17 +11285,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -11312,17 +11312,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>665368343bd1d1040fffb355</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Yoel Lago</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>665368343bd1d1040fffb355</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Yoel Lago</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>669e6b4f99e2e504052cbbe5</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Álex Padilla</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>687185e26e82700408ad8cc4</t>
+          <t>669e6b4f99e2e504052cbbe5</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Léo Pétrot</t>
+          <t>Álex Padilla</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,22 +11420,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>504f65684d8bec9a6700072d</t>
+          <t>687185e26e82700408ad8cc4</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Griezmann</t>
+          <t>Léo Pétrot</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -11447,22 +11447,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>504f65684d8bec9a6700072d</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -11474,17 +11474,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11501,17 +11501,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>521465c2dbf8b74f020000b8</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Yuri</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11528,22 +11528,22 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>521465c2dbf8b74f020000b8</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Yuri</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -11555,17 +11555,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11582,22 +11582,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5c4f5a16320b7b03f8688fac</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Espino</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -11609,22 +11609,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>5da39ad5b8e82e5c69ab75f9</t>
+          <t>5c4f5a16320b7b03f8688fac</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Valles</t>
+          <t>Espino</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -11636,22 +11636,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>5da39ad5b8e82e5c69ab75f9</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Valles</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -11663,22 +11663,22 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -11690,17 +11690,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6310da7e4028c607606859df</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Mumin</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6461127d49e91a03fb017cda</t>
+          <t>6310da7e4028c607606859df</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Carlos Martín</t>
+          <t>Mumin</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -11744,22 +11744,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>64d4d45594e9d33cda0d987d</t>
+          <t>6461127d49e91a03fb017cda</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Starfelt</t>
+          <t>Carlos Martín</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -11771,22 +11771,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>64d4d45594e9d33cda0d987d</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Starfelt</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -11798,22 +11798,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>65871ef403b798703d8c7dd6</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -11825,17 +11825,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>66b8ed0a702b9203b99a1705</t>
+          <t>65871ef403b798703d8c7dd6</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Hugo Rincón</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -11852,17 +11852,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>66b8fc5699635f03debf8fe8</t>
+          <t>66b8ed0a702b9203b99a1705</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Parada</t>
+          <t>Hugo Rincón</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -11879,22 +11879,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>66b8fc5699635f03debf8fe8</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -11906,22 +11906,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>672f816c29e197051e04e8e4</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Asencio</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,22 +11933,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>67804e6ab11a5e759942b02f</t>
+          <t>672f816c29e197051e04e8e4</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Kervin Arriaga</t>
+          <t>Asencio</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -11960,22 +11960,22 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6828939eb56c87346f2767f5</t>
+          <t>67804e6ab11a5e759942b02f</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Álvaro Carreras</t>
+          <t>Kervin Arriaga</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -11987,22 +11987,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>5b6e2823a2736a321a4d1003</t>
+          <t>6828939eb56c87346f2767f5</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Álvaro Carreras</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -12014,22 +12014,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>66d61f2aed648e0b1ac63f1a</t>
+          <t>5b6e2823a2736a321a4d1003</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Bergström</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -12041,22 +12041,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>68780dec5c7211044690a3a9</t>
+          <t>66d61f2aed648e0b1ac63f1a</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Enríquez</t>
+          <t>Bergström</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -12068,22 +12068,22 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6878cacd19c279041887fa6f</t>
+          <t>68780dec5c7211044690a3a9</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Iturbe</t>
+          <t>Enríquez</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -12095,22 +12095,22 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>6878cacd19c279041887fa6f</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Iturbe</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>5a81f13ce3c1953064f782e0</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Junior Firpo</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12149,12 +12149,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>687aa8cb00ed89046c1f7e6e</t>
+          <t>5a81f13ce3c1953064f782e0</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Gonzalo Petit</t>
+          <t>Junior Firpo</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12176,22 +12176,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>60e72704dfb903607d1f7d87</t>
+          <t>687aa8cb00ed89046c1f7e6e</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Dituro</t>
+          <t>Gonzalo Petit</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12203,22 +12203,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5d5570f69bb8253fe4f452d6</t>
+          <t>60e72704dfb903607d1f7d87</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Ahijado</t>
+          <t>Dituro</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12230,12 +12230,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>66d81870433f040b000aa40c</t>
+          <t>5d5570f69bb8253fe4f452d6</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Luka Ilic</t>
+          <t>Ahijado</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>57c73a7a803dc6bd7be02981</t>
+          <t>66d81870433f040b000aa40c</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Pau López</t>
+          <t>Luka Ilic</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12284,22 +12284,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>57c73a7a803dc6bd7be02981</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Pau López</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12311,22 +12311,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>56d314416116845b08e61bed</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Rashford</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>51d19d0f78d9b6850500003e</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12338,22 +12338,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>688318293777f6041274556c</t>
+          <t>56d314416116845b08e61bed</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Hancko</t>
+          <t>Rashford</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51d19d0f78d9b6850500003e</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -12365,22 +12365,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>62b3135fa81ab52db02ea690</t>
+          <t>688318293777f6041274556c</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Forés</t>
+          <t>Hancko</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -12392,17 +12392,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>68836f764e36d6040c695eb1</t>
+          <t>62b3135fa81ab52db02ea690</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Dolan</t>
+          <t>Forés</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -12419,22 +12419,22 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>68836f764e36d6040c695eb1</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Dolan</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -12446,17 +12446,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12473,22 +12473,22 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -12500,22 +12500,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>62f826f93355b0168987308d</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -12527,12 +12527,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6643e149974fb0361c6a6e9b</t>
+          <t>62f826f93355b0168987308d</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Mario Martín</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -12554,22 +12554,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>679505f4ea489a03b4fb00dc</t>
+          <t>6643e149974fb0361c6a6e9b</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Pablo García</t>
+          <t>Mario Martín</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -12581,12 +12581,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>682920fc77ba5003ca4869ce</t>
+          <t>679505f4ea489a03b4fb00dc</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Deossa</t>
+          <t>Pablo García</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -12608,22 +12608,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>682920fc77ba5003ca4869ce</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Deossa</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -12635,22 +12635,22 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>68951eec4e36d6040c695ed8</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Santamaria</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -12662,22 +12662,22 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>68951eec4e36d6040c695ed8</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Santamaria</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -12689,22 +12689,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>68951bdfb2ec15040b6eee00</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Fortuño</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -12716,22 +12716,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>68951bdfb2ec15040b6eee00</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>Fortuño</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -12743,22 +12743,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>68966a3623f462042dbe3298</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Ugrinic</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -12770,22 +12770,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>68169445172c6403d6396e7c</t>
+          <t>68966a3623f462042dbe3298</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Dani Rodríguez</t>
+          <t>Ugrinic</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -12797,22 +12797,22 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>668020900ab8ba417f327199</t>
+          <t>68169445172c6403d6396e7c</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Vertrouwd</t>
+          <t>Dani Rodríguez</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -12824,22 +12824,22 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>62c5da44fbbaa82d71999775</t>
+          <t>668020900ab8ba417f327199</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Witsel</t>
+          <t>Vertrouwd</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -12851,17 +12851,17 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>62c5da44fbbaa82d71999775</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Witsel</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -12878,22 +12878,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>65a2f7b8b94b7303dce5ccac</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Marco Esteban</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -12905,12 +12905,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>689fb8cb06428a0452dc8034</t>
+          <t>65a2f7b8b94b7303dce5ccac</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Omar Falah</t>
+          <t>Marco Esteban</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12932,17 +12932,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>68a0ec6aa9a91a0415a363e1</t>
+          <t>689fb8cb06428a0452dc8034</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Torrents</t>
+          <t>Omar Falah</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -12959,22 +12959,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>68a0ec6aa9a91a0415a363e1</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Torrents</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -12986,22 +12986,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>63cdb1fff41df804fa60e6f1</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Castrín</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13013,17 +13013,17 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>68a21b2501a094041b51ad5b</t>
+          <t>63cdb1fff41df804fa60e6f1</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Bekhoucha</t>
+          <t>Castrín</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -13040,22 +13040,22 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>68a234d9a9a91a0415a3788b</t>
+          <t>68a21b2501a094041b51ad5b</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Rego</t>
+          <t>Bekhoucha</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -13067,17 +13067,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>68a234d9a9a91a0415a3788b</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Rego</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -13094,17 +13094,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>5b6cc28068b47b496279f860</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Dendoncker</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -13121,22 +13121,22 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>68a9fc4cd20bb9540efa8666</t>
+          <t>5b6cc28068b47b496279f860</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Manu Fernández</t>
+          <t>Dendoncker</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -13148,17 +13148,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>53ac3e6c1933f2de6f0003fc</t>
+          <t>68a9fc4cd20bb9540efa8666</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Álex Moreno</t>
+          <t>Manu Fernández</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -13175,22 +13175,22 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>53ac3e6c1933f2de6f0003fc</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Álex Moreno</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -13202,22 +13202,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>66919efdc34e5603e02bfd43</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Renato Veiga</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -13229,17 +13229,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>68adba775730b11c3098162a</t>
+          <t>66919efdc34e5603e02bfd43</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Riedel</t>
+          <t>Renato Veiga</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -13256,22 +13256,22 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>55ad2871332f681702ac1350</t>
+          <t>68adba775730b11c3098162a</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Riedel</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -13283,17 +13283,17 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6305da4d46d783071421441c</t>
+          <t>55ad2871332f681702ac1350</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Arnau Tenas</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -13310,22 +13310,22 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>5f43f5bf0b759303ff680853</t>
+          <t>6305da4d46d783071421441c</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Ramazani</t>
+          <t>Arnau Tenas</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>57a1235f445c20291844c133</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -13337,17 +13337,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>68b0df5c11ed3a059c4912a3</t>
+          <t>5f43f5bf0b759303ff680853</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Virgili</t>
+          <t>Ramazani</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>57a1235f445c20291844c133</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -13364,17 +13364,17 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>68b22bf68eb5b005b415a5c6</t>
+          <t>68b0df5c11ed3a059c4912a3</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Oluwaseyi</t>
+          <t>Virgili</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -13391,17 +13391,17 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>5baf8177ffea6a45840b44a4</t>
+          <t>68b22bf68eb5b005b415a5c6</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Diangana</t>
+          <t>Oluwaseyi</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13418,22 +13418,22 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>68b37c6461185205e8c364db</t>
+          <t>5baf8177ffea6a45840b44a4</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Ounahi</t>
+          <t>Diangana</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -13445,22 +13445,22 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6866a463588465330dd378d1</t>
+          <t>68b37c6461185205e8c364db</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Rupérez</t>
+          <t>Ounahi</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -13472,22 +13472,22 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>68b486b8882e4a05b2d43111</t>
+          <t>6866a463588465330dd378d1</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Román</t>
+          <t>Rupérez</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -13499,22 +13499,22 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>68b59fba05c30a03fb36d382</t>
+          <t>68b486b8882e4a05b2d43111</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Vanat</t>
+          <t>Román</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -13526,17 +13526,17 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>630e1e745328c70716999d1d</t>
+          <t>68b59fba05c30a03fb36d382</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Vanat</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -13553,22 +13553,22 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>630e1e745328c70716999d1d</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -13580,22 +13580,22 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>68b5d6ae026ac303d72e0129</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Mikautadze</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -13607,22 +13607,22 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>57d56922c74b68af216c8ba3</t>
+          <t>68b5d6ae026ac303d72e0129</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Carlos Soler</t>
+          <t>Mikautadze</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -13634,22 +13634,22 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>504e58ca4d8bec9a670001e1</t>
+          <t>57d56922c74b68af216c8ba3</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Alexis Sánchez</t>
+          <t>Carlos Soler</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -13661,17 +13661,17 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>5c323b46bef16503ec960e1c</t>
+          <t>504e58ca4d8bec9a670001e1</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Bryan Gil</t>
+          <t>Alexis Sánchez</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -13688,17 +13688,17 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>5c323b46bef16503ec960e1c</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Bryan Gil</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -13715,22 +13715,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -13742,22 +13742,22 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -13769,22 +13769,22 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>504f64c44d8bec9a67000509</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Nyom</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -13796,22 +13796,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>68f3b8b9dd3614500b418a49</t>
+          <t>504f64c44d8bec9a67000509</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Lass</t>
+          <t>Nyom</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -13823,22 +13823,22 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>68f3bc99ffaac64fef985f6e</t>
+          <t>68f3b8b9dd3614500b418a49</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Toni Fernández</t>
+          <t>Lass</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>68fe7b135fa52f03fe008bad</t>
+          <t>68f3bc99ffaac64fef985f6e</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Osambela</t>
+          <t>Toni Fernández</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -13877,22 +13877,22 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>690c69e2c2cdbf03b2f132e8</t>
+          <t>68fe7b135fa52f03fe008bad</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Selton</t>
+          <t>Osambela</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -13904,22 +13904,22 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>690f6102072c5e03d67ac3e5</t>
+          <t>690c69e2c2cdbf03b2f132e8</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Selton</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -13931,22 +13931,22 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>690f6102072c5e03d67ac3e5</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -13958,17 +13958,17 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6935bcd342796103f7ed41db</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -13985,17 +13985,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>693c2462d47eab05710d78a0</t>
+          <t>6935bcd342796103f7ed41db</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Valdepeñas</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -14012,17 +14012,17 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fad9</t>
+          <t>693c2462d47eab05710d78a0</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Gattoni</t>
+          <t>Valdepeñas</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -14039,22 +14039,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>66a3c7736e037203f626834e</t>
+          <t>66a3d3797fc6ff03fb06fad9</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Thiago Fernández</t>
+          <t>Gattoni</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -14066,17 +14066,17 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>695a877f1b6b9103c47320ef</t>
+          <t>66a3c7736e037203f626834e</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Thiago Fernández</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -14093,12 +14093,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>68b61cee09819404060c520a</t>
+          <t>695a877f1b6b9103c47320ef</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Paco Cortés</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -14120,22 +14120,22 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>696184347cc74203effd6ff6</t>
+          <t>68b61cee09819404060c520a</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Mestanza</t>
+          <t>Paco Cortés</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -14147,12 +14147,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>696184347cc74203effd6ff6</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Mestanza</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -14174,12 +14174,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>69618351e6468d03e846934a</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Montes</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -14201,17 +14201,17 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>52024320737b88c937000019</t>
+          <t>69618351e6468d03e846934a</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t xml:space="preserve"> João Cancelo</t>
+          <t>Montes</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -14228,17 +14228,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>52024320737b88c937000019</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t xml:space="preserve"> João Cancelo</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -14255,22 +14255,22 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>696a39e9af58fa040efb5372</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Kalumba</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -14282,22 +14282,22 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>696a39e9af58fa040efb5372</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Kalumba</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fadf</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Echeverri</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>51d197b30719708a05000037</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -14336,17 +14336,17 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>64f11152061d1303c4816c1f</t>
+          <t>66a3d3797fc6ff03fb06fadf</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Tai Abed</t>
+          <t>Echeverri</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51d197b30719708a05000037</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -14363,22 +14363,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>64f11152061d1303c4816c1f</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Tai Abed</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -14390,22 +14390,22 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6973f63ad00321040c3be944</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Álex Sánchez</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -14417,22 +14417,22 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>69752256a68dd603be29f508</t>
+          <t>6973f63ad00321040c3be944</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Hierro</t>
+          <t>Álex Sánchez</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -14444,22 +14444,22 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6977e9c440eaa603f8aa3e87</t>
+          <t>69752256a68dd603be29f508</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Cepeda</t>
+          <t>Hierro</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -14471,22 +14471,22 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6977e776fee4e803e0e8bed5</t>
+          <t>6977e9c440eaa603f8aa3e87</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Arango</t>
+          <t>Cepeda</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -14498,22 +14498,22 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>6977e776fee4e803e0e8bed5</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Arango</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -14525,22 +14525,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>675366baf7be6b107f01b952</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Fer López</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>57a12447445c20291844c142</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -14552,17 +14552,17 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>52017fe74f1c7f1534000047</t>
+          <t>675366baf7be6b107f01b952</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Maupay</t>
+          <t>Fer López</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>57a12447445c20291844c142</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -14579,22 +14579,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>68c5f5d55bd165052e271611</t>
+          <t>52017fe74f1c7f1534000047</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Ángel Pérez</t>
+          <t>Maupay</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -14606,17 +14606,17 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>68c5f5d55bd165052e271611</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Ángel Pérez</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -14633,17 +14633,17 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>697e90b3ff715b03c5df8278</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Koski</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -14660,22 +14660,22 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>697e90b3ff715b03c5df8278</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Koski</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -14687,17 +14687,17 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>69810c427602e303cbed6a3e</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Obed Vargas</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -14714,12 +14714,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>69810c427602e303cbed6a3e</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Obed Vargas</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -14741,17 +14741,17 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -14768,12 +14768,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>5b43ab6e5c2992ae0bf69a35</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Gonzalo Villar</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -14795,17 +14795,17 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>68a0ebed3a1cb503e4684dca</t>
+          <t>5b43ab6e5c2992ae0bf69a35</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Jan  Salas</t>
+          <t>Gonzalo Villar</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -14822,17 +14822,17 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>51bcc35c377408301a00000c</t>
+          <t>68a0ebed3a1cb503e4684dca</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Vecino</t>
+          <t>Jan  Salas</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -14849,22 +14849,22 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>65e3820705716403fe13d771</t>
+          <t>51bcc35c377408301a00000c</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Sangare</t>
+          <t>Vecino</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -14876,22 +14876,22 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6988af503b0d1b03ea60fa11</t>
+          <t>65e3820705716403fe13d771</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Aitor Mañas</t>
+          <t>Sangare</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -14903,22 +14903,22 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>69890c8d777a260432d3c68c</t>
+          <t>6988af503b0d1b03ea60fa11</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>David Jiménez</t>
+          <t>Aitor Mañas</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -14930,12 +14930,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>69890d253b0d1b03ea61084c</t>
+          <t>69890c8d777a260432d3c68c</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Cestero</t>
+          <t>David Jiménez</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -14957,17 +14957,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6990b007612d5404638c8cfe</t>
+          <t>69890d253b0d1b03ea61084c</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Hugo López</t>
+          <t>Cestero</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -14984,22 +14984,22 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6992250a399cbe048cfd966e</t>
+          <t>6990b007612d5404638c8cfe</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Nacho Pérez</t>
+          <t>Hugo López</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -15011,17 +15011,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>69a37b194f0be803ae3e49e7</t>
+          <t>6992250a399cbe048cfd966e</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Julio Díaz</t>
+          <t>Nacho Pérez</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -15038,22 +15038,22 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>69a5ddd7cd2bdb03fcc07f8a</t>
+          <t>69a37b194f0be803ae3e49e7</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Thiago Pitarch</t>
+          <t>Julio Díaz</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -15065,12 +15065,12 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>69ab5b4653966303fb66b781</t>
+          <t>69a5ddd7cd2bdb03fcc07f8a</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Thiago Pitarch</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -15092,12 +15092,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>69ab5b84a3657e03f770ab51</t>
+          <t>69ab5b4653966303fb66b781</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Manuel Ángel</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15119,12 +15119,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>69b5e2a7c20e6203ae9f9a87</t>
+          <t>69ab5b84a3657e03f770ab51</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Diego Aguado</t>
+          <t>Manuel Ángel</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15146,12 +15146,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>69b5e2e55436d103b5c952e0</t>
+          <t>69b5e2a7c20e6203ae9f9a87</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Daniel Yáñez</t>
+          <t>Diego Aguado</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15173,22 +15173,22 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>69b5e2e55436d103b5c952e0</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>Daniel Yáñez</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15200,22 +15200,22 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>69d183cac5709804148dcb11</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Taufik</t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15227,12 +15227,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>69d1843021ab3804095dc5d2</t>
+          <t>69d183cac5709804148dcb11</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Taufik</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -15254,12 +15254,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>69daa74298d9eb0426259b22</t>
+          <t>69d1843021ab3804095dc5d2</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Boñar</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15281,12 +15281,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>69daa71455f89f041388274a</t>
+          <t>69daa74298d9eb0426259b22</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Dani Martínez</t>
+          <t>Boñar</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15308,12 +15308,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>69daa6da17877004192cea21</t>
+          <t>69daa71455f89f041388274a</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Belaid</t>
+          <t>Dani Martínez</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15335,12 +15335,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6687123799f9bf415ff44157</t>
+          <t>69daa6da17877004192cea21</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Puric</t>
+          <t>Belaid</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -15362,12 +15362,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>69f632161fe2c90424d568b4</t>
+          <t>6687123799f9bf415ff44157</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Cubo</t>
+          <t>Puric</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -15389,12 +15389,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>69f632503caa6b0472477da2</t>
+          <t>69f632161fe2c90424d568b4</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Iker Luque</t>
+          <t>Cubo</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -15416,22 +15416,22 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a04f3f3f8f6ef041e55261c</t>
+          <t>69f632503caa6b0472477da2</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Damián</t>
+          <t>Iker Luque</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -15443,22 +15443,22 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a04f502781278043f2eda16</t>
+          <t>6a04f3f3f8f6ef041e55261c</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Orejuela</t>
+          <t>Damián</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -15470,17 +15470,17 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a04f759781278043f2eda18</t>
+          <t>6a04f502781278043f2eda16</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Cortés</t>
+          <t>Orejuela</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -15497,17 +15497,17 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>5d6d7cd40bf0ba048d4b0379</t>
+          <t>6a04f759781278043f2eda18</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Thierry Correia</t>
+          <t>Cortés</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -15524,12 +15524,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>5d6d7cd40bf0ba048d4b0379</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Thierry Correia</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -15551,12 +15551,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -15578,22 +15578,22 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>5989a27fd094c1ec4bdbf741</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Unai Núñez</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -15605,22 +15605,22 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a06409cd60a6e0400dd5242</t>
+          <t>5989a27fd094c1ec4bdbf741</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Carrera</t>
+          <t>Unai Núñez</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -15632,17 +15632,17 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>6a06409cd60a6e0400dd5242</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Carrera</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -15659,22 +15659,22 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>61844713165d9f09c3eecd07</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Artero</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -15686,22 +15686,22 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a1221dac0afe2057c5f8e0c</t>
+          <t>61844713165d9f09c3eecd07</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Ochieng</t>
+          <t>Artero</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -15713,12 +15713,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a122197fd42ba053658e853</t>
+          <t>6a1221dac0afe2057c5f8e0c</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Beitia</t>
+          <t>Ochieng</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -15740,17 +15740,17 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>6a122197fd42ba053658e853</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Beitia</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -15767,17 +15767,17 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a358ea99542a303bf19bf7a</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Sangante</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -15794,22 +15794,22 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>6a358ea99542a303bf19bf7a</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>Sangante</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -15821,12 +15821,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -15848,17 +15848,17 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>521b69bf359d42743700007f</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Carlos Fernández</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -15875,22 +15875,22 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>65f7126c17c8f74f39434408</t>
+          <t>521b69bf359d42743700007f</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Damián Rodríguez</t>
+          <t>Carlos Fernández</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15902,17 +15902,17 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>65f7126c17c8f74f39434408</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Damián Rodríguez</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -15929,17 +15929,17 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>66a3c8069e452303b3fc0b22</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Albarracín</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -15956,17 +15956,17 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a35925b33c8f103cdc11d15</t>
+          <t>66a3c8069e452303b3fc0b22</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Bardeli</t>
+          <t>Albarracín</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -15983,22 +15983,22 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>5d547cd98517403fd8fab746</t>
+          <t>6a35925b33c8f103cdc11d15</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Maras</t>
+          <t>Bardeli</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -16010,22 +16010,22 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>66ba79564942001a16eafbb7</t>
+          <t>5d547cd98517403fd8fab746</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Dani Martín</t>
+          <t>Maras</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -16037,22 +16037,22 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>66ba79564942001a16eafbb7</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Dani Martín</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -16064,22 +16064,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>674b7a94c9efc910567f19b6</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -16091,17 +16091,17 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>64ea79b9b1931503ca17ef44</t>
+          <t>674b7a94c9efc910567f19b6</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Dani Requena</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -16118,22 +16118,22 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>64d3c4746167273d0ccc5c52</t>
+          <t>64ea79b9b1931503ca17ef44</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Pablo Ramón</t>
+          <t>Dani Requena</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -16145,12 +16145,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>5cfc2be98721525ead8d94b1</t>
+          <t>64d3c4746167273d0ccc5c52</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Gragera</t>
+          <t>Pablo Ramón</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -16172,22 +16172,22 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>5cfc2be98721525ead8d94b1</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Gragera</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -16199,22 +16199,22 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a358e6ff1bdb603db6fc1a4</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -16226,22 +16226,22 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>6a358e6ff1bdb603db6fc1a4</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -16253,22 +16253,22 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>688fbfc45c7211044690a3d3</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Selu Diallo</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -16280,22 +16280,22 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>66c25f14b5741f1a24b155a4</t>
+          <t>688fbfc45c7211044690a3d3</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Barzic</t>
+          <t>Selu Diallo</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -16307,12 +16307,12 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6610624ad70dc004141ec091</t>
+          <t>66c25f14b5741f1a24b155a4</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Rafa Núñez</t>
+          <t>Barzic</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -16334,22 +16334,22 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6683c6e90ab8ba417f3276b6</t>
+          <t>6610624ad70dc004141ec091</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Unai Ropero</t>
+          <t>Rafa Núñez</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -16361,17 +16361,17 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>66bb83844942001a16eafbb8</t>
+          <t>6683c6e90ab8ba417f3276b6</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Javi Hernández</t>
+          <t>Unai Ropero</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -16388,17 +16388,17 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>66f98191043342085bbcc7ce</t>
+          <t>66bb83844942001a16eafbb8</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Peio Canales</t>
+          <t>Javi Hernández</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -16415,22 +16415,22 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>66f98191043342085bbcc7ce</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>5e23437d616e7d03ba5dc21c</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -16469,22 +16469,22 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>614743ace216464c91a29186</t>
+          <t>5e23437d616e7d03ba5dc21c</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Owono</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -16496,22 +16496,22 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>61c3b14eb4f96c073bf94ce7</t>
+          <t>614743ace216464c91a29186</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Owono</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -16523,22 +16523,22 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>67d4acc7fb012703e17d1dc5</t>
+          <t>61c3b14eb4f96c073bf94ce7</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Adrián R.</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -16550,17 +16550,17 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>686feb558bef76044eadf791</t>
+          <t>67d4acc7fb012703e17d1dc5</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Adrián R.</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -16577,22 +16577,22 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>66cfa272b46ff704160ad00e</t>
+          <t>686feb558bef76044eadf791</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Adrián Pica</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -16604,17 +16604,17 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>66cfa272b46ff704160ad00e</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Adrián Pica</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -16631,12 +16631,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>59510d122a7f2df00504ab30</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Cucurella</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -16658,12 +16658,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>59510d122a7f2df00504ab30</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Cucurella</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -16685,22 +16685,22 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>5d630db9e7e62b777ebb59be</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Ansu Fati</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -16712,22 +16712,22 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>64b9b83013c6a63ccc32191b</t>
+          <t>5d630db9e7e62b777ebb59be</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Carlos Dotor</t>
+          <t>Ansu Fati</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -16739,17 +16739,17 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6866a56fca97b13338e6cd0b</t>
+          <t>64b9b83013c6a63ccc32191b</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Goti</t>
+          <t>Carlos Dotor</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -16766,22 +16766,22 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>66c8333550cfa503c1736efc</t>
+          <t>6866a56fca97b13338e6cd0b</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Goti</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -16793,22 +16793,22 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>66d39b3d58f2de32117efa18</t>
+          <t>66c8333550cfa503c1736efc</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Domenech</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -16820,12 +16820,12 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>67597e6b317cba0418bce297</t>
+          <t>66d39b3d58f2de32117efa18</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Dani Luna</t>
+          <t>Domenech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -16847,17 +16847,17 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>57b94a3c7ce1feed040b24e3</t>
+          <t>67597e6b317cba0418bce297</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Jacobo González</t>
+          <t>Dani Luna</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -16874,12 +16874,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>60e6e2841a405a604ca8c2d7</t>
+          <t>57b94a3c7ce1feed040b24e3</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Luengo</t>
+          <t>Jacobo González</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -16901,12 +16901,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>64b1c502c35fcb3cfd3ed505</t>
+          <t>60e6e2841a405a604ca8c2d7</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Youness</t>
+          <t>Luengo</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -16928,12 +16928,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6865adefd4d22b330615f7ca</t>
+          <t>64b1c502c35fcb3cfd3ed505</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Youness</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -16955,12 +16955,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>669274f3ce303803d6f77330</t>
+          <t>6865adefd4d22b330615f7ca</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Paraschiv</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -16982,12 +16982,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>62b3117afea5532da7ee56f0</t>
+          <t>669274f3ce303803d6f77330</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Del Moral</t>
+          <t>Paraschiv</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -17009,17 +17009,17 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>697be226df6332040670c6c1</t>
+          <t>62b3117afea5532da7ee56f0</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Izan González</t>
+          <t>Del Moral</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -17036,12 +17036,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a35c168152d0603c64c029a</t>
+          <t>697be226df6332040670c6c1</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Pyshchur</t>
+          <t>Izan González</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -17063,12 +17063,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>66c9b0acf119260402e26288</t>
+          <t>6a35c168152d0603c64c029a</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Asprilla</t>
+          <t>Pyshchur</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -17090,12 +17090,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>68a9e8aab479f05404a946c8</t>
+          <t>66c9b0acf119260402e26288</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Asprilla</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17117,12 +17117,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6713fdc9a1b917176a03238a</t>
+          <t>68a9e8aab479f05404a946c8</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Min-su Kim</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -17144,12 +17144,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>65f5fc5000ffc34f05f1cb1f</t>
+          <t>6713fdc9a1b917176a03238a</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Jastin</t>
+          <t>Min-su Kim</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -17171,25 +17171,52 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
+          <t>65f5fc5000ffc34f05f1cb1f</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Jastin</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>520347e4b8d07d930b00000f</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>delantero</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
           <t>6310c8d8ad2f6e072207b4c5</t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>Fuidias</t>
         </is>
       </c>
-      <c r="C621" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr">
+      <c r="D622" t="inlineStr">
         <is>
           <t>portero</t>
         </is>
       </c>
-      <c r="E621" t="inlineStr">
+      <c r="E622" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E623"/>
+  <dimension ref="A1:E627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2321,22 +2321,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>5f6eee81be8fe949f2105939</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Iñaki Peña</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2348,22 +2348,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>65ff6b016f0f544f132ae71b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Gastón Valles</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520384b42e80d2950b000092</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2375,22 +2375,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2402,17 +2402,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2429,17 +2429,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2456,22 +2456,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2483,22 +2483,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>51d70ed7a7178a7654000012</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mojica</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2510,17 +2510,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2537,22 +2537,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>51d70ed7a7178a7654000012</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Mojica</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2564,22 +2564,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2591,22 +2591,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2618,17 +2618,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>504f647e4d8bec9a67000484</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Stuani</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2645,22 +2645,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2672,17 +2672,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>504f647e4d8bec9a67000484</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Stuani</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2699,22 +2699,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2726,17 +2726,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5313988280c359915f000011</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Portu</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2753,22 +2753,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2780,22 +2780,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>5313988280c359915f000011</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Portu</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2807,22 +2807,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2834,22 +2834,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2861,22 +2861,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2888,22 +2888,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2915,22 +2915,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2942,12 +2942,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2969,22 +2969,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2996,22 +2996,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3023,22 +3023,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3050,22 +3050,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3077,17 +3077,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3104,22 +3104,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3131,22 +3131,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>51cab26c01d64ad470000096</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Gazzaniga</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3158,22 +3158,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3185,22 +3185,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5210908da776cc826b000067</t>
+          <t>51cab26c01d64ad470000096</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Darder</t>
+          <t>Gazzaniga</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3212,22 +3212,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3239,22 +3239,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>577fc05cd0b969de4e1a7096</t>
+          <t>5210908da776cc826b000067</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Chimy Ávila</t>
+          <t>Darder</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3266,22 +3266,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3293,22 +3293,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>577fc05cd0b969de4e1a7096</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Chimy Ávila</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3320,22 +3320,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3347,17 +3347,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>54c509f75d97b9070200178c</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dani Calvo</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3374,22 +3374,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3401,17 +3401,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>577743d027ae4bd9135ae3d8</t>
+          <t>54c509f75d97b9070200178c</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nahuel Molina</t>
+          <t>Dani Calvo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3428,22 +3428,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>57583b4733dbe3424c05e8ee</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Luis Milla</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3455,22 +3455,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>577743d027ae4bd9135ae3d8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Nahuel Molina</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3482,22 +3482,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>57583b4733dbe3424c05e8ee</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Luis Milla</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>521b5f939f2adc783700001e</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>David Costas</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3536,17 +3536,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>520263c1ed2e70cb370000c1</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Raíllo</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3563,17 +3563,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>521b5f939f2adc783700001e</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>David Costas</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3590,17 +3590,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>520263c1ed2e70cb370000c1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Raíllo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3617,22 +3617,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3644,22 +3644,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3671,22 +3671,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>504f65684d8bec9a6700072d</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Griezmann</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3698,17 +3698,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,22 +3725,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>504f65684d8bec9a6700072d</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3752,22 +3752,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000bc</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Szczesny</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3779,17 +3779,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3806,22 +3806,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>59c419ed548e551c0db5b308</t>
+          <t>51cb698301d64ad4700000bc</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gorosabel</t>
+          <t>Szczesny</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3860,17 +3860,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>59c419ed548e551c0db5b308</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Gorosabel</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5c0eea87e3eca97d26f62cee</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Pedrosa</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3914,22 +3914,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5d17ceb62cef430674ec2674</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Isi Palazón</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3941,22 +3941,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5c0eea87e3eca97d26f62cee</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Pedrosa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3968,22 +3968,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5f0cbbb3075d9b03e1b24de9</t>
+          <t>5d17ceb62cef430674ec2674</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Baena</t>
+          <t>Isi Palazón</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3995,17 +3995,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4022,12 +4022,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6126993bb52ba2079fdc7828</t>
+          <t>5f0cbbb3075d9b03e1b24de9</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Sorloth</t>
+          <t>Baena</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4049,17 +4049,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>614cc15d3916210732959cc3</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Robert Navarro</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4076,22 +4076,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>6126993bb52ba2079fdc7828</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Sorloth</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4103,22 +4103,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>614cc15d3916210732959cc3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Robert Navarro</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4130,17 +4130,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>62fd1a08e88c090690b05916</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nianzou</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>630274ff9906dc0691df670b</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Bretones</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>63d8eb7b1d17ae5aff1f4c52</t>
+          <t>62fd1a08e88c090690b05916</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Nianzou</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4211,17 +4211,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>65b56235a3176a0e0fdb8f74</t>
+          <t>630274ff9906dc0691df670b</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Héctor Fort</t>
+          <t>Bretones</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6647cad9bd5be20441bcc95c</t>
+          <t>63d8eb7b1d17ae5aff1f4c52</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Boayar</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4265,22 +4265,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>65b56235a3176a0e0fdb8f74</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Héctor Fort</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,22 +4292,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>66cf964ebd0d6403c8b5d5ad</t>
+          <t>6647cad9bd5be20441bcc95c</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Viñas</t>
+          <t>Boayar</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>520025dc19cbe47807000087</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4319,22 +4319,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6861bef57775a433449e9581</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Jutglà</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4346,22 +4346,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5b3341dc20ba80411d09afaf</t>
+          <t>66cf964ebd0d6403c8b5d5ad</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lunin</t>
+          <t>Viñas</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520025dc19cbe47807000087</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4373,22 +4373,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5d43ec6312ba017aeb3ad5ae</t>
+          <t>6861bef57775a433449e9581</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sancet</t>
+          <t>Jutglà</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4400,22 +4400,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5b3341dc20ba80411d09afaf</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Lunin</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,17 +4427,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5d6c122c5501724f700d2f42</t>
+          <t>5d43ec6312ba017aeb3ad5ae</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Riquelme</t>
+          <t>Sancet</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4454,22 +4454,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4481,22 +4481,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5f496aba33a68903ecffc11e</t>
+          <t>5d6c122c5501724f700d2f42</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Diego Conde</t>
+          <t>Riquelme</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4508,17 +4508,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5f7c91e784180b4fc44cd0ee</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Raphinha</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4535,22 +4535,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>60980a25b7ad5b0920afde9e</t>
+          <t>5f496aba33a68903ecffc11e</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Carlos Domínguez</t>
+          <t>Diego Conde</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4562,22 +4562,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>62f12359f1b09a7dd27ba96c</t>
+          <t>5f7c91e784180b4fc44cd0ee</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Juanlu</t>
+          <t>Raphinha</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4589,22 +4589,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>60980a25b7ad5b0920afde9e</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Carlos Domínguez</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>63a8cd87bfb65a271f11db10</t>
+          <t>62f12359f1b09a7dd27ba96c</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Carlos Álvarez</t>
+          <t>Juanlu</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,22 +4643,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>63f14fbb79f25a5b3f34fedd</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Álvaro Rodríguez</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4670,22 +4670,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>63a8cd87bfb65a271f11db10</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Carlos Álvarez</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4697,22 +4697,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>63f14fbb79f25a5b3f34fedd</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Álvaro Rodríguez</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4724,22 +4724,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4751,22 +4751,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>66b3e34ece303803d6f77533</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Javi Rueda</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4778,22 +4778,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>66bfad063bdc581a0f65ead1</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Javi Rodríguez</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,22 +4805,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>66b3e34ece303803d6f77533</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Javi Rueda</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4832,17 +4832,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>67771f89cdd220756cfabdb0</t>
+          <t>66bfad063bdc581a0f65ead1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Garcés</t>
+          <t>Javi Rodríguez</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4859,22 +4859,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>56116ea6ffa60f6504776520</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>51b1aac753cd14971700002e</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4886,17 +4886,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>51b8ab26e401a15f2c00016a</t>
+          <t>67771f89cdd220756cfabdb0</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Carvajal</t>
+          <t>Garcés</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>584521ee88569163361f22cc</t>
+          <t>56116ea6ffa60f6504776520</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Javi Galán</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>51b1aac753cd14971700002e</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4940,17 +4940,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>51b8ab26e401a15f2c00016a</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Carvajal</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4967,22 +4967,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5ce0070a94a66a03f197ee55</t>
+          <t>584521ee88569163361f22cc</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Camello</t>
+          <t>Javi Galán</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4994,22 +4994,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5021,22 +5021,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5fbe33c11fd5fa0e8491689f</t>
+          <t>5ce0070a94a66a03f197ee55</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mingueza</t>
+          <t>Camello</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5048,17 +5048,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5075,17 +5075,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>610abc4f328e98602847897f</t>
+          <t>5fbe33c11fd5fa0e8491689f</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ratiu</t>
+          <t>Mingueza</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5102,22 +5102,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>61fef82a9b83fa2769ffc896</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Iker Benito</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5129,12 +5129,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6310da7e4028c607606859df</t>
+          <t>610abc4f328e98602847897f</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mumin</t>
+          <t>Ratiu</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5156,22 +5156,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>61fef82a9b83fa2769ffc896</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Iker Benito</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5183,22 +5183,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>541fbd531c12d0493b000a12</t>
+          <t>6310da7e4028c607606859df</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ceballos</t>
+          <t>Mumin</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5210,17 +5210,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6461127d49e91a03fb017cda</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Carlos Martín</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>541fbd531c12d0493b000a12</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Ceballos</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5264,17 +5264,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>6461127d49e91a03fb017cda</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Carlos Martín</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5291,22 +5291,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000c7</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cazorla</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5318,22 +5318,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5345,22 +5345,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>65ff69ffaa35cf4f4218da3e</t>
+          <t>51cb698301d64ad4700000c7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Pau Navarro</t>
+          <t>Cazorla</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>66ade7b9702b9203b99a16eb</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Luka Sucic</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5399,17 +5399,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>57b5c2d87e2ec2df1922966f</t>
+          <t>65ff69ffaa35cf4f4218da3e</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Elgezabal</t>
+          <t>Pau Navarro</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5426,22 +5426,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>57bb7cea45e6bed0520a420a</t>
+          <t>66ade7b9702b9203b99a16eb</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Rafa Mir</t>
+          <t>Luka Sucic</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5453,22 +5453,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>596fe00fc6269ff074e8eed3</t>
+          <t>57b5c2d87e2ec2df1922966f</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sivera</t>
+          <t>Elgezabal</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5480,17 +5480,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5d430d22b1b9c77b1c9551f7</t>
+          <t>57bb7cea45e6bed0520a420a</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nicolas Pépé</t>
+          <t>Rafa Mir</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5507,22 +5507,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>66ccfe37683d1203dc8a58b3</t>
+          <t>596fe00fc6269ff074e8eed3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Alfon</t>
+          <t>Sivera</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5534,22 +5534,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5d51a593fbc39d3fa25f7eb0</t>
+          <t>5d430d22b1b9c77b1c9551f7</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sergio Gómez</t>
+          <t>Nicolas Pépé</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5561,22 +5561,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>67772046474b6075b3a81ef3</t>
+          <t>66ccfe37683d1203dc8a58b3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Krapyvtsov</t>
+          <t>Alfon</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5588,22 +5588,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5df6b2179cb8ff03f65a7529</t>
+          <t>5d51a593fbc39d3fa25f7eb0</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Agoumé</t>
+          <t>Sergio Gómez</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5615,22 +5615,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5eef6e9c4fa17f5218f7d433</t>
+          <t>67772046474b6075b3a81ef3</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Javier López</t>
+          <t>Krapyvtsov</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5642,22 +5642,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>5df6b2179cb8ff03f65a7529</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Agoumé</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5669,17 +5669,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5f6fae0738429649dbf263d6</t>
+          <t>5eef6e9c4fa17f5218f7d433</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Boyomo</t>
+          <t>Javier López</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5696,22 +5696,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>60d73641b7fb6703d3e21ba8</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Olasagasti</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5723,22 +5723,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>60d738a576fd6803f9cb75d3</t>
+          <t>5f6fae0738429649dbf263d6</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Karrikaburu</t>
+          <t>Boyomo</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5750,22 +5750,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>61c0ff53122e933e3d15a643</t>
+          <t>60d73641b7fb6703d3e21ba8</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Iranzo</t>
+          <t>Olasagasti</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -5777,22 +5777,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>628135edd1a6e308e48ee195</t>
+          <t>60d738a576fd6803f9cb75d3</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>John Donald</t>
+          <t>Karrikaburu</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5804,17 +5804,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>630a8dadb3e9b206bc1bb9c4</t>
+          <t>61c0ff53122e933e3d15a643</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Carmona</t>
+          <t>Iranzo</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5831,17 +5831,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>628135edd1a6e308e48ee195</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>John Donald</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5858,22 +5858,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>667ddd02cf0d0c4167933890</t>
+          <t>630a8dadb3e9b206bc1bb9c4</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Abel Ruiz</t>
+          <t>Carmona</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -5885,22 +5885,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>668e7743c34e5603e02bf624</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Misehouy</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5912,22 +5912,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>667ddd02cf0d0c4167933890</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Abel Ruiz</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5939,22 +5939,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>680529fb802b9e0450bb226a</t>
+          <t>668e7743c34e5603e02bf624</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Eyong</t>
+          <t>Misehouy</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5966,22 +5966,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>586d073fc1a578af33267429</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Lenglet</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5993,22 +5993,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>680529fb802b9e0450bb226a</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Eyong</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -6020,17 +6020,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5f04e39ee9102e0410faa4fb</t>
+          <t>586d073fc1a578af33267429</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Víctor García</t>
+          <t>Lenglet</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6047,22 +6047,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -6074,17 +6074,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>5f04e39ee9102e0410faa4fb</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Víctor García</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6150ac3c7d1deb0894919f9c</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Turrientes</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6128,22 +6128,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>64a0a08ba58cb1732757ad81</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Reina</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6155,22 +6155,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>64a67bacafd9eb7360360e75</t>
+          <t>6150ac3c7d1deb0894919f9c</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Ilyas Chaira</t>
+          <t>Turrientes</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6182,22 +6182,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>66998d319e452303b3fc0ae8</t>
+          <t>64a0a08ba58cb1732757ad81</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Moussa Diarra</t>
+          <t>Reina</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6209,22 +6209,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facd</t>
+          <t>64a67bacafd9eb7360360e75</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Batalla</t>
+          <t>Ilyas Chaira</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6236,22 +6236,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>66b4b8f16e037203f626839f</t>
+          <t>66998d319e452303b3fc0ae8</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Izeta</t>
+          <t>Moussa Diarra</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6263,22 +6263,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>66b4df579e452303b3fc0b76</t>
+          <t>66a3d3797fc6ff03fb06facd</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Yoldi</t>
+          <t>Batalla</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6290,22 +6290,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>66b8fc5699635f03debf8fe8</t>
+          <t>66b4b8f16e037203f626839f</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Parada</t>
+          <t>Izeta</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6317,22 +6317,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>578a39f79572c04c06eb3daf</t>
+          <t>66b4df579e452303b3fc0b76</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Comesaña</t>
+          <t>Yoldi</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -6344,12 +6344,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>58e1616852a7d14c54bb26d3</t>
+          <t>66b8fc5699635f03debf8fe8</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Carles Aleñá</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -6371,17 +6371,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5b34a882447188471d9677fc</t>
+          <t>578a39f79572c04c06eb3daf</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Óscar Valentín</t>
+          <t>Comesaña</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6398,17 +6398,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5d58321f489a8e5316ca89d6</t>
+          <t>58e1616852a7d14c54bb26d3</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Iker Losada</t>
+          <t>Carles Aleñá</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6425,22 +6425,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5ee8f3b114cfa703f145c050</t>
+          <t>5b34a882447188471d9677fc</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Francés</t>
+          <t>Óscar Valentín</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6452,22 +6452,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5efa4e35ee5a640417710119</t>
+          <t>5d58321f489a8e5316ca89d6</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Jon Pacheco</t>
+          <t>Iker Losada</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6479,22 +6479,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>5ee8f3b114cfa703f145c050</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Francés</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6506,22 +6506,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>5efa4e35ee5a640417710119</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Jon Pacheco</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6533,22 +6533,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6560,22 +6560,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>657cccb79a154503e6fa2fa8</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Rodri Mendoza</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6587,17 +6587,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fae3</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mastantuono</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6614,17 +6614,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>657cccb79a154503e6fa2fa8</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Rodri Mendoza</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6641,22 +6641,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>66a3d3797fc6ff03fb06fae3</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Mastantuono</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6668,22 +6668,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6695,22 +6695,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>57a63dc00aba5e3906c78493</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Escandell</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6722,22 +6722,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>58cf3a6c9a7273c10560f295</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Foyth</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6749,22 +6749,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>57a63dc00aba5e3906c78493</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Escandell</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6776,22 +6776,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>596110f0f7e346dd7f32a188</t>
+          <t>58cf3a6c9a7273c10560f295</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Cucho</t>
+          <t>Foyth</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6803,22 +6803,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5995a8857c7bb19d3a5d41cd</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Nacho Vidal</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6830,17 +6830,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>596110f0f7e346dd7f32a188</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Cucho</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6857,22 +6857,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5b32c9ec3200b74d1d721549</t>
+          <t>5995a8857c7bb19d3a5d41cd</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Lemar</t>
+          <t>Nacho Vidal</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6884,17 +6884,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6911,17 +6911,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5b32c9ec3200b74d1d721549</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Lemar</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6938,22 +6938,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6965,17 +6965,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5c8bf51dc84b6a5140cdd554</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Guevara</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6992,22 +6992,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5d02362afe811c5ea82295cb</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Mendy</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -7019,22 +7019,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>5c8bf51dc84b6a5140cdd554</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Guevara</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -7046,22 +7046,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5e499be66e12ab0422cc40fb</t>
+          <t>5d02362afe811c5ea82295cb</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Unai Vencedor</t>
+          <t>Mendy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -7073,22 +7073,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5f4fd2e6c5c6f903e7c2522e</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Van de Beek</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -7100,22 +7100,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>602826e66e7e166c3abf1ec0</t>
+          <t>5e499be66e12ab0422cc40fb</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Miguel Rubio</t>
+          <t>Unai Vencedor</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -7127,17 +7127,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>614f52dfe470a3088d0b7049</t>
+          <t>5f4fd2e6c5c6f903e7c2522e</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Nico Serrano</t>
+          <t>Van de Beek</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7154,22 +7154,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>602826e66e7e166c3abf1ec0</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Miguel Rubio</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7181,22 +7181,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>614f52dfe470a3088d0b7049</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Nico Serrano</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7208,17 +7208,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7235,17 +7235,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>62c8810bb1a2d22da1beec0b</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Marcão</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7262,17 +7262,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7289,12 +7289,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>64725d78b20752040bc73eb8</t>
+          <t>62c8810bb1a2d22da1beec0b</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Bueno</t>
+          <t>Marcão</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -7316,17 +7316,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>63e943f6dea9c15b0d504d4e</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Iker Muñoz</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7343,17 +7343,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>64a7487e94e9d33cda0d9840</t>
+          <t>64725d78b20752040bc73eb8</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>S. Altimira</t>
+          <t>Bueno</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7370,22 +7370,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>64d4d45594e9d33cda0d987d</t>
+          <t>63e943f6dea9c15b0d504d4e</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Starfelt</t>
+          <t>Iker Muñoz</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7397,17 +7397,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64a7487e94e9d33cda0d9840</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>S. Altimira</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7424,17 +7424,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>64d4d45594e9d33cda0d987d</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Starfelt</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7451,22 +7451,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -7478,22 +7478,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -7505,22 +7505,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>6671ab8611ff341c4c5eac0d</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Chidera Ejuke</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7532,22 +7532,22 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -7559,12 +7559,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>6797e70083b5f103b7013774</t>
+          <t>6671ab8611ff341c4c5eac0d</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Akor Adams</t>
+          <t>Chidera Ejuke</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7586,22 +7586,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>66b8ed0a702b9203b99a1705</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Hugo Rincón</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>6797e70083b5f103b7013774</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>Akor Adams</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7640,17 +7640,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>687185e26e82700408ad8cc4</t>
+          <t>66b8ed0a702b9203b99a1705</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Léo Pétrot</t>
+          <t>Hugo Rincón</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7667,22 +7667,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -7694,22 +7694,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>687185e26e82700408ad8cc4</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Léo Pétrot</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -7721,22 +7721,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7748,17 +7748,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>59c2d829bd61e7f10c49a9b6</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Edu Expósito</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7775,22 +7775,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7802,22 +7802,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5f614957d59f315e1fc77bd2</t>
+          <t>59c2d829bd61e7f10c49a9b6</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Muriqi</t>
+          <t>Edu Expósito</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>5220ce9fc90c7ea70b000047</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -7829,22 +7829,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -7856,22 +7856,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>61efea4ec6dfbe0a4fa10b18</t>
+          <t>5f614957d59f315e1fc77bd2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Eray Cömert</t>
+          <t>Muriqi</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>5220ce9fc90c7ea70b000047</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -7883,17 +7883,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7910,22 +7910,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>635d3cab6b7e0c0865360f8d</t>
+          <t>61efea4ec6dfbe0a4fa10b18</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Pablo Durán</t>
+          <t>Eray Cömert</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7937,17 +7937,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7964,22 +7964,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>65b23452ad8bc354111e6659</t>
+          <t>635d3cab6b7e0c0865360f8d</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Adama Boiro</t>
+          <t>Pablo Durán</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -7991,22 +7991,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>665368343bd1d1040fffb355</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Yoel Lago</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -8018,12 +8018,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>65b23452ad8bc354111e6659</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Adama Boiro</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8045,22 +8045,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>6861c08a7275493329a95613</t>
+          <t>665368343bd1d1040fffb355</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dominguès</t>
+          <t>Yoel Lago</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8072,17 +8072,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>521ddaa240f3fd66010001fa</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Abdón Prats</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>6861c08a7275493329a95613</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Dominguès</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,22 +8126,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5965241adff2c6ba74e48df7</t>
+          <t>521ddaa240f3fd66010001fa</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Febas</t>
+          <t>Abdón Prats</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8153,17 +8153,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5a3578e0feceda7e2716a6c7</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrán Torres </t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8180,22 +8180,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5bd4d4dd2549d75a2c65508e</t>
+          <t>5965241adff2c6ba74e48df7</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Febas</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5d0235d88721525ead8d96db</t>
+          <t>5a3578e0feceda7e2716a6c7</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Militao</t>
+          <t xml:space="preserve">Ferrán Torres </t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8234,17 +8234,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5d0236a3167d9e5eb611db9b</t>
+          <t>5bd4d4dd2549d75a2c65508e</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Rodrygo</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>5d0235d88721525ead8d96db</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Militao</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5d69113cf91a3f7778179cb7</t>
+          <t>5d0236a3167d9e5eb611db9b</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Antonio Sánchez</t>
+          <t>Rodrygo</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,22 +8315,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5f36db010b759303ff680104</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Martín </t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6060aa1a7a64b003da0efc7d</t>
+          <t>5d69113cf91a3f7778179cb7</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Arnau Martínez</t>
+          <t>Antonio Sánchez</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8369,22 +8369,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5f36db010b759303ff680104</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t xml:space="preserve">Iván Martín </t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>61112696dfb903607d1f7e45</t>
+          <t>6060aa1a7a64b003da0efc7d</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Haissem Hassan</t>
+          <t>Arnau Martínez</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>61be5d8bd58cb63e086bb365</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Iván Romero</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,17 +8450,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>61112696dfb903607d1f7e45</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Haissem Hassan</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>6307de876f6c600403bb7bda</t>
+          <t>61be5d8bd58cb63e086bb365</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>André Almeida</t>
+          <t>Iván Romero</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,17 +8504,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>63092ba34c71a52ba37b8165</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Joel Roca</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8531,22 +8531,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>63c6945172c559051c25d9fa</t>
+          <t>6307de876f6c600403bb7bda</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Tsygankov</t>
+          <t>André Almeida</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8558,17 +8558,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>644d90d4479a44042784eb9f</t>
+          <t>63092ba34c71a52ba37b8165</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Joel Roca</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8585,22 +8585,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>64a72d1f537887736c506e33</t>
+          <t>63c6945172c559051c25d9fa</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mouriño</t>
+          <t>Tsygankov</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,22 +8612,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>644d90d4479a44042784eb9f</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8639,22 +8639,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>64eb8df805eacc03e7172e29</t>
+          <t>64a72d1f537887736c506e33</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Fermín</t>
+          <t>Mouriño</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -8666,22 +8666,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>65b68e44017f760e15bff480</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Jauregizar</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,17 +8693,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>64eb8df805eacc03e7172e29</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Fermín</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8720,17 +8720,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>57b94cfee3480bb6049eb14b</t>
+          <t>65b68e44017f760e15bff480</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Fran Beltrán</t>
+          <t>Jauregizar</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>587413fa39af105c4b075f23</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Toni Lato</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,17 +8774,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5f5a930b58df197b1823bfe7</t>
+          <t>57b94cfee3480bb6049eb14b</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Samú Costa</t>
+          <t>Fran Beltrán</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8801,22 +8801,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5f70efc9b69ba04a25453f2c</t>
+          <t>587413fa39af105c4b075f23</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Toni Lato</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8828,22 +8828,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>5f5a930b58df197b1823bfe7</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Samú Costa</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,12 +8855,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>5f70efc9b69ba04a25453f2c</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Jofre</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>63541e5a9a58e01b9ca70367</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Pablo Marín</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>63fb9deb1d17ae5aff200834</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Hugo Sotelo</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,17 +8936,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>63fd2d48e13c195af1f7112f</t>
+          <t>63541e5a9a58e01b9ca70367</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Terrats</t>
+          <t>Pablo Marín</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8963,22 +8963,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>64d1243213c6a63ccc321949</t>
+          <t>63fb9deb1d17ae5aff200834</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Campos</t>
+          <t>Hugo Sotelo</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -8990,17 +8990,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>64d803c883596124e55c064f</t>
+          <t>63fd2d48e13c195af1f7112f</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Unai Gómez</t>
+          <t>Terrats</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9017,22 +9017,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>6689c562e0157a03f87fbf0e</t>
+          <t>64d1243213c6a63ccc321949</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Morey</t>
+          <t>Campos</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -9044,17 +9044,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>66b69fb39e452303b3fc0b77</t>
+          <t>64d803c883596124e55c064f</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Dani Olmo</t>
+          <t>Unai Gómez</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9071,17 +9071,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>6689c562e0157a03f87fbf0e</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Morey</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9098,22 +9098,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>66b69fb39e452303b3fc0b77</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Dani Olmo</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,17 +9125,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>68679d128486ff33404f2eef</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Davinchi</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>68679d128486ff33404f2eef</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Davinchi</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,17 +9206,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9233,22 +9233,22 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -9260,22 +9260,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5851e8da3defeb5375f2cb30</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,17 +9287,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9314,22 +9314,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5c3f61fd864c2103cbcfdd31</t>
+          <t>5851e8da3defeb5375f2cb30</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Yangel Herrera</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -9341,22 +9341,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5d5870e8489a8e5316ca8fc0</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Moncayola</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5d9a575c370ecd5c7486de5c</t>
+          <t>5c3f61fd864c2103cbcfdd31</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Ronald Araújo</t>
+          <t>Yangel Herrera</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,22 +9395,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5d5870e8489a8e5316ca8fc0</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Moncayola</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>5d9a575c370ecd5c7486de5c</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Ronald Araújo</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9449,17 +9449,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9476,17 +9476,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>632f6f28d2f4c20bd75d484b</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Carlos Romero</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9503,17 +9503,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>64b1c5b3afeb393cf738c4f3</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Álvaro Núñez</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9530,22 +9530,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>632f6f28d2f4c20bd75d484b</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Carlos Romero</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>64b1c5b3afeb393cf738c4f3</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Álvaro Núñez</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>6689c4a399e2e504052caf27</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Rosier</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,22 +9611,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>669e6b4f99e2e504052cbbe5</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Álex Padilla</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>66b5ea2dc34e5603e02c025e</t>
+          <t>6689c4a399e2e504052caf27</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Marc Vidal</t>
+          <t>Rosier</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,22 +9665,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>66c11e2cdad1bc1a1cff9a81</t>
+          <t>669e6b4f99e2e504052cbbe5</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Gerard Martín</t>
+          <t>Álex Padilla</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9692,22 +9692,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>672f816c29e197051e04e8e4</t>
+          <t>66b5ea2dc34e5603e02c025e</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Asencio</t>
+          <t>Marc Vidal</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -9719,22 +9719,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>67575e411a57f003d0b21843</t>
+          <t>66c11e2cdad1bc1a1cff9a81</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Coba da Costa</t>
+          <t>Gerard Martín</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>6757ff71d2717703ca746142</t>
+          <t>672f816c29e197051e04e8e4</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Cabanes</t>
+          <t>Asencio</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,22 +9773,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>6795064560299f03fb5de648</t>
+          <t>67575e411a57f003d0b21843</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Ángel Ortiz</t>
+          <t>Coba da Costa</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,22 +9800,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>6757ff71d2717703ca746142</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Cabanes</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>6795064560299f03fb5de648</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Ángel Ortiz</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,22 +9854,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>51c1fdeac7694f5f66000051</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>David López</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -9881,22 +9881,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>596fc4490ef6710375cfbc85</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Javi Muñoz</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -9908,22 +9908,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5a889150e53a191d64cb8264</t>
+          <t>51c1fdeac7694f5f66000051</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Pablo Martínez</t>
+          <t>David López</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -9935,17 +9935,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5b58ada3c1287fe25740991c</t>
+          <t>596fc4490ef6710375cfbc85</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Benavídez</t>
+          <t>Javi Muñoz</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5b59e02c66831ded570d44f4</t>
+          <t>5a889150e53a191d64cb8264</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Valjent</t>
+          <t>Pablo Martínez</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,17 +9989,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5b786a5d95ea0b2b07e4e66e</t>
+          <t>5b58ada3c1287fe25740991c</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Morlanes</t>
+          <t>Benavídez</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10016,17 +10016,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5d8650e8333c3d058e0e3a3b</t>
+          <t>5b59e02c66831ded570d44f4</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Eric García</t>
+          <t>Valjent</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5f6eee81be8fe949f2105939</t>
+          <t>5b786a5d95ea0b2b07e4e66e</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Iñaki Peña</t>
+          <t>Morlanes</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,22 +10070,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5fc1512d94ce070e962e3a3c</t>
+          <t>5d8650e8333c3d058e0e3a3b</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Cárdenas</t>
+          <t>Eric García</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10097,22 +10097,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>5fc1512d94ce070e962e3a3c</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10124,22 +10124,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>612bc20d8f3edc07a4a81def</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Gavi</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>617db824fca9f703e07b2a81</t>
+          <t>612bc20d8f3edc07a4a81def</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Abde Ezzalzouli</t>
+          <t>Gavi</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>61dcacebb6d6540425b75dce</t>
+          <t>617db824fca9f703e07b2a81</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Abde Ezzalzouli</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>65ff6b016f0f544f132ae71b</t>
+          <t>61dcacebb6d6540425b75dce</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Gastón Valles</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>520384b42e80d2950b000092</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -17244,6 +17244,114 @@
         </is>
       </c>
       <c r="E623" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>63053ef3f14610075abd00f0</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Özkacar</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>6a39255e9b413b03b20c1fd5</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>De Haas</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>5738fcf88179bfa8526e19ce</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Sergi Canós</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>delantero</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>666828c79fdd6e041049a44d</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Javi Serrano</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000c8</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -1619,22 +1619,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>581fba819c916c915578e99b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Ejaria</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,22 +1646,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>581fba819c916c915578e99b</t>
+          <t>52024296ed2e70cb37000043</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ejaria</t>
+          <t>André Silva</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>52024296ed2e70cb37000043</t>
+          <t>5d63a31035a3437797dab04d</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>André Silva</t>
+          <t>Kumbulla</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1700,22 +1700,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5d63a31035a3437797dab04d</t>
+          <t>62dbcf70fa54ce2d70dddd13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kumbulla</t>
+          <t>Pickel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1727,22 +1727,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>62dbcf70fa54ce2d70dddd13</t>
+          <t>6859d8d150c8fc331b635087</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pickel</t>
+          <t>Carmo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1754,22 +1754,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6859d8d150c8fc331b635087</t>
+          <t>68b6024f9b628c03d5b3fb8b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Carmo</t>
+          <t>B. Mendy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>68b6024f9b628c03d5b3fb8b</t>
+          <t>68b602f19b628c03d5b3fb8c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B. Mendy</t>
+          <t>Abu Kamara</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1808,17 +1808,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>68b602f19b628c03d5b3fb8c</t>
+          <t>5c04e8a7bfe0253b80f7552d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abu Kamara</t>
+          <t>Lucas Beltrán</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5c04e8a7bfe0253b80f7552d</t>
+          <t>5976115f879a56720f732b5e</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lucas Beltrán</t>
+          <t>Nico González</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1862,17 +1862,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5976115f879a56720f732b5e</t>
+          <t>5d63a2b836ff30777c364c51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nico González</t>
+          <t>S. Amrabat</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1889,22 +1889,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5d63a2b836ff30777c364c51</t>
+          <t>545fd4eec664b2e852000905</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S. Amrabat</t>
+          <t>Eric Bailly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1916,17 +1916,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>545fd4eec664b2e852000905</t>
+          <t>51cc092a01d64ad470000109</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eric Bailly</t>
+          <t>Azpilicueta</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1943,22 +1943,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>51cc092a01d64ad470000109</t>
+          <t>66a3d3797fc6ff03fb06fadb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Azpilicueta</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1970,12 +1970,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fadb</t>
+          <t>6957a8d191f45503f9aa9960</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Borbas</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1997,22 +1997,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6957a8d191f45503f9aa9960</t>
+          <t>6968cb93af58fa040efb5279</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Borbas</t>
+          <t>Raghouber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2024,22 +2024,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6968cb93af58fa040efb5279</t>
+          <t>696c1bb8af58fa040efb6d15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Raghouber</t>
+          <t>Zaid Romero</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>696c1bb8af58fa040efb6d15</t>
+          <t>6970f82d1cca57043d0f4afe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Zaid Romero</t>
+          <t>Luis Vázquez</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2078,17 +2078,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6970f82d1cca57043d0f4afe</t>
+          <t>63cabb2172c559051c25de44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Luis Vázquez</t>
+          <t>Ngonge</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2105,17 +2105,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63cabb2172c559051c25de44</t>
+          <t>697e911a7602e303cbed3ffd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ngonge</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2132,17 +2132,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>697e911a7602e303cbed3ffd</t>
+          <t>69812cbb163f5f03fb3b417e</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Diabate</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2159,17 +2159,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>69812cbb163f5f03fb3b417e</t>
+          <t>6126e29b3b5c3e07dbe4c963</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Diabate</t>
+          <t>Birmancevic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2186,17 +2186,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6126e29b3b5c3e07dbe4c963</t>
+          <t>649b52e9e66c2c1e5531368e</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Birmancevic</t>
+          <t>Luvumbo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2213,22 +2213,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>649b52e9e66c2c1e5531368e</t>
+          <t>5217561c84abda6d260000e7</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luvumbo</t>
+          <t>Rubén Blanco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2240,22 +2240,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5217561c84abda6d260000e7</t>
+          <t>69eb7a681c117403c191f41a</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rubén Blanco</t>
+          <t>Saravia</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2267,17 +2267,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>69eb7a681c117403c191f41a</t>
+          <t>66d0ad52e0140203ceb61c30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Saravia</t>
+          <t>Dadie</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51fbd40cb53862dd3e00001c</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2294,22 +2294,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>66d0ad52e0140203ceb61c30</t>
+          <t>5f6eee81be8fe949f2105939</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dadie</t>
+          <t>Iñaki Peña</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>51fbd40cb53862dd3e00001c</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2321,22 +2321,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5f6eee81be8fe949f2105939</t>
+          <t>65ff6b016f0f544f132ae71b</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Iñaki Peña</t>
+          <t>Gastón Valles</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520384b42e80d2950b000092</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2348,17 +2348,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>65ff6b016f0f544f132ae71b</t>
+          <t>577fc05cd0b969de4e1a7096</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gastón Valles</t>
+          <t>Chimy Ávila</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>520384b42e80d2950b000092</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2375,22 +2375,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>577fc05cd0b969de4e1a7096</t>
+          <t>541fbd531c12d0493b000a12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chimy Ávila</t>
+          <t>Ceballos</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2402,22 +2402,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>541fbd531c12d0493b000a12</t>
+          <t>5d630db9e7e62b777ebb59be</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ceballos</t>
+          <t>Ansu Fati</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2429,22 +2429,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5d630db9e7e62b777ebb59be</t>
+          <t>6310c8d8ad2f6e072207b4c5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ansu Fati</t>
+          <t>Fuidias</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2456,22 +2456,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6310c8d8ad2f6e072207b4c5</t>
+          <t>504f64c44d8bec9a67000509</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fuidias</t>
+          <t>Nyom</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>504f64c44d8bec9a67000509</t>
+          <t>68f3b8b9dd3614500b418a49</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Nyom</t>
+          <t>Lass</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -13877,22 +13877,22 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>68f3b8b9dd3614500b418a49</t>
+          <t>68f3bc99ffaac64fef985f6e</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Lass</t>
+          <t>Toni Fernández</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -13904,22 +13904,22 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>68f3bc99ffaac64fef985f6e</t>
+          <t>68fe7b135fa52f03fe008bad</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Toni Fernández</t>
+          <t>Osambela</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -13931,17 +13931,17 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>68fe7b135fa52f03fe008bad</t>
+          <t>690c69e2c2cdbf03b2f132e8</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Osambela</t>
+          <t>Selton</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -13958,22 +13958,22 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>690c69e2c2cdbf03b2f132e8</t>
+          <t>690f6102072c5e03d67ac3e5</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Selton</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -13985,22 +13985,22 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>690f6102072c5e03d67ac3e5</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -14012,17 +14012,17 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>6935bcd342796103f7ed41db</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -14039,17 +14039,17 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6935bcd342796103f7ed41db</t>
+          <t>693c2462d47eab05710d78a0</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Valdepeñas</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -14066,17 +14066,17 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>693c2462d47eab05710d78a0</t>
+          <t>66a3d3797fc6ff03fb06fad9</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Valdepeñas</t>
+          <t>Gattoni</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -14093,22 +14093,22 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fad9</t>
+          <t>66a3c7736e037203f626834e</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Gattoni</t>
+          <t>Thiago Fernández</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -14120,22 +14120,22 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>66a3c7736e037203f626834e</t>
+          <t>695a877f1b6b9103c47320ef</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Thiago Fernández</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -14147,12 +14147,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>695a877f1b6b9103c47320ef</t>
+          <t>68b61cee09819404060c520a</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Paco Cortés</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -14174,17 +14174,17 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>68b61cee09819404060c520a</t>
+          <t>696184347cc74203effd6ff6</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Paco Cortés</t>
+          <t>Mestanza</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -14201,12 +14201,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>696184347cc74203effd6ff6</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Mestanza</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -14228,12 +14228,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>69618351e6468d03e846934a</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Montes</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -14255,17 +14255,17 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>69618351e6468d03e846934a</t>
+          <t>52024320737b88c937000019</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Montes</t>
+          <t xml:space="preserve"> João Cancelo</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -14282,17 +14282,17 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>52024320737b88c937000019</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t xml:space="preserve"> João Cancelo</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>696a39e9af58fa040efb5372</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t>Kalumba</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -14336,22 +14336,22 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>696a39e9af58fa040efb5372</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Kalumba</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -14363,22 +14363,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>66a3d3797fc6ff03fb06fadf</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Echeverri</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51d197b30719708a05000037</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -14390,17 +14390,17 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fadf</t>
+          <t>64f11152061d1303c4816c1f</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Echeverri</t>
+          <t>Tai Abed</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>51d197b30719708a05000037</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -14417,17 +14417,17 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>64f11152061d1303c4816c1f</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Tai Abed</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -14444,17 +14444,17 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>6973f63ad00321040c3be944</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Álex Sánchez</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -14471,22 +14471,22 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6973f63ad00321040c3be944</t>
+          <t>69752256a68dd603be29f508</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Álex Sánchez</t>
+          <t>Hierro</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -14498,22 +14498,22 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>69752256a68dd603be29f508</t>
+          <t>6977e9c440eaa603f8aa3e87</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Hierro</t>
+          <t>Cepeda</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -14525,22 +14525,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6977e9c440eaa603f8aa3e87</t>
+          <t>6977e776fee4e803e0e8bed5</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Cepeda</t>
+          <t>Arango</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -14552,22 +14552,22 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6977e776fee4e803e0e8bed5</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Arango</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -14579,17 +14579,17 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>675366baf7be6b107f01b952</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Fer López</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>57a12447445c20291844c142</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -14606,17 +14606,17 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>675366baf7be6b107f01b952</t>
+          <t>52017fe74f1c7f1534000047</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Fer López</t>
+          <t>Maupay</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>57a12447445c20291844c142</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -14633,22 +14633,22 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>52017fe74f1c7f1534000047</t>
+          <t>68c5f5d55bd165052e271611</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Maupay</t>
+          <t>Ángel Pérez</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -14660,17 +14660,17 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>68c5f5d55bd165052e271611</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Ángel Pérez</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -14687,17 +14687,17 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>697e90b3ff715b03c5df8278</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Koski</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>697e90b3ff715b03c5df8278</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Koski</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -14741,17 +14741,17 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>69810c427602e303cbed6a3e</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Obed Vargas</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -14768,12 +14768,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>69810c427602e303cbed6a3e</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Obed Vargas</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -14795,22 +14795,22 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -14822,12 +14822,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>5b43ab6e5c2992ae0bf69a35</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Gonzalo Villar</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -14849,17 +14849,17 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>5b43ab6e5c2992ae0bf69a35</t>
+          <t>68a0ebed3a1cb503e4684dca</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Gonzalo Villar</t>
+          <t>Jan  Salas</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -14876,17 +14876,17 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>68a0ebed3a1cb503e4684dca</t>
+          <t>51bcc35c377408301a00000c</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Jan  Salas</t>
+          <t>Vecino</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -14903,22 +14903,22 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>51bcc35c377408301a00000c</t>
+          <t>65e3820705716403fe13d771</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Vecino</t>
+          <t>Sangare</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -14930,22 +14930,22 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>65e3820705716403fe13d771</t>
+          <t>6988af503b0d1b03ea60fa11</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Sangare</t>
+          <t>Aitor Mañas</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -14957,22 +14957,22 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6988af503b0d1b03ea60fa11</t>
+          <t>69890c8d777a260432d3c68c</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Aitor Mañas</t>
+          <t>David Jiménez</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -14984,12 +14984,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>69890c8d777a260432d3c68c</t>
+          <t>69890d253b0d1b03ea61084c</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>David Jiménez</t>
+          <t>Cestero</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -15011,17 +15011,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>69890d253b0d1b03ea61084c</t>
+          <t>6990b007612d5404638c8cfe</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Cestero</t>
+          <t>Hugo López</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -15038,22 +15038,22 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6990b007612d5404638c8cfe</t>
+          <t>6992250a399cbe048cfd966e</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Hugo López</t>
+          <t>Nacho Pérez</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -15065,17 +15065,17 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6992250a399cbe048cfd966e</t>
+          <t>69a37b194f0be803ae3e49e7</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Nacho Pérez</t>
+          <t>Julio Díaz</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -15092,22 +15092,22 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>69a37b194f0be803ae3e49e7</t>
+          <t>69a5ddd7cd2bdb03fcc07f8a</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Julio Díaz</t>
+          <t>Thiago Pitarch</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -15119,12 +15119,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>69a5ddd7cd2bdb03fcc07f8a</t>
+          <t>69ab5b4653966303fb66b781</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Thiago Pitarch</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -15146,12 +15146,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>69ab5b4653966303fb66b781</t>
+          <t>69ab5b84a3657e03f770ab51</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Manuel Ángel</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -15173,12 +15173,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>69ab5b84a3657e03f770ab51</t>
+          <t>69b5e2a7c20e6203ae9f9a87</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Manuel Ángel</t>
+          <t>Diego Aguado</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15200,12 +15200,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>69b5e2a7c20e6203ae9f9a87</t>
+          <t>69b5e2e55436d103b5c952e0</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Diego Aguado</t>
+          <t>Daniel Yáñez</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15227,22 +15227,22 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>69b5e2e55436d103b5c952e0</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Daniel Yáñez</t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -15254,22 +15254,22 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>69d183cac5709804148dcb11</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>Taufik</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15281,12 +15281,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>69d183cac5709804148dcb11</t>
+          <t>69d1843021ab3804095dc5d2</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Taufik</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15308,12 +15308,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>69d1843021ab3804095dc5d2</t>
+          <t>69daa74298d9eb0426259b22</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Boñar</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15335,12 +15335,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>69daa74298d9eb0426259b22</t>
+          <t>69daa71455f89f041388274a</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Boñar</t>
+          <t>Dani Martínez</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15362,12 +15362,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>69daa71455f89f041388274a</t>
+          <t>69daa6da17877004192cea21</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Dani Martínez</t>
+          <t>Belaid</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -15389,12 +15389,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>69daa6da17877004192cea21</t>
+          <t>6687123799f9bf415ff44157</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Belaid</t>
+          <t>Puric</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -15404,7 +15404,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -15416,12 +15416,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6687123799f9bf415ff44157</t>
+          <t>69f632161fe2c90424d568b4</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Puric</t>
+          <t>Cubo</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -15443,12 +15443,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>69f632161fe2c90424d568b4</t>
+          <t>69f632503caa6b0472477da2</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Cubo</t>
+          <t>Iker Luque</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -15470,22 +15470,22 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>69f632503caa6b0472477da2</t>
+          <t>6a04f3f3f8f6ef041e55261c</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Iker Luque</t>
+          <t>Damián</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -15497,22 +15497,22 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a04f3f3f8f6ef041e55261c</t>
+          <t>6a04f502781278043f2eda16</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Damián</t>
+          <t>Orejuela</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -15524,17 +15524,17 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a04f502781278043f2eda16</t>
+          <t>6a04f759781278043f2eda18</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Orejuela</t>
+          <t>Cortés</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -15551,17 +15551,17 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a04f759781278043f2eda18</t>
+          <t>5d6d7cd40bf0ba048d4b0379</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Cortés</t>
+          <t>Thierry Correia</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -15578,12 +15578,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>5d6d7cd40bf0ba048d4b0379</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Thierry Correia</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -15605,12 +15605,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -15632,22 +15632,22 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>5989a27fd094c1ec4bdbf741</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Unai Núñez</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -15659,22 +15659,22 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>5989a27fd094c1ec4bdbf741</t>
+          <t>6a06409cd60a6e0400dd5242</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Unai Núñez</t>
+          <t>Carrera</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -15686,17 +15686,17 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a06409cd60a6e0400dd5242</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Carrera</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -15713,22 +15713,22 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>61844713165d9f09c3eecd07</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Artero</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -15740,17 +15740,17 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>61844713165d9f09c3eecd07</t>
+          <t>6a1221dac0afe2057c5f8e0c</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Artero</t>
+          <t>Ochieng</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -15767,12 +15767,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a1221dac0afe2057c5f8e0c</t>
+          <t>6a122197fd42ba053658e853</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Ochieng</t>
+          <t>Beitia</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -15794,17 +15794,17 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a122197fd42ba053658e853</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Beitia</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -15821,17 +15821,17 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>6a358ea99542a303bf19bf7a</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Sangante</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -15848,22 +15848,22 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a358ea99542a303bf19bf7a</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Sangante</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -15875,12 +15875,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15902,17 +15902,17 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>521b69bf359d42743700007f</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Carlos Fernández</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -15929,22 +15929,22 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>521b69bf359d42743700007f</t>
+          <t>65f7126c17c8f74f39434408</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Carlos Fernández</t>
+          <t>Damián Rodríguez</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -15956,17 +15956,17 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>65f7126c17c8f74f39434408</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Damián Rodríguez</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -15983,17 +15983,17 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>66a3c8069e452303b3fc0b22</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Albarracín</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -16010,17 +16010,17 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>66a3c8069e452303b3fc0b22</t>
+          <t>6a35925b33c8f103cdc11d15</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Albarracín</t>
+          <t>Bardeli</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -16037,22 +16037,22 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a35925b33c8f103cdc11d15</t>
+          <t>5d547cd98517403fd8fab746</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Bardeli</t>
+          <t>Maras</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -16064,22 +16064,22 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>5d547cd98517403fd8fab746</t>
+          <t>66ba79564942001a16eafbb7</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Maras</t>
+          <t>Dani Martín</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -16091,22 +16091,22 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>66ba79564942001a16eafbb7</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Dani Martín</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -16118,22 +16118,22 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>674b7a94c9efc910567f19b6</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -16145,17 +16145,17 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>674b7a94c9efc910567f19b6</t>
+          <t>64ea79b9b1931503ca17ef44</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Dani Requena</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -16172,22 +16172,22 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>64ea79b9b1931503ca17ef44</t>
+          <t>64d3c4746167273d0ccc5c52</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Dani Requena</t>
+          <t>Pablo Ramón</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -16199,12 +16199,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>64d3c4746167273d0ccc5c52</t>
+          <t>5cfc2be98721525ead8d94b1</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Pablo Ramón</t>
+          <t>Gragera</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -16226,22 +16226,22 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>5cfc2be98721525ead8d94b1</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Gragera</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -16253,22 +16253,22 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>6a358e6ff1bdb603db6fc1a4</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -16280,22 +16280,22 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a358e6ff1bdb603db6fc1a4</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -16307,22 +16307,22 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>688fbfc45c7211044690a3d3</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Selu Diallo</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -16334,22 +16334,22 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>688fbfc45c7211044690a3d3</t>
+          <t>66c25f14b5741f1a24b155a4</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Selu Diallo</t>
+          <t>Barzic</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -16361,12 +16361,12 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>66c25f14b5741f1a24b155a4</t>
+          <t>6610624ad70dc004141ec091</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Barzic</t>
+          <t>Rafa Núñez</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -16388,17 +16388,17 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6610624ad70dc004141ec091</t>
+          <t>6683c6e90ab8ba417f3276b6</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Rafa Núñez</t>
+          <t>Unai Ropero</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -16415,17 +16415,17 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6683c6e90ab8ba417f3276b6</t>
+          <t>66bb83844942001a16eafbb8</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Unai Ropero</t>
+          <t>Javi Hernández</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -16442,17 +16442,17 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>66bb83844942001a16eafbb8</t>
+          <t>66f98191043342085bbcc7ce</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Javi Hernández</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -16469,22 +16469,22 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>66f98191043342085bbcc7ce</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Peio Canales</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -16496,22 +16496,22 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>5e23437d616e7d03ba5dc21c</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -16523,22 +16523,22 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>5e23437d616e7d03ba5dc21c</t>
+          <t>614743ace216464c91a29186</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Owono</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -16550,22 +16550,22 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>614743ace216464c91a29186</t>
+          <t>61c3b14eb4f96c073bf94ce7</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Owono</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -16577,22 +16577,22 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>61c3b14eb4f96c073bf94ce7</t>
+          <t>67d4acc7fb012703e17d1dc5</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Adrián R.</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -16604,17 +16604,17 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>67d4acc7fb012703e17d1dc5</t>
+          <t>686feb558bef76044eadf791</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Adrián R.</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -16631,22 +16631,22 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>686feb558bef76044eadf791</t>
+          <t>66cfa272b46ff704160ad00e</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Adrián Pica</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -16658,17 +16658,17 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>66cfa272b46ff704160ad00e</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Adrián Pica</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -16685,12 +16685,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>59510d122a7f2df00504ab30</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Cucurella</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -16712,12 +16712,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>59510d122a7f2df00504ab30</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Cucurella</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
@@ -16739,17 +16739,17 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>64b9b83013c6a63ccc32191b</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Carlos Dotor</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -16766,17 +16766,17 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>64b9b83013c6a63ccc32191b</t>
+          <t>6866a56fca97b13338e6cd0b</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Carlos Dotor</t>
+          <t>Goti</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -16793,22 +16793,22 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6866a56fca97b13338e6cd0b</t>
+          <t>66c8333550cfa503c1736efc</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Goti</t>
+          <t>Diaby</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -16820,22 +16820,22 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>66c8333550cfa503c1736efc</t>
+          <t>66d39b3d58f2de32117efa18</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Diaby</t>
+          <t>Domenech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -16847,12 +16847,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>66d39b3d58f2de32117efa18</t>
+          <t>67597e6b317cba0418bce297</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Domenech</t>
+          <t>Dani Luna</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -16874,17 +16874,17 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>67597e6b317cba0418bce297</t>
+          <t>57b94a3c7ce1feed040b24e3</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Dani Luna</t>
+          <t>Jacobo González</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -16901,12 +16901,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>57b94a3c7ce1feed040b24e3</t>
+          <t>60e6e2841a405a604ca8c2d7</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Jacobo González</t>
+          <t>Luengo</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -16928,12 +16928,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>60e6e2841a405a604ca8c2d7</t>
+          <t>64b1c502c35fcb3cfd3ed505</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Luengo</t>
+          <t>Youness</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -16955,12 +16955,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>64b1c502c35fcb3cfd3ed505</t>
+          <t>6865adefd4d22b330615f7ca</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Youness</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16982,12 +16982,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6865adefd4d22b330615f7ca</t>
+          <t>6584aa689b9f5d700573fd05</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Cardero</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -17009,12 +17009,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6584aa689b9f5d700573fd05</t>
+          <t>669274f3ce303803d6f77330</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Cardero</t>
+          <t>Paraschiv</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -17036,12 +17036,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>669274f3ce303803d6f77330</t>
+          <t>62b3117afea5532da7ee56f0</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Paraschiv</t>
+          <t>Del Moral</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -17063,17 +17063,17 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>62b3117afea5532da7ee56f0</t>
+          <t>697be226df6332040670c6c1</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Del Moral</t>
+          <t>Izan González</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -17090,12 +17090,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>697be226df6332040670c6c1</t>
+          <t>6a35c168152d0603c64c029a</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Izan González</t>
+          <t>Pyshchur</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -17117,12 +17117,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a35c168152d0603c64c029a</t>
+          <t>66c9b0acf119260402e26288</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Pyshchur</t>
+          <t>Asprilla</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -17144,12 +17144,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>66c9b0acf119260402e26288</t>
+          <t>68a9e8aab479f05404a946c8</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Asprilla</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -17171,12 +17171,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>68a9e8aab479f05404a946c8</t>
+          <t>6713fdc9a1b917176a03238a</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Min-su Kim</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -17198,12 +17198,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6713fdc9a1b917176a03238a</t>
+          <t>65f5fc5000ffc34f05f1cb1f</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Min-su Kim</t>
+          <t>Jastin</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -17225,22 +17225,22 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>65f5fc5000ffc34f05f1cb1f</t>
+          <t>6a39255e9b413b03b20c1fd5</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Jastin</t>
+          <t>De Haas</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -17252,12 +17252,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a39255e9b413b03b20c1fd5</t>
+          <t>63053ef3f14610075abd00f0</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>De Haas</t>
+          <t>Özkacar</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -17279,22 +17279,22 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>63053ef3f14610075abd00f0</t>
+          <t>666828c79fdd6e041049a44d</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Özkacar</t>
+          <t>Javi Serrano</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -17306,17 +17306,17 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>666828c79fdd6e041049a44d</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Javi Serrano</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -17333,22 +17333,22 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -17360,22 +17360,22 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>6861890daedcdd33075dd01d</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Adri Fuentes</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -17387,22 +17387,22 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6861890daedcdd33075dd01d</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Adri Fuentes</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E630"/>
+  <dimension ref="A1:E631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2861,17 +2861,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>59c40c341962b7220d0c523e</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Brais Méndez</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2888,22 +2888,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2915,22 +2915,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2942,22 +2942,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2969,22 +2969,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2996,22 +2996,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3023,22 +3023,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>51d70ed7a7178a7654000012</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mojica</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3050,22 +3050,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>51d70ed7a7178a7654000012</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Mojica</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3077,22 +3077,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3104,22 +3104,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3131,22 +3131,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3158,22 +3158,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>504f647e4d8bec9a67000484</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stuani</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3185,22 +3185,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>504f647e4d8bec9a67000484</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Stuani</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3212,22 +3212,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3239,22 +3239,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3266,22 +3266,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5313988280c359915f000011</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Portu</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3293,17 +3293,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>5313988280c359915f000011</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Portu</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3320,22 +3320,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3347,22 +3347,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3374,12 +3374,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3401,22 +3401,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3455,22 +3455,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3482,17 +3482,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3536,22 +3536,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3563,22 +3563,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3590,17 +3590,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3617,12 +3617,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3644,22 +3644,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3671,22 +3671,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>51cab26c01d64ad470000096</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Gazzaniga</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3698,22 +3698,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>51cab26c01d64ad470000096</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Gazzaniga</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5210908da776cc826b000067</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Darder</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3752,22 +3752,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>5210908da776cc826b000067</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Darder</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3806,22 +3806,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3833,12 +3833,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3860,22 +3860,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>54c509f75d97b9070200178c</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dani Calvo</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3887,22 +3887,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>54c509f75d97b9070200178c</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Dani Calvo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3914,12 +3914,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>577743d027ae4bd9135ae3d8</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nahuel Molina</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3941,22 +3941,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>57583b4733dbe3424c05e8ee</t>
+          <t>577743d027ae4bd9135ae3d8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Luis Milla</t>
+          <t>Nahuel Molina</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>6662aa5981b2080416a23781</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3968,17 +3968,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>57583b4733dbe3424c05e8ee</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Luis Milla</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>6662aa5981b2080416a23781</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3995,22 +3995,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4022,17 +4022,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>521b5f939f2adc783700001e</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>David Costas</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4049,17 +4049,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>520263c1ed2e70cb370000c1</t>
+          <t>521b5f939f2adc783700001e</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Raíllo</t>
+          <t>David Costas</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4076,17 +4076,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>520263c1ed2e70cb370000c1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Raíllo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4103,17 +4103,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4130,22 +4130,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4184,17 +4184,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>504f65684d8bec9a6700072d</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Griezmann</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4211,17 +4211,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>504f65684d8bec9a6700072d</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,22 +4238,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4265,22 +4265,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000bc</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Szczesny</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,22 +4292,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>51cb698301d64ad4700000bc</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Szczesny</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4319,17 +4319,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>59c419ed548e551c0db5b308</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Gorosabel</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4346,17 +4346,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>59c419ed548e551c0db5b308</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Gorosabel</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4373,17 +4373,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5c0eea87e3eca97d26f62cee</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pedrosa</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4400,22 +4400,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5d17ceb62cef430674ec2674</t>
+          <t>5c0eea87e3eca97d26f62cee</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Isi Palazón</t>
+          <t>Pedrosa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5d17ceb62cef430674ec2674</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Isi Palazón</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4454,17 +4454,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5f0cbbb3075d9b03e1b24de9</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Baena</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4481,17 +4481,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5f0cbbb3075d9b03e1b24de9</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Baena</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4508,22 +4508,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6126993bb52ba2079fdc7828</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sorloth</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4535,22 +4535,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>614cc15d3916210732959cc3</t>
+          <t>6126993bb52ba2079fdc7828</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Robert Navarro</t>
+          <t>Sorloth</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4562,22 +4562,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>614cc15d3916210732959cc3</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Robert Navarro</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4589,22 +4589,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>62fd1a08e88c090690b05916</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nianzou</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,17 +4643,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>630274ff9906dc0691df670b</t>
+          <t>62fd1a08e88c090690b05916</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Bretones</t>
+          <t>Nianzou</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4670,22 +4670,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>63d8eb7b1d17ae5aff1f4c52</t>
+          <t>630274ff9906dc0691df670b</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Bretones</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4697,22 +4697,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>65b56235a3176a0e0fdb8f74</t>
+          <t>63d8eb7b1d17ae5aff1f4c52</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Héctor Fort</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4724,22 +4724,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6647cad9bd5be20441bcc95c</t>
+          <t>65b56235a3176a0e0fdb8f74</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Boayar</t>
+          <t>Héctor Fort</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4751,22 +4751,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>6647cad9bd5be20441bcc95c</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Boayar</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4778,22 +4778,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>66cf964ebd0d6403c8b5d5ad</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Viñas</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>520025dc19cbe47807000087</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,17 +4805,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6861bef57775a433449e9581</t>
+          <t>66cf964ebd0d6403c8b5d5ad</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jutglà</t>
+          <t>Viñas</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520025dc19cbe47807000087</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4832,22 +4832,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5b3341dc20ba80411d09afaf</t>
+          <t>6861bef57775a433449e9581</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lunin</t>
+          <t>Jutglà</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4859,22 +4859,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5d43ec6312ba017aeb3ad5ae</t>
+          <t>5b3341dc20ba80411d09afaf</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sancet</t>
+          <t>Lunin</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4886,22 +4886,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5d43ec6312ba017aeb3ad5ae</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Sancet</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,22 +4913,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5d6c122c5501724f700d2f42</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Riquelme</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4940,22 +4940,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>5d6c122c5501724f700d2f42</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Riquelme</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4967,22 +4967,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5f496aba33a68903ecffc11e</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Diego Conde</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4994,22 +4994,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5f7c91e784180b4fc44cd0ee</t>
+          <t>5f496aba33a68903ecffc11e</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Raphinha</t>
+          <t>Diego Conde</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5021,22 +5021,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>60980a25b7ad5b0920afde9e</t>
+          <t>5f7c91e784180b4fc44cd0ee</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Carlos Domínguez</t>
+          <t>Raphinha</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5048,17 +5048,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>62f12359f1b09a7dd27ba96c</t>
+          <t>60980a25b7ad5b0920afde9e</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Juanlu</t>
+          <t>Carlos Domínguez</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5075,22 +5075,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>62f12359f1b09a7dd27ba96c</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Juanlu</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,17 +5102,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>63a8cd87bfb65a271f11db10</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Carlos Álvarez</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5129,22 +5129,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>63f14fbb79f25a5b3f34fedd</t>
+          <t>63a8cd87bfb65a271f11db10</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Álvaro Rodríguez</t>
+          <t>Carlos Álvarez</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5156,22 +5156,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>63f14fbb79f25a5b3f34fedd</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Álvaro Rodríguez</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5183,22 +5183,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5210,22 +5210,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>66b3e34ece303803d6f77533</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Javi Rueda</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5264,12 +5264,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>66bfad063bdc581a0f65ead1</t>
+          <t>66b3e34ece303803d6f77533</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Javi Rodríguez</t>
+          <t>Javi Rueda</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5291,22 +5291,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>66bfad063bdc581a0f65ead1</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Javi Rodríguez</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5318,22 +5318,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>67771f89cdd220756cfabdb0</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Garcés</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5345,17 +5345,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>56116ea6ffa60f6504776520</t>
+          <t>67771f89cdd220756cfabdb0</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Garcés</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>51b1aac753cd14971700002e</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5372,17 +5372,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>51b8ab26e401a15f2c00016a</t>
+          <t>56116ea6ffa60f6504776520</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Carvajal</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>51b1aac753cd14971700002e</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5399,17 +5399,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>584521ee88569163361f22cc</t>
+          <t>51b8ab26e401a15f2c00016a</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Javi Galán</t>
+          <t>Carvajal</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5426,17 +5426,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>584521ee88569163361f22cc</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Javi Galán</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5453,22 +5453,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5ce0070a94a66a03f197ee55</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Camello</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5480,22 +5480,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>5ce0070a94a66a03f197ee55</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Camello</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5507,22 +5507,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5fbe33c11fd5fa0e8491689f</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Mingueza</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5534,22 +5534,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>5fbe33c11fd5fa0e8491689f</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Mingueza</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5561,22 +5561,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>610abc4f328e98602847897f</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ratiu</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5588,22 +5588,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>61fef82a9b83fa2769ffc896</t>
+          <t>610abc4f328e98602847897f</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Iker Benito</t>
+          <t>Ratiu</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5615,17 +5615,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>61fef82a9b83fa2769ffc896</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Iker Benito</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5642,17 +5642,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>6461127d49e91a03fb017cda</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Carlos Martín</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5669,22 +5669,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>6461127d49e91a03fb017cda</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Carlos Martín</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5696,22 +5696,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5723,22 +5723,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5750,17 +5750,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>65ff69ffaa35cf4f4218da3e</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Pau Navarro</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5777,22 +5777,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>66ade7b9702b9203b99a16eb</t>
+          <t>65ff69ffaa35cf4f4218da3e</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Luka Sucic</t>
+          <t>Pau Navarro</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5804,22 +5804,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>57b5c2d87e2ec2df1922966f</t>
+          <t>66ade7b9702b9203b99a16eb</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Elgezabal</t>
+          <t>Luka Sucic</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -5831,22 +5831,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>57bb7cea45e6bed0520a420a</t>
+          <t>57b5c2d87e2ec2df1922966f</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Rafa Mir</t>
+          <t>Elgezabal</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5858,22 +5858,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>596fe00fc6269ff074e8eed3</t>
+          <t>57bb7cea45e6bed0520a420a</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Sivera</t>
+          <t>Rafa Mir</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -5885,22 +5885,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5d430d22b1b9c77b1c9551f7</t>
+          <t>596fe00fc6269ff074e8eed3</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Nicolas Pépé</t>
+          <t>Sivera</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5912,22 +5912,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>66ccfe37683d1203dc8a58b3</t>
+          <t>5d430d22b1b9c77b1c9551f7</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Alfon</t>
+          <t>Nicolas Pépé</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5939,22 +5939,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5d51a593fbc39d3fa25f7eb0</t>
+          <t>66ccfe37683d1203dc8a58b3</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sergio Gómez</t>
+          <t>Alfon</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5966,22 +5966,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>67772046474b6075b3a81ef3</t>
+          <t>5d51a593fbc39d3fa25f7eb0</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Krapyvtsov</t>
+          <t>Sergio Gómez</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5993,22 +5993,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5df6b2179cb8ff03f65a7529</t>
+          <t>67772046474b6075b3a81ef3</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Agoumé</t>
+          <t>Krapyvtsov</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -6020,22 +6020,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5eef6e9c4fa17f5218f7d433</t>
+          <t>5df6b2179cb8ff03f65a7529</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Javier López</t>
+          <t>Agoumé</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6047,17 +6047,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>5eef6e9c4fa17f5218f7d433</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Javier López</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6074,17 +6074,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5f6fae0738429649dbf263d6</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Boyomo</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>60d73641b7fb6703d3e21ba8</t>
+          <t>5f6fae0738429649dbf263d6</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Olasagasti</t>
+          <t>Boyomo</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6128,22 +6128,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>60d738a576fd6803f9cb75d3</t>
+          <t>60d73641b7fb6703d3e21ba8</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Karrikaburu</t>
+          <t>Olasagasti</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6155,22 +6155,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>61c0ff53122e933e3d15a643</t>
+          <t>60d738a576fd6803f9cb75d3</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Iranzo</t>
+          <t>Karrikaburu</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6182,17 +6182,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>628135edd1a6e308e48ee195</t>
+          <t>61c0ff53122e933e3d15a643</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>John Donald</t>
+          <t>Iranzo</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6209,17 +6209,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>630a8dadb3e9b206bc1bb9c4</t>
+          <t>628135edd1a6e308e48ee195</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Carmona</t>
+          <t>John Donald</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6236,17 +6236,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>630a8dadb3e9b206bc1bb9c4</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Carmona</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6263,22 +6263,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>667ddd02cf0d0c4167933890</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Abel Ruiz</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6290,12 +6290,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>668e7743c34e5603e02bf624</t>
+          <t>667ddd02cf0d0c4167933890</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Misehouy</t>
+          <t>Abel Ruiz</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6317,17 +6317,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>668e7743c34e5603e02bf624</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Misehouy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6344,22 +6344,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>680529fb802b9e0450bb226a</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Eyong</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -6371,22 +6371,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>680529fb802b9e0450bb226a</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Eyong</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -6398,22 +6398,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5f04e39ee9102e0410faa4fb</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Víctor García</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6425,17 +6425,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5f04e39ee9102e0410faa4fb</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Víctor García</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6452,17 +6452,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6479,22 +6479,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6150ac3c7d1deb0894919f9c</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Turrientes</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6506,17 +6506,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>64a0a08ba58cb1732757ad81</t>
+          <t>6150ac3c7d1deb0894919f9c</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Reina</t>
+          <t>Turrientes</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6533,12 +6533,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>64a67bacafd9eb7360360e75</t>
+          <t>64a0a08ba58cb1732757ad81</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Ilyas Chaira</t>
+          <t>Reina</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6560,22 +6560,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>66998d319e452303b3fc0ae8</t>
+          <t>64a67bacafd9eb7360360e75</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Moussa Diarra</t>
+          <t>Ilyas Chaira</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6587,22 +6587,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facd</t>
+          <t>66998d319e452303b3fc0ae8</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Batalla</t>
+          <t>Moussa Diarra</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -6614,22 +6614,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>66b4b8f16e037203f626839f</t>
+          <t>66a3d3797fc6ff03fb06facd</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Izeta</t>
+          <t>Batalla</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -6641,17 +6641,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>66b4df579e452303b3fc0b76</t>
+          <t>66b4b8f16e037203f626839f</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Yoldi</t>
+          <t>Izeta</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6668,22 +6668,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>66b8fc5699635f03debf8fe8</t>
+          <t>66b4df579e452303b3fc0b76</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Parada</t>
+          <t>Yoldi</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6695,22 +6695,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>578a39f79572c04c06eb3daf</t>
+          <t>66b8fc5699635f03debf8fe8</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Comesaña</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6722,17 +6722,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>58e1616852a7d14c54bb26d3</t>
+          <t>578a39f79572c04c06eb3daf</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Carles Aleñá</t>
+          <t>Comesaña</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6749,17 +6749,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5b34a882447188471d9677fc</t>
+          <t>58e1616852a7d14c54bb26d3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Óscar Valentín</t>
+          <t>Carles Aleñá</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6776,17 +6776,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5d58321f489a8e5316ca89d6</t>
+          <t>5b34a882447188471d9677fc</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Iker Losada</t>
+          <t>Óscar Valentín</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6803,22 +6803,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5ee8f3b114cfa703f145c050</t>
+          <t>5d58321f489a8e5316ca89d6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Francés</t>
+          <t>Iker Losada</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6830,17 +6830,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5efa4e35ee5a640417710119</t>
+          <t>5ee8f3b114cfa703f145c050</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Jon Pacheco</t>
+          <t>Francés</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6857,22 +6857,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>5efa4e35ee5a640417710119</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Jon Pacheco</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6884,12 +6884,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6911,17 +6911,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6938,22 +6938,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>657cccb79a154503e6fa2fa8</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Rodri Mendoza</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6965,17 +6965,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fae3</t>
+          <t>657cccb79a154503e6fa2fa8</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mastantuono</t>
+          <t>Rodri Mendoza</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6992,17 +6992,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>66a3d3797fc6ff03fb06fae3</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Mastantuono</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7019,22 +7019,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -7046,22 +7046,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -7073,22 +7073,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>57a63dc00aba5e3906c78493</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Escandell</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -7100,22 +7100,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>58cf3a6c9a7273c10560f295</t>
+          <t>57a63dc00aba5e3906c78493</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Foyth</t>
+          <t>Escandell</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -7127,22 +7127,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>58cf3a6c9a7273c10560f295</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Foyth</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -7154,12 +7154,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>596110f0f7e346dd7f32a188</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Cucho</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7181,22 +7181,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5995a8857c7bb19d3a5d41cd</t>
+          <t>596110f0f7e346dd7f32a188</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Nacho Vidal</t>
+          <t>Cucho</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7208,22 +7208,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>5995a8857c7bb19d3a5d41cd</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Nacho Vidal</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -7235,22 +7235,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5b32c9ec3200b74d1d721549</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Lemar</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -7262,22 +7262,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5b32c9ec3200b74d1d721549</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Lemar</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -7289,22 +7289,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -7316,17 +7316,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7343,17 +7343,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5c8bf51dc84b6a5140cdd554</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Guevara</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7370,22 +7370,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5d02362afe811c5ea82295cb</t>
+          <t>5c8bf51dc84b6a5140cdd554</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mendy</t>
+          <t>Guevara</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7397,22 +7397,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>5d02362afe811c5ea82295cb</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Mendy</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7424,22 +7424,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5e499be66e12ab0422cc40fb</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Unai Vencedor</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -7451,17 +7451,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5f4fd2e6c5c6f903e7c2522e</t>
+          <t>5e499be66e12ab0422cc40fb</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Van de Beek</t>
+          <t>Unai Vencedor</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7478,22 +7478,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>602826e66e7e166c3abf1ec0</t>
+          <t>5f4fd2e6c5c6f903e7c2522e</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Miguel Rubio</t>
+          <t>Van de Beek</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -7505,22 +7505,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>614f52dfe470a3088d0b7049</t>
+          <t>602826e66e7e166c3abf1ec0</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nico Serrano</t>
+          <t>Miguel Rubio</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7532,17 +7532,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>614f52dfe470a3088d0b7049</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Nico Serrano</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7559,22 +7559,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7586,22 +7586,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7613,22 +7613,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>62c8810bb1a2d22da1beec0b</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Marcão</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -7640,22 +7640,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62c8810bb1a2d22da1beec0b</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>Marcão</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -7667,17 +7667,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>64725d78b20752040bc73eb8</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Bueno</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7694,17 +7694,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>63e943f6dea9c15b0d504d4e</t>
+          <t>64725d78b20752040bc73eb8</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Iker Muñoz</t>
+          <t>Bueno</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7721,22 +7721,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>64d4d45594e9d33cda0d987d</t>
+          <t>63e943f6dea9c15b0d504d4e</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Starfelt</t>
+          <t>Iker Muñoz</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7748,12 +7748,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d4d45594e9d33cda0d987d</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Starfelt</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7775,22 +7775,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7802,17 +7802,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7829,22 +7829,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -7856,17 +7856,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>6671ab8611ff341c4c5eac0d</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Chidera Ejuke</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7883,22 +7883,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>6671ab8611ff341c4c5eac0d</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Chidera Ejuke</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7910,17 +7910,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>6797e70083b5f103b7013774</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Akor Adams</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7937,22 +7937,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>66b8ed0a702b9203b99a1705</t>
+          <t>6797e70083b5f103b7013774</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Hugo Rincón</t>
+          <t>Akor Adams</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -7964,22 +7964,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>66b8ed0a702b9203b99a1705</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>Hugo Rincón</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8018,17 +8018,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8045,17 +8045,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8072,17 +8072,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>59c2d829bd61e7f10c49a9b6</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Edu Expósito</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>59c2d829bd61e7f10c49a9b6</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Edu Expósito</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,22 +8126,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5f614957d59f315e1fc77bd2</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Muriqi</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>5220ce9fc90c7ea70b000047</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8153,22 +8153,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5f614957d59f315e1fc77bd2</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Muriqi</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>5220ce9fc90c7ea70b000047</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8180,22 +8180,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>61efea4ec6dfbe0a4fa10b18</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Eray Cömert</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>52026c99fdbb14c13700007f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>61efea4ec6dfbe0a4fa10b18</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Eray Cömert</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52026c99fdbb14c13700007f</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8234,22 +8234,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>635d3cab6b7e0c0865360f8d</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Pablo Durán</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>635d3cab6b7e0c0865360f8d</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Pablo Durán</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>65b23452ad8bc354111e6659</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Adama Boiro</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,17 +8315,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>665368343bd1d1040fffb355</t>
+          <t>65b23452ad8bc354111e6659</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Yoel Lago</t>
+          <t>Adama Boiro</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>665368343bd1d1040fffb355</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Yoel Lago</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8369,22 +8369,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>6861c08a7275493329a95613</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Dominguès</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>521ddaa240f3fd66010001fa</t>
+          <t>6861c08a7275493329a95613</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Abdón Prats</t>
+          <t>Dominguès</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,17 +8423,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>521ddaa240f3fd66010001fa</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Abdón Prats</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5965241adff2c6ba74e48df7</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Febas</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5a3578e0feceda7e2716a6c7</t>
+          <t>5965241adff2c6ba74e48df7</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrán Torres </t>
+          <t>Febas</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,17 +8504,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5bd4d4dd2549d75a2c65508e</t>
+          <t>5a3578e0feceda7e2716a6c7</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t xml:space="preserve">Ferrán Torres </t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8531,22 +8531,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5d0235d88721525ead8d96db</t>
+          <t>5bd4d4dd2549d75a2c65508e</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Militao</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5d0236a3167d9e5eb611db9b</t>
+          <t>5d0235d88721525ead8d96db</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Rodrygo</t>
+          <t>Militao</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,22 +8585,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>5d0236a3167d9e5eb611db9b</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Rodrygo</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,17 +8612,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5d69113cf91a3f7778179cb7</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Antonio Sánchez</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8639,17 +8639,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5f36db010b759303ff680104</t>
+          <t>5d69113cf91a3f7778179cb7</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Martín </t>
+          <t>Antonio Sánchez</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8666,12 +8666,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>6060aa1a7a64b003da0efc7d</t>
+          <t>5f36db010b759303ff680104</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Arnau Martínez</t>
+          <t xml:space="preserve">Iván Martín </t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,17 +8693,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>6060aa1a7a64b003da0efc7d</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Arnau Martínez</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8720,22 +8720,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>61112696dfb903607d1f7e45</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Haissem Hassan</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8747,17 +8747,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>61be5d8bd58cb63e086bb365</t>
+          <t>61112696dfb903607d1f7e45</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Iván Romero</t>
+          <t>Haissem Hassan</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8774,17 +8774,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>61be5d8bd58cb63e086bb365</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Iván Romero</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8801,22 +8801,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>6307de876f6c600403bb7bda</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>André Almeida</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8828,22 +8828,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>63092ba34c71a52ba37b8165</t>
+          <t>6307de876f6c600403bb7bda</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Joel Roca</t>
+          <t>André Almeida</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,12 +8855,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>63c6945172c559051c25d9fa</t>
+          <t>63092ba34c71a52ba37b8165</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Tsygankov</t>
+          <t>Joel Roca</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8882,17 +8882,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>644d90d4479a44042784eb9f</t>
+          <t>63c6945172c559051c25d9fa</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Tsygankov</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>64a72d1f537887736c506e33</t>
+          <t>644d90d4479a44042784eb9f</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Mouriño</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,17 +8936,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>64a72d1f537887736c506e33</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Mouriño</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8963,22 +8963,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>64eb8df805eacc03e7172e29</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Fermín</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -8990,17 +8990,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>65b68e44017f760e15bff480</t>
+          <t>64eb8df805eacc03e7172e29</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jauregizar</t>
+          <t>Fermín</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9017,17 +9017,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>65b68e44017f760e15bff480</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Jauregizar</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9044,17 +9044,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>57b94cfee3480bb6049eb14b</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Fran Beltrán</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9071,22 +9071,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>587413fa39af105c4b075f23</t>
+          <t>57b94cfee3480bb6049eb14b</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Toni Lato</t>
+          <t>Fran Beltrán</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -9098,12 +9098,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5f5a930b58df197b1823bfe7</t>
+          <t>587413fa39af105c4b075f23</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Samú Costa</t>
+          <t>Toni Lato</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,17 +9125,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5f70efc9b69ba04a25453f2c</t>
+          <t>5f5a930b58df197b1823bfe7</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Samú Costa</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>5f70efc9b69ba04a25453f2c</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Jofre</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,17 +9179,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9206,22 +9206,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>63541e5a9a58e01b9ca70367</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Pablo Marín</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>63fb9deb1d17ae5aff200834</t>
+          <t>63541e5a9a58e01b9ca70367</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Hugo Sotelo</t>
+          <t>Pablo Marín</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,17 +9260,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>63fd2d48e13c195af1f7112f</t>
+          <t>63fb9deb1d17ae5aff200834</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Terrats</t>
+          <t>Hugo Sotelo</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9287,22 +9287,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>64d1243213c6a63ccc321949</t>
+          <t>63fd2d48e13c195af1f7112f</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Campos</t>
+          <t>Terrats</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -9314,22 +9314,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>64d803c883596124e55c064f</t>
+          <t>64d1243213c6a63ccc321949</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Unai Gómez</t>
+          <t>Campos</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -9341,22 +9341,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>6689c562e0157a03f87fbf0e</t>
+          <t>64d803c883596124e55c064f</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Morey</t>
+          <t>Unai Gómez</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>66b69fb39e452303b3fc0b77</t>
+          <t>6689c562e0157a03f87fbf0e</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Dani Olmo</t>
+          <t>Morey</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,22 +9395,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>66b69fb39e452303b3fc0b77</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Dani Olmo</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9422,22 +9422,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9449,22 +9449,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>68679d128486ff33404f2eef</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Davinchi</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -9476,22 +9476,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>68679d128486ff33404f2eef</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Davinchi</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,17 +9530,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,17 +9584,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5851e8da3defeb5375f2cb30</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9611,17 +9611,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>5851e8da3defeb5375f2cb30</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5c3f61fd864c2103cbcfdd31</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Yangel Herrera</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,17 +9665,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5d5870e8489a8e5316ca8fc0</t>
+          <t>5c3f61fd864c2103cbcfdd31</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Moncayola</t>
+          <t>Yangel Herrera</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9692,22 +9692,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5d9a575c370ecd5c7486de5c</t>
+          <t>5d5870e8489a8e5316ca8fc0</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Ronald Araújo</t>
+          <t>Moncayola</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -9719,17 +9719,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5d9a575c370ecd5c7486de5c</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Ronald Araújo</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9746,17 +9746,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9773,17 +9773,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9800,12 +9800,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>632f6f28d2f4c20bd75d484b</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Carlos Romero</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -9827,17 +9827,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>64b1c5b3afeb393cf738c4f3</t>
+          <t>632f6f28d2f4c20bd75d484b</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Álvaro Núñez</t>
+          <t>Carlos Romero</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9854,22 +9854,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>64b1c5b3afeb393cf738c4f3</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Álvaro Núñez</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -9881,22 +9881,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -9908,22 +9908,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>6689c4a399e2e504052caf27</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Rosier</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>669e6b4f99e2e504052cbbe5</t>
+          <t>6689c4a399e2e504052caf27</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Álex Padilla</t>
+          <t>Rosier</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>66c11e2cdad1bc1a1cff9a81</t>
+          <t>669e6b4f99e2e504052cbbe5</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Gerard Martín</t>
+          <t>Álex Padilla</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,17 +9989,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>672f816c29e197051e04e8e4</t>
+          <t>66c11e2cdad1bc1a1cff9a81</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Asencio</t>
+          <t>Gerard Martín</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10016,22 +10016,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>67575e411a57f003d0b21843</t>
+          <t>672f816c29e197051e04e8e4</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Coba da Costa</t>
+          <t>Asencio</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,17 +10043,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>6757ff71d2717703ca746142</t>
+          <t>67575e411a57f003d0b21843</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Cabanes</t>
+          <t>Coba da Costa</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10070,22 +10070,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>6795064560299f03fb5de648</t>
+          <t>6757ff71d2717703ca746142</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Ángel Ortiz</t>
+          <t>Cabanes</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10097,22 +10097,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>6795064560299f03fb5de648</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Ángel Ortiz</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10124,17 +10124,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>51c1fdeac7694f5f66000051</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>David López</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>596fc4490ef6710375cfbc85</t>
+          <t>51c1fdeac7694f5f66000051</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Javi Muñoz</t>
+          <t>David López</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,17 +10205,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5b58ada3c1287fe25740991c</t>
+          <t>596fc4490ef6710375cfbc85</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Benavídez</t>
+          <t>Javi Muñoz</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10232,22 +10232,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5b59e02c66831ded570d44f4</t>
+          <t>5b58ada3c1287fe25740991c</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Valjent</t>
+          <t>Benavídez</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10259,12 +10259,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5b786a5d95ea0b2b07e4e66e</t>
+          <t>5b59e02c66831ded570d44f4</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Morlanes</t>
+          <t>Valjent</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10286,22 +10286,22 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5d8650e8333c3d058e0e3a3b</t>
+          <t>5b786a5d95ea0b2b07e4e66e</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Eric García</t>
+          <t>Morlanes</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -10313,22 +10313,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>5fc1512d94ce070e962e3a3c</t>
+          <t>5d8650e8333c3d058e0e3a3b</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Cárdenas</t>
+          <t>Eric García</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>5fc1512d94ce070e962e3a3c</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>612bc20d8f3edc07a4a81def</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Gavi</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>617db824fca9f703e07b2a81</t>
+          <t>612bc20d8f3edc07a4a81def</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Abde Ezzalzouli</t>
+          <t>Gavi</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,22 +10421,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>61dcacebb6d6540425b75dce</t>
+          <t>617db824fca9f703e07b2a81</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Abde Ezzalzouli</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10448,17 +10448,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>61dcacebb6d6540425b75dce</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,17 +10502,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>679e3ac197b9af042545f308</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Sannadi</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10529,17 +10529,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>68251aa7172c6403d639c211</t>
+          <t>679e3ac197b9af042545f308</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Sannadi</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>68251aa7172c6403d639c211</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,22 +10583,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>54026d04e8a4c9292a0001db</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Joan Jordan</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -10610,12 +10610,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>5895c85a1b85076162dab6ac</t>
+          <t>54026d04e8a4c9292a0001db</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Joan Jordan</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5a23f0b68a9f96c2332504ab</t>
+          <t>5895c85a1b85076162dab6ac</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Raba</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,22 +10664,22 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5b375e0567e86d14114d4601</t>
+          <t>5a23f0b68a9f96c2332504ab</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Ionuț Radu</t>
+          <t>Raba</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -10691,22 +10691,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5c0416954c47343bad939db8</t>
+          <t>5b375e0567e86d14114d4601</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Valery Fernández</t>
+          <t>Ionuț Radu</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d4</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5c324dbe189263041db72b84</t>
+          <t>5c0416954c47343bad939db8</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Aihen Muñoz</t>
+          <t>Valery Fernández</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d4</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,12 +10745,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>5c324dbe189263041db72b84</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Aihen Muñoz</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -10772,17 +10772,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5cdf2e37121b5404171c6fad</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Pedro Díaz</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10799,17 +10799,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5cdf2e37121b5404171c6fad</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Pedro Díaz</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -10826,22 +10826,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>5df53e5007000504461ce182</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Manu Sánchez</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -10853,17 +10853,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5f80c8e8a9c2e74fca8282e9</t>
+          <t>5df53e5007000504461ce182</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Ruggeri</t>
+          <t>Manu Sánchez</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10880,22 +10880,22 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>5f80c8e8a9c2e74fca8282e9</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Ruggeri</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -10907,22 +10907,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10934,22 +10934,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10961,17 +10961,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10988,17 +10988,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>62ab326f996d511b380d0d7f</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Marc Aguado</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11015,17 +11015,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>62c3721bc057ca2d85a00512</t>
+          <t>62ab326f996d511b380d0d7f</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Giuliano Simeone</t>
+          <t>Marc Aguado</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11042,17 +11042,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>62e39ff011f4242dbd725314</t>
+          <t>62c3721bc057ca2d85a00512</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Pablo Torre</t>
+          <t>Giuliano Simeone</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>62e39ff011f4242dbd725314</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Pablo Torre</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -11096,17 +11096,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>66b352197fc6ff03fb06fb13</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>D. López</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11123,17 +11123,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>66b352197fc6ff03fb06fb13</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>D. López</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11150,17 +11150,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>67310caf29e197051e04f422</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Ferrán Ruiz</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11177,22 +11177,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5590e843b804493642903daa</t>
+          <t>67310caf29e197051e04f422</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Vesga</t>
+          <t>Ferrán Ruiz</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -11204,22 +11204,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>5590e843b804493642903daa</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Vesga</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -11231,22 +11231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11258,17 +11258,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>599893cd0999c98e0c5fa382</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Berrocal</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11285,22 +11285,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>59c40c341962b7220d0c523e</t>
+          <t>599893cd0999c98e0c5fa382</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Brais Méndez</t>
+          <t>Berrocal</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -17225,17 +17225,17 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>63053ef3f14610075abd00f0</t>
+          <t>65ad994d76a3e353be71263f</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Özkacar</t>
+          <t>Antal Yaakobishvili</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -17252,12 +17252,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a39255e9b413b03b20c1fd5</t>
+          <t>63053ef3f14610075abd00f0</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>De Haas</t>
+          <t>Özkacar</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -17279,12 +17279,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>6a39255e9b413b03b20c1fd5</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t>De Haas</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -17306,17 +17306,17 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>666828c79fdd6e041049a44d</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Javi Serrano</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -17333,22 +17333,22 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6861890daedcdd33075dd01d</t>
+          <t>666828c79fdd6e041049a44d</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Adri Fuentes</t>
+          <t>Javi Serrano</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -17360,22 +17360,22 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>6861890daedcdd33075dd01d</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Adri Fuentes</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -17387,22 +17387,22 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -17414,25 +17414,52 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
+          <t>6685186cd766964157307273</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Vlachodimos</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d5</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>portero</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
           <t>66905806702b9203b99a1357</t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B631" t="inlineStr">
         <is>
           <t>Álex Calatrava</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
+      <c r="C631" t="inlineStr">
         <is>
           <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>centrocampista</t>
-        </is>
-      </c>
-      <c r="E630" t="inlineStr">
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E726"/>
+  <dimension ref="A1:E728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -20025,6 +20025,60 @@
         </is>
       </c>
       <c r="E726" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>5f79bdeb02358a040ca3ed7c</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Miguel Rodríguez</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>52038563b8d07d930b00008a</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>delantero</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>62d7299dfbbaa82d7199978f</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Dubasin</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E728"/>
+  <dimension ref="A1:E729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2996,17 +2996,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>69a37b194f0be803ae3e49e7</t>
+          <t>69b5e2a7c20e6203ae9f9a87</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Julio Díaz</t>
+          <t>Diego Aguado</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>69b5e2a7c20e6203ae9f9a87</t>
+          <t>69b5e2e55436d103b5c952e0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Diego Aguado</t>
+          <t>Daniel Yáñez</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3050,17 +3050,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>69b5e2e55436d103b5c952e0</t>
+          <t>69d183cac5709804148dcb11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Daniel Yáñez</t>
+          <t>Taufik</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3077,12 +3077,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>69d183cac5709804148dcb11</t>
+          <t>69d1843021ab3804095dc5d2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Taufik</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>69d1843021ab3804095dc5d2</t>
+          <t>69daa74298d9eb0426259b22</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Boñar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3131,12 +3131,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>69daa74298d9eb0426259b22</t>
+          <t>69daa6da17877004192cea21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Boñar</t>
+          <t>Belaid</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3158,12 +3158,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>69daa6da17877004192cea21</t>
+          <t>69daa71455f89f041388274a</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Belaid</t>
+          <t>Dani Martínez</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3185,12 +3185,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>69daa71455f89f041388274a</t>
+          <t>6687123799f9bf415ff44157</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dani Martínez</t>
+          <t>Puric</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3212,12 +3212,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6687123799f9bf415ff44157</t>
+          <t>69f632503caa6b0472477da2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Puric</t>
+          <t>Iker Luque</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>69f632503caa6b0472477da2</t>
+          <t>69f632161fe2c90424d568b4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Iker Luque</t>
+          <t>Cubo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3266,17 +3266,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>69f632161fe2c90424d568b4</t>
+          <t>6a06409cd60a6e0400dd5242</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cubo</t>
+          <t>Carrera</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3293,12 +3293,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6a06409cd60a6e0400dd5242</t>
+          <t>6a1221dac0afe2057c5f8e0c</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Carrera</t>
+          <t>Ochieng</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6a1221dac0afe2057c5f8e0c</t>
+          <t>6a122197fd42ba053658e853</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ochieng</t>
+          <t>Beitia</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3347,22 +3347,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6a122197fd42ba053658e853</t>
+          <t>666828c79fdd6e041049a44d</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Beitia</t>
+          <t>Javi Serrano</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3374,22 +3374,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>666828c79fdd6e041049a44d</t>
+          <t>51d70ed7a7178a7654000012</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Javi Serrano</t>
+          <t>Mojica</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3401,22 +3401,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>51d70ed7a7178a7654000012</t>
+          <t>504f647e4d8bec9a67000484</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mojica</t>
+          <t>Stuani</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>504f647e4d8bec9a67000484</t>
+          <t>5313988280c359915f000011</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Stuani</t>
+          <t>Portu</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3455,12 +3455,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5313988280c359915f000011</t>
+          <t>51cab26c01d64ad470000096</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Portu</t>
+          <t>Gazzaniga</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3482,22 +3482,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>51cab26c01d64ad470000096</t>
+          <t>5210908da776cc826b000067</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Gazzaniga</t>
+          <t>Darder</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5210908da776cc826b000067</t>
+          <t>54c509f75d97b9070200178c</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Darder</t>
+          <t>Dani Calvo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3536,22 +3536,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>54c509f75d97b9070200178c</t>
+          <t>57583b4733dbe3424c05e8ee</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dani Calvo</t>
+          <t>Luis Milla</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>6662aa5981b2080416a23781</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3563,22 +3563,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>57583b4733dbe3424c05e8ee</t>
+          <t>521b5f939f2adc783700001e</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Luis Milla</t>
+          <t>David Costas</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>6662aa5981b2080416a23781</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3590,17 +3590,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>521b5f939f2adc783700001e</t>
+          <t>520263c1ed2e70cb370000c1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>David Costas</t>
+          <t>Raíllo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3617,22 +3617,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>520263c1ed2e70cb370000c1</t>
+          <t>504f65684d8bec9a6700072d</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Raíllo</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3644,22 +3644,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>504f65684d8bec9a6700072d</t>
+          <t>62fd1a08e88c090690b05916</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Griezmann</t>
+          <t>Nianzou</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3671,22 +3671,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>62fd1a08e88c090690b05916</t>
+          <t>66cf964ebd0d6403c8b5d5ad</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nianzou</t>
+          <t>Viñas</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520025dc19cbe47807000087</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3698,17 +3698,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>66cf964ebd0d6403c8b5d5ad</t>
+          <t>63f14fbb79f25a5b3f34fedd</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Viñas</t>
+          <t>Álvaro Rodríguez</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>520025dc19cbe47807000087</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,22 +3725,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>63f14fbb79f25a5b3f34fedd</t>
+          <t>56116ea6ffa60f6504776520</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Álvaro Rodríguez</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b1aac753cd14971700002e</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3752,17 +3752,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>56116ea6ffa60f6504776520</t>
+          <t>51b8ab26e401a15f2c00016a</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Carvajal</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>51b1aac753cd14971700002e</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3779,12 +3779,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>51b8ab26e401a15f2c00016a</t>
+          <t>5fbe33c11fd5fa0e8491689f</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Carvajal</t>
+          <t>Mingueza</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3806,22 +3806,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5fbe33c11fd5fa0e8491689f</t>
+          <t>67772046474b6075b3a81ef3</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mingueza</t>
+          <t>Krapyvtsov</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3833,12 +3833,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>67772046474b6075b3a81ef3</t>
+          <t>667ddd02cf0d0c4167933890</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Krapyvtsov</t>
+          <t>Abel Ruiz</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3860,12 +3860,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>667ddd02cf0d0c4167933890</t>
+          <t>668e7743c34e5603e02bf624</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Abel Ruiz</t>
+          <t>Misehouy</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>668e7743c34e5603e02bf624</t>
+          <t>64a0a08ba58cb1732757ad81</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Misehouy</t>
+          <t>Reina</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3914,12 +3914,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>64a0a08ba58cb1732757ad81</t>
+          <t>64a67bacafd9eb7360360e75</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Reina</t>
+          <t>Ilyas Chaira</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3941,17 +3941,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>64a67bacafd9eb7360360e75</t>
+          <t>66b4b8f16e037203f626839f</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ilyas Chaira</t>
+          <t>Izeta</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3968,22 +3968,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>66b4b8f16e037203f626839f</t>
+          <t>66b8fc5699635f03debf8fe8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Izeta</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3995,17 +3995,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>66b8fc5699635f03debf8fe8</t>
+          <t>5ee8f3b114cfa703f145c050</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Parada</t>
+          <t>Francés</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4022,22 +4022,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5ee8f3b114cfa703f145c050</t>
+          <t>57a63dc00aba5e3906c78493</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Francés</t>
+          <t>Escandell</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4049,12 +4049,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>57a63dc00aba5e3906c78493</t>
+          <t>5995a8857c7bb19d3a5d41cd</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Escandell</t>
+          <t>Nacho Vidal</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4076,22 +4076,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5995a8857c7bb19d3a5d41cd</t>
+          <t>5f4fd2e6c5c6f903e7c2522e</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nacho Vidal</t>
+          <t>Van de Beek</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4103,22 +4103,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5f4fd2e6c5c6f903e7c2522e</t>
+          <t>6797e70083b5f103b7013774</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Van de Beek</t>
+          <t>Akor Adams</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4130,17 +4130,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6797e70083b5f103b7013774</t>
+          <t>5f614957d59f315e1fc77bd2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Akor Adams</t>
+          <t>Muriqi</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>5220ce9fc90c7ea70b000047</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5f614957d59f315e1fc77bd2</t>
+          <t>61efea4ec6dfbe0a4fa10b18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Muriqi</t>
+          <t>Eray Cömert</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>5220ce9fc90c7ea70b000047</t>
+          <t>52026c99fdbb14c13700007f</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>61efea4ec6dfbe0a4fa10b18</t>
+          <t>6861c08a7275493329a95613</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Eray Cömert</t>
+          <t>Dominguès</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>52026c99fdbb14c13700007f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4211,22 +4211,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6861c08a7275493329a95613</t>
+          <t>521ddaa240f3fd66010001fa</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dominguès</t>
+          <t>Abdón Prats</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4238,12 +4238,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>521ddaa240f3fd66010001fa</t>
+          <t>5d69113cf91a3f7778179cb7</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Abdón Prats</t>
+          <t>Antonio Sánchez</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4265,17 +4265,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5d69113cf91a3f7778179cb7</t>
+          <t>5f36db010b759303ff680104</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Antonio Sánchez</t>
+          <t xml:space="preserve">Iván Martín </t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4292,12 +4292,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5f36db010b759303ff680104</t>
+          <t>6060aa1a7a64b003da0efc7d</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Martín </t>
+          <t>Arnau Martínez</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4319,22 +4319,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6060aa1a7a64b003da0efc7d</t>
+          <t>61112696dfb903607d1f7e45</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Arnau Martínez</t>
+          <t>Haissem Hassan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4346,17 +4346,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>61112696dfb903607d1f7e45</t>
+          <t>63092ba34c71a52ba37b8165</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Haissem Hassan</t>
+          <t>Joel Roca</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4373,12 +4373,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>63092ba34c71a52ba37b8165</t>
+          <t>63c6945172c559051c25d9fa</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Joel Roca</t>
+          <t>Tsygankov</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4400,12 +4400,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>63c6945172c559051c25d9fa</t>
+          <t>57b94cfee3480bb6049eb14b</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tsygankov</t>
+          <t>Fran Beltrán</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,22 +4427,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>57b94cfee3480bb6049eb14b</t>
+          <t>587413fa39af105c4b075f23</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Fran Beltrán</t>
+          <t>Toni Lato</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4454,12 +4454,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>587413fa39af105c4b075f23</t>
+          <t>5f5a930b58df197b1823bfe7</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Toni Lato</t>
+          <t>Samú Costa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4481,17 +4481,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5f5a930b58df197b1823bfe7</t>
+          <t>64d803c883596124e55c064f</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Samú Costa</t>
+          <t>Unai Gómez</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4508,22 +4508,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>64d803c883596124e55c064f</t>
+          <t>6689c562e0157a03f87fbf0e</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Unai Gómez</t>
+          <t>Morey</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4535,22 +4535,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6689c562e0157a03f87fbf0e</t>
+          <t>67575e411a57f003d0b21843</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Morey</t>
+          <t>Coba da Costa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4562,22 +4562,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>67575e411a57f003d0b21843</t>
+          <t>51c1fdeac7694f5f66000051</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Coba da Costa</t>
+          <t>David López</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4589,17 +4589,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>51c1fdeac7694f5f66000051</t>
+          <t>5b59e02c66831ded570d44f4</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>David López</t>
+          <t>Valjent</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4616,12 +4616,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5b59e02c66831ded570d44f4</t>
+          <t>5b786a5d95ea0b2b07e4e66e</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Valjent</t>
+          <t>Morlanes</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,22 +4643,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5b786a5d95ea0b2b07e4e66e</t>
+          <t>5c0416954c47343bad939db8</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Morlanes</t>
+          <t>Valery Fernández</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d4</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4670,22 +4670,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5c0416954c47343bad939db8</t>
+          <t>62e39ff011f4242dbd725314</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Valery Fernández</t>
+          <t>Pablo Torre</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d4</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4697,12 +4697,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>62e39ff011f4242dbd725314</t>
+          <t>66b352197fc6ff03fb06fb13</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Pablo Torre</t>
+          <t>D. López</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4724,17 +4724,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>66b352197fc6ff03fb06fb13</t>
+          <t>67310caf29e197051e04f422</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>D. López</t>
+          <t>Ferrán Ruiz</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4751,17 +4751,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>67310caf29e197051e04f422</t>
+          <t>6695372399e2e504052cbbae</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ferrán Ruiz</t>
+          <t>Rahim</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4778,22 +4778,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6695372399e2e504052cbbae</t>
+          <t>65b12f7b992bcf53bfe2fc31</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Rahim</t>
+          <t>Moldovan</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,17 +4805,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>65b12f7b992bcf53bfe2fc31</t>
+          <t>66d61f2aed648e0b1ac63f1a</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Moldovan</t>
+          <t>Bergström</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4832,22 +4832,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>66d61f2aed648e0b1ac63f1a</t>
+          <t>5d5570f69bb8253fe4f452d6</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Bergström</t>
+          <t>Ahijado</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4859,12 +4859,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5d5570f69bb8253fe4f452d6</t>
+          <t>66d81870433f040b000aa40c</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ahijado</t>
+          <t>Luka Ilic</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4886,22 +4886,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>66d81870433f040b000aa40c</t>
+          <t>57c73a7a803dc6bd7be02981</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Luka Ilic</t>
+          <t>Pau López</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,22 +4913,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>57c73a7a803dc6bd7be02981</t>
+          <t>56d314416116845b08e61bed</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Pau López</t>
+          <t>Rashford</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51d19d0f78d9b6850500003e</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4940,22 +4940,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>56d314416116845b08e61bed</t>
+          <t>68951eec4e36d6040c695ed8</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Rashford</t>
+          <t>Santamaria</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>51d19d0f78d9b6850500003e</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4967,17 +4967,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>68951eec4e36d6040c695ed8</t>
+          <t>62c5da44fbbaa82d71999775</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Santamaria</t>
+          <t>Witsel</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4994,22 +4994,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>62c5da44fbbaa82d71999775</t>
+          <t>65a2f7b8b94b7303dce5ccac</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Witsel</t>
+          <t>Marco Esteban</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5021,12 +5021,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>65a2f7b8b94b7303dce5ccac</t>
+          <t>689fb8cb06428a0452dc8034</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Marco Esteban</t>
+          <t>Omar Falah</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5048,12 +5048,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>689fb8cb06428a0452dc8034</t>
+          <t>5b6cc28068b47b496279f860</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Omar Falah</t>
+          <t>Dendoncker</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5075,22 +5075,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5b6cc28068b47b496279f860</t>
+          <t>53ac3e6c1933f2de6f0003fc</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dendoncker</t>
+          <t>Álex Moreno</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,22 +5102,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>53ac3e6c1933f2de6f0003fc</t>
+          <t>5f43f5bf0b759303ff680853</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Álex Moreno</t>
+          <t>Ramazani</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>57a1235f445c20291844c133</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5129,17 +5129,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5f43f5bf0b759303ff680853</t>
+          <t>68b0df5c11ed3a059c4912a3</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ramazani</t>
+          <t>Virgili</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>57a1235f445c20291844c133</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5156,22 +5156,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>68b0df5c11ed3a059c4912a3</t>
+          <t>68b37c6461185205e8c364db</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Virgili</t>
+          <t>Ounahi</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5183,12 +5183,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>68b37c6461185205e8c364db</t>
+          <t>68b59fba05c30a03fb36d382</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ounahi</t>
+          <t>Vanat</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5210,12 +5210,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>68b59fba05c30a03fb36d382</t>
+          <t>5c323b46bef16503ec960e1c</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vanat</t>
+          <t>Bryan Gil</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5237,12 +5237,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5c323b46bef16503ec960e1c</t>
+          <t>68f3b8b9dd3614500b418a49</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Bryan Gil</t>
+          <t>Lass</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5264,22 +5264,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>68f3b8b9dd3614500b418a49</t>
+          <t>52024320737b88c937000019</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Lass</t>
+          <t xml:space="preserve"> João Cancelo</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5291,22 +5291,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>52024320737b88c937000019</t>
+          <t>696a39e9af58fa040efb5372</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> João Cancelo</t>
+          <t>Kalumba</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5318,17 +5318,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>696a39e9af58fa040efb5372</t>
+          <t>66a3d3797fc6ff03fb06fadf</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kalumba</t>
+          <t>Echeverri</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51d197b30719708a05000037</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5345,22 +5345,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fadf</t>
+          <t>6977e776fee4e803e0e8bed5</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Echeverri</t>
+          <t>Arango</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>51d197b30719708a05000037</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5372,22 +5372,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6977e776fee4e803e0e8bed5</t>
+          <t>675366baf7be6b107f01b952</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Arango</t>
+          <t>Fer López</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>57a12447445c20291844c142</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5399,17 +5399,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>675366baf7be6b107f01b952</t>
+          <t>68a0ebed3a1cb503e4684dca</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Fer López</t>
+          <t>Jan  Salas</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>57a12447445c20291844c142</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5426,17 +5426,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>68a0ebed3a1cb503e4684dca</t>
+          <t>6a04f3f3f8f6ef041e55261c</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Jan  Salas</t>
+          <t>Damián</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5453,22 +5453,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6a04f3f3f8f6ef041e55261c</t>
+          <t>6a04f502781278043f2eda16</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Damián</t>
+          <t>Orejuela</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5480,22 +5480,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6a04f502781278043f2eda16</t>
+          <t>61844713165d9f09c3eecd07</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Orejuela</t>
+          <t>Artero</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5507,17 +5507,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>61844713165d9f09c3eecd07</t>
+          <t>61c3b14eb4f96c073bf94ce7</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Artero</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5534,17 +5534,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>61c3b14eb4f96c073bf94ce7</t>
+          <t>674b7a94c9efc910567f19b6</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5561,22 +5561,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>674b7a94c9efc910567f19b6</t>
+          <t>66cfa272b46ff704160ad00e</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Adrián Pica</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5588,22 +5588,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>66cfa272b46ff704160ad00e</t>
+          <t>686feb558bef76044eadf791</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Adrián Pica</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5615,22 +5615,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>686feb558bef76044eadf791</t>
+          <t>6683c6e90ab8ba417f3276b6</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Unai Ropero</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5642,17 +5642,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>6683c6e90ab8ba417f3276b6</t>
+          <t>67597e6b317cba0418bce297</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Unai Ropero</t>
+          <t>Dani Luna</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>67597e6b317cba0418bce297</t>
+          <t>66d39b3d58f2de32117efa18</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Dani Luna</t>
+          <t>Domenech</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5696,17 +5696,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>66d39b3d58f2de32117efa18</t>
+          <t>57b94a3c7ce1feed040b24e3</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Domenech</t>
+          <t>Jacobo González</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5723,12 +5723,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>57b94a3c7ce1feed040b24e3</t>
+          <t>64b1c502c35fcb3cfd3ed505</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Jacobo González</t>
+          <t>Youness</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>64b1c502c35fcb3cfd3ed505</t>
+          <t>6865adefd4d22b330615f7ca</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Youness</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5777,12 +5777,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>6865adefd4d22b330615f7ca</t>
+          <t>60e6e2841a405a604ca8c2d7</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Luengo</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5804,12 +5804,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>60e6e2841a405a604ca8c2d7</t>
+          <t>669274f3ce303803d6f77330</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Luengo</t>
+          <t>Paraschiv</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>669274f3ce303803d6f77330</t>
+          <t>6584aa689b9f5d700573fd05</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Paraschiv</t>
+          <t>Cardero</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5858,17 +5858,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6584aa689b9f5d700573fd05</t>
+          <t>697be226df6332040670c6c1</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cardero</t>
+          <t>Izan González</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5885,12 +5885,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>697be226df6332040670c6c1</t>
+          <t>6a35c168152d0603c64c029a</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Izan González</t>
+          <t>Pyshchur</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5912,12 +5912,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>6a35c168152d0603c64c029a</t>
+          <t>68a9e8aab479f05404a946c8</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Pyshchur</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5939,12 +5939,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>68a9e8aab479f05404a946c8</t>
+          <t>6713fdc9a1b917176a03238a</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Min-su Kim</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5966,12 +5966,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6713fdc9a1b917176a03238a</t>
+          <t>66c9b0acf119260402e26288</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Min-su Kim</t>
+          <t>Asprilla</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5993,12 +5993,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>66c9b0acf119260402e26288</t>
+          <t>65f5fc5000ffc34f05f1cb1f</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Asprilla</t>
+          <t>Jastin</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6020,12 +6020,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>65f5fc5000ffc34f05f1cb1f</t>
+          <t>65ad994d76a3e353be71263f</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Jastin</t>
+          <t>Antal Yaakobishvili</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6047,17 +6047,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>65ad994d76a3e353be71263f</t>
+          <t>63053ef3f14610075abd00f0</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Antal Yaakobishvili</t>
+          <t>Özkacar</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6074,22 +6074,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>63053ef3f14610075abd00f0</t>
+          <t>6861890daedcdd33075dd01d</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Özkacar</t>
+          <t>Adri Fuentes</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6101,17 +6101,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6861890daedcdd33075dd01d</t>
+          <t>6795426c91d9bd03c793c426</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Adri Fuentes</t>
+          <t>Diego Gómez</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6128,22 +6128,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>6795426c91d9bd03c793c426</t>
+          <t>63bb149eba53bb03cdfc2e9f</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Diego Gómez</t>
+          <t>Cabanzón</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6155,17 +6155,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>63bb149eba53bb03cdfc2e9f</t>
+          <t>64fb90eebc6e0003e0366f4f</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Cabanzón</t>
+          <t>Roca</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6182,22 +6182,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>64fb90eebc6e0003e0366f4f</t>
+          <t>521b69bf359d42743700007f</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Roca</t>
+          <t>Carlos Fernández</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6209,22 +6209,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>521b69bf359d42743700007f</t>
+          <t>6305da4d46d783071421441c</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Carlos Fernández</t>
+          <t>Arnau Tenas</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6236,22 +6236,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6305da4d46d783071421441c</t>
+          <t>5cfc2be98721525ead8d94b1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Arnau Tenas</t>
+          <t>Gragera</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6263,22 +6263,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5cfc2be98721525ead8d94b1</t>
+          <t>64be9241b6533c3d2112572f</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Gragera</t>
+          <t>Petxarroman</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -16793,22 +16793,22 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>64be9241b6533c3d2112572f</t>
+          <t>5f0cbbb3075d9b03e1b24de9</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Petxarroman</t>
+          <t>Baena</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -16820,22 +16820,22 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>5f0cbbb3075d9b03e1b24de9</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Baena</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -16847,22 +16847,22 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -16874,22 +16874,22 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>6551104e5a61972b4cdf05d3</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Tomás Mendes</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -16901,22 +16901,22 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6551104e5a61972b4cdf05d3</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Tomás Mendes</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -16928,22 +16928,22 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>65f7126c17c8f74f39434408</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Damián Rodríguez</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -16955,22 +16955,22 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>65f7126c17c8f74f39434408</t>
+          <t>60e72704dfb903607d1f7d87</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Damián Rodríguez</t>
+          <t>Dituro</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -16982,17 +16982,17 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>60e72704dfb903607d1f7d87</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Dituro</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -17009,22 +17009,22 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -17036,22 +17036,22 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>66c25f14b5741f1a24b155a4</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Barzic</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -17063,22 +17063,22 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>66c25f14b5741f1a24b155a4</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Barzic</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -17090,12 +17090,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>6757ff71d2717703ca746142</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Cabanes</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -17117,22 +17117,22 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6757ff71d2717703ca746142</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Cabanes</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -17144,22 +17144,22 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>6866a4e8ca97b13338e6cd0a</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Mikel Rodríguez</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -17171,17 +17171,17 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6866a4e8ca97b13338e6cd0a</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Mikel Rodríguez</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -17198,22 +17198,22 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>68b22bf68eb5b005b415a5c6</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Oluwaseyi</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -17225,22 +17225,22 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>68b22bf68eb5b005b415a5c6</t>
+          <t>614743ace216464c91a29186</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Oluwaseyi</t>
+          <t>Owono</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -17252,22 +17252,22 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>614743ace216464c91a29186</t>
+          <t>68b5a03548ead604163e6894</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Owono</t>
+          <t>Eto'o</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -17279,22 +17279,22 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>68b5a03548ead604163e6894</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Eto'o</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -17306,17 +17306,17 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6a4f529258624805c6d283eb</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Moscardo</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -17333,22 +17333,22 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4f529258624805c6d283eb</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Moscardo</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -17360,22 +17360,22 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>62b3135fa81ab52db02ea690</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Forés</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -17387,22 +17387,22 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>62b3135fa81ab52db02ea690</t>
+          <t>62c8810bb1a2d22da1beec0b</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Forés</t>
+          <t>Marcão</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -17414,17 +17414,17 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>62c8810bb1a2d22da1beec0b</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Marcão</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -17441,22 +17441,22 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>630e1e745328c70716999d1d</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -17468,22 +17468,22 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>630e1e745328c70716999d1d</t>
+          <t>64f4d4b99318fc03ee16e82d</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Amatucci</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -17495,17 +17495,17 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>64f4d4b99318fc03ee16e82d</t>
+          <t>6593da11751ea070478c47cc</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Amatucci</t>
+          <t>J. Cardoso</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -17522,22 +17522,22 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6593da11751ea070478c47cc</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>J. Cardoso</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -17549,22 +17549,22 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>66802b2c654982413588730e</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Eric Puerto</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -17576,22 +17576,22 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>66802b2c654982413588730e</t>
+          <t>6689c4a399e2e504052caf27</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Eric Puerto</t>
+          <t>Rosier</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -17603,17 +17603,17 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6689c4a399e2e504052caf27</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Rosier</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -17630,22 +17630,22 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>66c0c8fb8107211a38038907</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t>Ochoa</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -17657,17 +17657,17 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>66c0c8fb8107211a38038907</t>
+          <t>66ccfe37683d1203dc8a58b3</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Ochoa</t>
+          <t>Alfon</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -17684,22 +17684,22 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>66ccfe37683d1203dc8a58b3</t>
+          <t>676889368e803803f4d3ae2f</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Alfon</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -17711,22 +17711,22 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>676889368e803803f4d3ae2f</t>
+          <t>67804e6ab11a5e759942b02f</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Kervin Arriaga</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -17738,22 +17738,22 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>67804e6ab11a5e759942b02f</t>
+          <t>6866a463588465330dd378d1</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Kervin Arriaga</t>
+          <t>Rupérez</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -17765,22 +17765,22 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6866a463588465330dd378d1</t>
+          <t>6876c12606428a0452dc7fa6</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Rupérez</t>
+          <t>Áron Yaakobishvili</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -17792,22 +17792,22 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6876c12606428a0452dc7fa6</t>
+          <t>68c5f5d55bd165052e271611</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Áron Yaakobishvili</t>
+          <t>Ángel Pérez</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -17819,22 +17819,22 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>68c5f5d55bd165052e271611</t>
+          <t>69810c427602e303cbed6a3e</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Ángel Pérez</t>
+          <t>Obed Vargas</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -17846,17 +17846,17 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>69810c427602e303cbed6a3e</t>
+          <t>6a35ba801636ff03e132961e</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Obed Vargas</t>
+          <t>Gijselhart</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -17873,22 +17873,22 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a35ba801636ff03e132961e</t>
+          <t>5a3578e0feceda7e2716a6c7</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Gijselhart</t>
+          <t xml:space="preserve">Ferrán Torres </t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -17900,12 +17900,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>5a3578e0feceda7e2716a6c7</t>
+          <t>5d9a575c370ecd5c7486de5c</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrán Torres </t>
+          <t>Ronald Araújo</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -17927,17 +17927,17 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>5d9a575c370ecd5c7486de5c</t>
+          <t>5f32e17633a68903ecffbd1f</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Ronald Araújo</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -17954,17 +17954,17 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>5f32e17633a68903ecffbd1f</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -17981,17 +17981,17 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>5f6fae0738429649dbf263d6</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Boyomo</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -18008,22 +18008,22 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>5f6fae0738429649dbf263d6</t>
+          <t>5f70efc9b69ba04a25453f2c</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Boyomo</t>
+          <t>Jofre</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -18035,22 +18035,22 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>5f70efc9b69ba04a25453f2c</t>
+          <t>5f80c8e8a9c2e74fca8282e9</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Ruggeri</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -18062,22 +18062,22 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>5f80c8e8a9c2e74fca8282e9</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Ruggeri</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -18089,17 +18089,17 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -18116,22 +18116,22 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -18143,22 +18143,22 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>61228f14bee4ec08574d99bf</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Haitam</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -18170,22 +18170,22 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>61228f14bee4ec08574d99bf</t>
+          <t>614cc15d3916210732959cc3</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Haitam</t>
+          <t>Robert Navarro</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -18197,22 +18197,22 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>614cc15d3916210732959cc3</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Robert Navarro</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -18224,17 +18224,17 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>62ab326f996d511b380d0d7a</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Álex Pastor</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -18251,22 +18251,22 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>62ab326f996d511b380d0d7a</t>
+          <t>62ab326f996d511b380d0d7f</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Álex Pastor</t>
+          <t>Marc Aguado</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -18278,17 +18278,17 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>62ab326f996d511b380d0d7f</t>
+          <t>63fd2d48e13c195af1f7112f</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Marc Aguado</t>
+          <t>Terrats</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -18305,22 +18305,22 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>63fd2d48e13c195af1f7112f</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Terrats</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -18332,22 +18332,22 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>657cccb79a154503e6fa2fa8</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Rodri Mendoza</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -18359,17 +18359,17 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>657cccb79a154503e6fa2fa8</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Rodri Mendoza</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -18386,22 +18386,22 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -18413,22 +18413,22 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>6643e149974fb0361c6a6e9b</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Mario Martín</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -18440,22 +18440,22 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6643e149974fb0361c6a6e9b</t>
+          <t>668020900ab8ba417f327199</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Mario Martín</t>
+          <t>Vertrouwd</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -18467,22 +18467,22 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>668020900ab8ba417f327199</t>
+          <t>66ade7b9702b9203b99a16eb</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Vertrouwd</t>
+          <t>Luka Sucic</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -18494,17 +18494,17 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>66ade7b9702b9203b99a16eb</t>
+          <t>66b69fb39e452303b3fc0b77</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Luka Sucic</t>
+          <t>Dani Olmo</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -18521,17 +18521,17 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>66b69fb39e452303b3fc0b77</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Dani Olmo</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -18548,22 +18548,22 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -18575,22 +18575,22 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>679542c43f683203b32f39d0</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -18602,22 +18602,22 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>679542c43f683203b32f39d0</t>
+          <t>68a234d9a9a91a0415a3788b</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Rego</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -18629,22 +18629,22 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>68a234d9a9a91a0415a3788b</t>
+          <t>68adbb77d1d08d1c1f1228ce</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Rego</t>
+          <t>Hinojo</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -18656,17 +18656,17 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>68adbb77d1d08d1c1f1228ce</t>
+          <t>697e90b3ff715b03c5df8278</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Hinojo</t>
+          <t>Koski</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -18683,17 +18683,17 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>697e90b3ff715b03c5df8278</t>
+          <t>521465c2dbf8b74f020000b8</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Koski</t>
+          <t>Yuri</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -18710,22 +18710,22 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>521465c2dbf8b74f020000b8</t>
+          <t>578a39f79572c04c06eb3daf</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Yuri</t>
+          <t>Comesaña</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -18737,22 +18737,22 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>578a39f79572c04c06eb3daf</t>
+          <t>57bb7cea45e6bed0520a420a</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Comesaña</t>
+          <t>Rafa Mir</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -18764,22 +18764,22 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>57bb7cea45e6bed0520a420a</t>
+          <t>5b34a882447188471d9677fc</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Rafa Mir</t>
+          <t>Óscar Valentín</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -18791,12 +18791,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>5b34a882447188471d9677fc</t>
+          <t>5cdf2e37121b5404171c6fad</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Óscar Valentín</t>
+          <t>Pedro Díaz</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -18818,22 +18818,22 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>5cdf2e37121b5404171c6fad</t>
+          <t>5d51a593fbc39d3fa25f7eb0</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Pedro Díaz</t>
+          <t>Sergio Gómez</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -18845,17 +18845,17 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>5d51a593fbc39d3fa25f7eb0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Sergio Gómez</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -18872,22 +18872,22 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>5f7c91e784180b4fc44cd0ee</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Raphinha</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -18899,22 +18899,22 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>5f7c91e784180b4fc44cd0ee</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Raphinha</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -18926,17 +18926,17 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>61c0ff53122e933e3d15a643</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Iranzo</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -18953,22 +18953,22 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>61c0ff53122e933e3d15a643</t>
+          <t>61da0a69b6d6540425b749e4</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Iranzo</t>
+          <t>Bouldini</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -18980,22 +18980,22 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>61da0a69b6d6540425b749e4</t>
+          <t>62f12359f1b09a7dd27ba96c</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Bouldini</t>
+          <t>Juanlu</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -19007,17 +19007,17 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>62f12359f1b09a7dd27ba96c</t>
+          <t>665368343bd1d1040fffb355</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Juanlu</t>
+          <t>Yoel Lago</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -19034,22 +19034,22 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>665368343bd1d1040fffb355</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Yoel Lago</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -19061,22 +19061,22 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -19088,22 +19088,22 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>66802dd799f9bf415ff4350c</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Diego Villares</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -19115,17 +19115,17 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>66802dd799f9bf415ff4350c</t>
+          <t>66bb83844942001a16eafbb8</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Diego Villares</t>
+          <t>Javi Hernández</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -19142,22 +19142,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>66bb83844942001a16eafbb8</t>
+          <t>66bfad063bdc581a0f65ead1</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Javi Hernández</t>
+          <t>Javi Rodríguez</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -19169,22 +19169,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>66bfad063bdc581a0f65ead1</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Javi Rodríguez</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -19196,22 +19196,22 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -19223,22 +19223,22 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>680529fb802b9e0450bb226a</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>Eyong</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -19250,17 +19250,17 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>680529fb802b9e0450bb226a</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Eyong</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -19277,22 +19277,22 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>68c5f54d83815b05817ba3bd</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Ángel Recio</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -19304,22 +19304,22 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>68c5f54d83815b05817ba3bd</t>
+          <t>6977e9c440eaa603f8aa3e87</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Ángel Recio</t>
+          <t>Cepeda</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -19331,22 +19331,22 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6977e9c440eaa603f8aa3e87</t>
+          <t>51cb698301d64ad4700000bc</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Cepeda</t>
+          <t>Szczesny</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -19358,22 +19358,22 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000bc</t>
+          <t>596fc4490ef6710375cfbc85</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Szczesny</t>
+          <t>Javi Muñoz</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -19385,17 +19385,17 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>596fc4490ef6710375cfbc85</t>
+          <t>5a639998e2a0fd3424128d06</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Javi Muñoz</t>
+          <t>Brahim Díaz</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -19412,12 +19412,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>5a639998e2a0fd3424128d06</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Brahim Díaz</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -19439,22 +19439,22 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -19466,12 +19466,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>607325f27b19b30c4fb34081</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Urko González</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -19493,22 +19493,22 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>607325f27b19b30c4fb34081</t>
+          <t>610abc4f328e98602847897f</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Urko González</t>
+          <t>Ratiu</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -19520,22 +19520,22 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>610abc4f328e98602847897f</t>
+          <t>612bc20d8f3edc07a4a81def</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Ratiu</t>
+          <t>Gavi</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -19547,17 +19547,17 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>612bc20d8f3edc07a4a81def</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Gavi</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -19574,17 +19574,17 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>62c3721bc057ca2d85a00512</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Giuliano Simeone</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -19601,22 +19601,22 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>62c3721bc057ca2d85a00512</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Giuliano Simeone</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -19628,22 +19628,22 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -19655,22 +19655,22 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>644d90d4479a44042784eb9f</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -19682,22 +19682,22 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>644d90d4479a44042784eb9f</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
@@ -19709,22 +19709,22 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -19736,12 +19736,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>66a3d3797fc6ff03fb06fae3</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Mastantuono</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -19763,17 +19763,17 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fae3</t>
+          <t>66c72a0476de1f03e6d2b55a</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Mastantuono</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -19790,17 +19790,17 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>66c72a0476de1f03e6d2b55a</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -19817,17 +19817,17 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>682920fc77ba5003ca4869ce</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Deossa</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -19844,17 +19844,17 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>682920fc77ba5003ca4869ce</t>
+          <t>6866a56fca97b13338e6cd0b</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Deossa</t>
+          <t>Goti</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -19871,22 +19871,22 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6866a56fca97b13338e6cd0b</t>
+          <t>687aa8cb00ed89046c1f7e6e</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Goti</t>
+          <t>Gonzalo Petit</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -19898,22 +19898,22 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>687aa8cb00ed89046c1f7e6e</t>
+          <t>68b5ed22026ac303d72e012e</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Gonzalo Petit</t>
+          <t>Puerta</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -19925,22 +19925,22 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>68b5ed22026ac303d72e012e</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Puerta</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -19952,22 +19952,22 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>69a5ddd7cd2bdb03fcc07f8a</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Thiago Pitarch</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -19979,17 +19979,17 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>69a5ddd7cd2bdb03fcc07f8a</t>
+          <t>5c3a22fd2eb0f60409307e95</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Thiago Pitarch</t>
+          <t>Kang-in Lee</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -20006,22 +20006,22 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>5c3a22fd2eb0f60409307e95</t>
+          <t>5f79bdeb02358a040ca3ed7c</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Kang-in Lee</t>
+          <t>Miguel Rodríguez</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -20033,22 +20033,22 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>5f79bdeb02358a040ca3ed7c</t>
+          <t>62d7299dfbbaa82d7199978f</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Miguel Rodríguez</t>
+          <t>Dubasin</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -20060,25 +20060,52 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>62d7299dfbbaa82d7199978f</t>
+          <t>69a37b194f0be803ae3e49e7</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Dubasin</t>
+          <t>Julio Díaz</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>5e2c95e681b4f252c1de887c</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Fer Niño</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>51b889b1e401a15f2c0000f0</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>delantero</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E732"/>
+  <dimension ref="A1:E733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6452,22 +6452,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>69ab5b4653966303fb66b781</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6479,17 +6479,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>68251aa7172c6403d639c211</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6506,22 +6506,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>62c03520b2a1132d77c957bd</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6533,17 +6533,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5591624ea1736b3a42844561</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Villalibre</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6560,22 +6560,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>52017ff1cf55e01b3400002e</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6587,22 +6587,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -6614,22 +6614,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>5591624ea1736b3a42844561</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Villalibre</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -6641,22 +6641,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5202890bd7a595bd3700007b</t>
+          <t>52017ff1cf55e01b3400002e</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán </t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6668,22 +6668,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6695,12 +6695,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6722,22 +6722,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>5202890bd7a595bd3700007b</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t xml:space="preserve">Germán </t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6749,22 +6749,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6776,22 +6776,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6803,17 +6803,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005a6</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ximo Navarro</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6830,17 +6830,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6857,12 +6857,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6884,22 +6884,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>51b9d964e401a15f2c000174</t>
+          <t>504f65024d8bec9a670005a6</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Ter Stegen</t>
+          <t>Ximo Navarro</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6911,22 +6911,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6938,17 +6938,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6965,22 +6965,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>51b9d964e401a15f2c000174</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Ter Stegen</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6992,22 +6992,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -7019,22 +7019,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -7046,12 +7046,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7073,22 +7073,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -7100,12 +7100,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -7127,22 +7127,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>520d0d314386b4816b000029</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Alfonso Herrero</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -7154,17 +7154,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7181,17 +7181,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7208,22 +7208,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>520d0d314386b4816b000029</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Alfonso Herrero</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -7235,22 +7235,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -7262,22 +7262,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -7289,22 +7289,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -7316,17 +7316,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7343,12 +7343,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -7370,22 +7370,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7397,22 +7397,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>51d71d02a7178a7654000017</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Aubameyang</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7424,22 +7424,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -7451,22 +7451,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -7478,22 +7478,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>51d71d02a7178a7654000017</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Aubameyang</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -7505,22 +7505,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7532,17 +7532,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7559,22 +7559,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7586,22 +7586,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7613,22 +7613,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -7640,17 +7640,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7667,17 +7667,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7694,17 +7694,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>52167e295d086a6726000238</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Jurado</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7721,17 +7721,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7748,22 +7748,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7775,22 +7775,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>52167e295d086a6726000238</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Jurado</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7802,17 +7802,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7829,22 +7829,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -7856,22 +7856,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -7883,22 +7883,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7910,22 +7910,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7937,17 +7937,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7964,17 +7964,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7991,22 +7991,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>577743d027ae4bd9135ae3d8</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nahuel Molina</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -8018,22 +8018,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8045,22 +8045,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8072,22 +8072,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>577743d027ae4bd9135ae3d8</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Nahuel Molina</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,17 +8126,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>53a01453b33bed3b010002b1</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Denis Suárez</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8153,22 +8153,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8180,17 +8180,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>53a01453b33bed3b010002b1</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Denis Suárez</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8234,17 +8234,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,17 +8315,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>57b5c2d87e2ec2df1922966f</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Elgezabal</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8369,22 +8369,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>57b5c2d87e2ec2df1922966f</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Elgezabal</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>57e816de3c438763749abb90</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Álvaro Fernández</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,22 +8504,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -8531,17 +8531,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8558,22 +8558,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>57e816de3c438763749abb90</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Álvaro Fernández</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8612,22 +8612,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8639,17 +8639,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8666,22 +8666,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,22 +8693,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8720,17 +8720,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,22 +8774,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8801,17 +8801,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8828,12 +8828,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>61c0ff53122e933e3d15a643</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Iranzo</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8855,17 +8855,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>61c0ff53122e933e3d15a643</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Iranzo</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,22 +8936,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -8963,17 +8963,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8990,17 +8990,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9017,17 +9017,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>64c039a313c6a63ccc321929</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Luismi Cruz</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9044,22 +9044,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -9071,17 +9071,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9098,17 +9098,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>64c039a313c6a63ccc321929</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Luismi Cruz</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9125,22 +9125,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>66802f240c14414136e408c3</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Mella</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,22 +9206,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>66802f240c14414136e408c3</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Mella</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,12 +9260,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,17 +9287,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9314,22 +9314,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -9341,22 +9341,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,17 +9395,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,22 +9422,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9449,22 +9449,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>69ab5b4653966303fb66b781</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -9476,22 +9476,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,17 +9530,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>6a4d1bfcae633549bd0f0744</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9557,17 +9557,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>65b23452ad8bc354111e6659</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Adama Boiro</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>6a4d1bfcae633549bd0f0744</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,17 +9611,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>668011e40ab8ba417f327193</t>
+          <t>65b23452ad8bc354111e6659</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Dani Sánchez</t>
+          <t>Adama Boiro</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,17 +9665,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>66cfa0f08be9a7041ad309f9</t>
+          <t>668011e40ab8ba417f327193</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Jon Martín</t>
+          <t>Dani Sánchez</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9692,17 +9692,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9719,22 +9719,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>66cfa0f08be9a7041ad309f9</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Jon Martín</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -9746,17 +9746,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>69ab5b84a3657e03f770ab51</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Manuel Ángel</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9773,22 +9773,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,22 +9800,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>69ab5b84a3657e03f770ab51</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Manuel Ángel</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,12 +9827,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>6a621c32c6d839058e965748</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,22 +9854,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -9881,22 +9881,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>6a621c32c6d839058e965748</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -9908,17 +9908,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,22 +9989,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10016,17 +10016,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,17 +10070,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10097,17 +10097,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>5f78e79033215d0412a634a7</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Larrubia</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10124,22 +10124,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>602826e66e7e166c3abf1ec0</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Miguel Rubio</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10151,17 +10151,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5f78e79033215d0412a634a7</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Larrubia</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10178,17 +10178,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>602826e66e7e166c3abf1ec0</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Miguel Rubio</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10205,12 +10205,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,22 +10232,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10259,22 +10259,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>614743ace216464c91a29186</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Owono</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10286,17 +10286,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10313,22 +10313,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>614743ace216464c91a29186</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Owono</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,17 +10394,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>62e0f3d5fbbaa82d719997a2</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Quagliata</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10421,17 +10421,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10448,22 +10448,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62e0f3d5fbbaa82d719997a2</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>Quagliata</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>630f3695b0b3fe076438ce57</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Yvan Neyou</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,17 +10502,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>630d3c68b640225ddc5861c9</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Fran Pérez</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10529,17 +10529,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>630f3695b0b3fe076438ce57</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Yvan Neyou</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>64d2b9156167273d0ccc5c4f</t>
+          <t>630d3c68b640225ddc5861c9</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Facundo González</t>
+          <t>Fran Pérez</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,17 +10583,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10610,17 +10610,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>65871ef403b798703d8c7dd6</t>
+          <t>64d2b9156167273d0ccc5c4f</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Facundo González</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,12 +10664,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65871ef403b798703d8c7dd6</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -10691,17 +10691,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,17 +10745,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10772,22 +10772,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,17 +10826,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10853,22 +10853,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -10880,22 +10880,22 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -10907,22 +10907,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>66ba79564942001a16eafbb7</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Dani Martín</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10934,22 +10934,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>66802cdbfd03ab41756b1dc9</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Dani Barcia</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10961,22 +10961,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>66ba79564942001a16eafbb7</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Dani Martín</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -10988,22 +10988,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66802cdbfd03ab41756b1dc9</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Dani Barcia</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -11015,22 +11015,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -11042,12 +11042,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -11096,17 +11096,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6865a9767775a433449e9c85</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Noubi</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11123,22 +11123,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -11150,17 +11150,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6866a463588465330dd378d1</t>
+          <t>6865a9767775a433449e9c85</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Rupérez</t>
+          <t>Noubi</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11177,22 +11177,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -11204,17 +11204,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>6866a463588465330dd378d1</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Rupérez</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11231,22 +11231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>679d3d34fdee6403d89449fe</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Eddahchouri</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11258,17 +11258,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>68ebfeadaff4d55004ae1572</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Rafita</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11285,22 +11285,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>679d3d34fdee6403d89449fe</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Eddahchouri</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -11312,17 +11312,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6935bcd342796103f7ed41db</t>
+          <t>68ebfeadaff4d55004ae1572</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Rafita</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>695a877f1b6b9103c47320ef</t>
+          <t>6935bcd342796103f7ed41db</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,17 +11420,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4d1b4e2ae0d649eac3a152</t>
+          <t>695a877f1b6b9103c47320ef</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Bernal</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -11447,22 +11447,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -11474,17 +11474,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>54026d04e8a4c9292a0001db</t>
+          <t>6a4d1b4e2ae0d649eac3a152</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Joan Jordan</t>
+          <t>Bernal</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11501,17 +11501,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11528,12 +11528,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>5895c85a1b85076162dab6ac</t>
+          <t>54026d04e8a4c9292a0001db</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Joan Jordan</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11555,17 +11555,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5b6e2823a2736a321a4d1003</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11582,22 +11582,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>5895c85a1b85076162dab6ac</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -11609,22 +11609,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>5989a4391f9fb9af4ba1b806</t>
+          <t>5b6e2823a2736a321a4d1003</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Calero</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -11636,22 +11636,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5e499be66e12ab0422cc40fb</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unai Vencedor</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -11663,17 +11663,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5989a4391f9fb9af4ba1b806</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Calero</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -11690,22 +11690,22 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5e499be66e12ab0422cc40fb</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Unai Vencedor</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>5a23f0b68a9f96c2332504ab</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Raba</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -11744,17 +11744,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -11771,12 +11771,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>5a23f0b68a9f96c2332504ab</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Raba</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11798,22 +11798,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -11825,22 +11825,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -11852,22 +11852,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11879,22 +11879,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -11906,22 +11906,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,22 +11933,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5f3d059a3e2aea03b6fe0456</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Pep Chavarría</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -11960,22 +11960,22 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -11987,22 +11987,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>5f3d059a3e2aea03b6fe0456</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Pep Chavarría</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -12014,22 +12014,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>62b30b7011f4242dbd7252b0</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Mantilla</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -12041,22 +12041,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -12068,17 +12068,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>62f826f93355b0168987308d</t>
+          <t>62b30b7011f4242dbd7252b0</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Mantilla</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12095,17 +12095,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>62f826f93355b0168987308d</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12149,22 +12149,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12176,22 +12176,22 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12203,17 +12203,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -12230,17 +12230,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6461127d49e91a03fb017cda</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Carlos Martín</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12284,22 +12284,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12311,17 +12311,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>6461127d49e91a03fb017cda</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Carlos Martín</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -12338,22 +12338,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>62ae4ce2c057ca2d85a004e2</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Hjulmand</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -12365,22 +12365,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>655be3da0cc5192b1a75785c</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Xavi Grande</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>630e1e745328c70716999d1d</t>
+          <t>62ae4ce2c057ca2d85a004e2</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Hjulmand</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -12419,17 +12419,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>631ca92becf9a206fe07abea</t>
+          <t>655be3da0cc5192b1a75785c</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Kike Salas</t>
+          <t>Xavi Grande</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12446,22 +12446,22 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>63a8cd87bfb65a271f11db10</t>
+          <t>630e1e745328c70716999d1d</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Carlos Álvarez</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -12473,17 +12473,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>631ca92becf9a206fe07abea</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Kike Salas</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12500,22 +12500,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>63a8cd87bfb65a271f11db10</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Carlos Álvarez</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -12527,17 +12527,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12554,17 +12554,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -12581,22 +12581,22 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -12608,22 +12608,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>66802e7e654982413588730f</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Rubén López</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -12635,17 +12635,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>668015b50ab8ba417f327194</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Roberto Fernández</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -12662,17 +12662,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>66905806702b9203b99a1357</t>
+          <t>66802e7e654982413588730f</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Álex Calatrava</t>
+          <t>Rubén López</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -12689,22 +12689,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>66802dd799f9bf415ff4350c</t>
+          <t>668015b50ab8ba417f327194</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Diego Villares</t>
+          <t>Roberto Fernández</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -12716,22 +12716,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>66802fd539012a413c5d995f</t>
+          <t>66905806702b9203b99a1357</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Yeremay Hernández</t>
+          <t>Álex Calatrava</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -12743,17 +12743,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>66f98191043342085bbcc7ce</t>
+          <t>66802dd799f9bf415ff4350c</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Peio Canales</t>
+          <t>Diego Villares</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12770,22 +12770,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>66802fd539012a413c5d995f</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t>Yeremay Hernández</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -12797,22 +12797,22 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6865791adf31913331fecaf7</t>
+          <t>66f98191043342085bbcc7ce</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Hartman</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -12824,22 +12824,22 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>66c72a0476de1f03e6d2b55a</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -12851,17 +12851,17 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>688318293777f6041274556c</t>
+          <t>6865791adf31913331fecaf7</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Hancko</t>
+          <t>Hartman</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -12878,22 +12878,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6861bef57775a433449e9581</t>
+          <t>66c72a0476de1f03e6d2b55a</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Jutglà</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -12905,17 +12905,17 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>68a21b2501a094041b51ad5b</t>
+          <t>688318293777f6041274556c</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Bekhoucha</t>
+          <t>Hancko</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -12932,17 +12932,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>6861bef57775a433449e9581</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Jutglà</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -12959,22 +12959,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>68a234d9a9a91a0415a3788b</t>
+          <t>68a21b2501a094041b51ad5b</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Rego</t>
+          <t>Bekhoucha</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -12986,22 +12986,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>68780dec5c7211044690a3a9</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Enríquez</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13013,22 +13013,22 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>68a9fc4cd20bb9540efa8666</t>
+          <t>68a234d9a9a91a0415a3788b</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Manu Fernández</t>
+          <t>Rego</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -13040,22 +13040,22 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>68a0bcdf773d7404220761b2</t>
+          <t>68780dec5c7211044690a3a9</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sergio M. </t>
+          <t>Enríquez</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -13067,22 +13067,22 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>68b5a03548ead604163e6894</t>
+          <t>68a9fc4cd20bb9540efa8666</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Eto'o</t>
+          <t>Manu Fernández</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -13094,22 +13094,22 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>68adbb77d1d08d1c1f1228ce</t>
+          <t>68a0bcdf773d7404220761b2</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Hinojo</t>
+          <t xml:space="preserve">Sergio M. </t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -13121,22 +13121,22 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>68b5ed22026ac303d72e012e</t>
+          <t>68b5a03548ead604163e6894</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Puerta</t>
+          <t>Eto'o</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -13148,22 +13148,22 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>68b486b8882e4a05b2d43111</t>
+          <t>68adbb77d1d08d1c1f1228ce</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Román</t>
+          <t>Hinojo</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -13175,12 +13175,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6960f922cd59040409e50fd9</t>
+          <t>68b5ed22026ac303d72e012e</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Guliashvili</t>
+          <t>Puerta</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -13202,22 +13202,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6946c6f73a8ebd03f25fc9a3</t>
+          <t>68b486b8882e4a05b2d43111</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Nsongo</t>
+          <t>Román</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -13229,12 +13229,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>696e8199368a5803c07f3bc1</t>
+          <t>6960f922cd59040409e50fd9</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Eriksson</t>
+          <t>Guliashvili</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -13256,17 +13256,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>69752256a68dd603be29f508</t>
+          <t>6946c6f73a8ebd03f25fc9a3</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Hierro</t>
+          <t>Nsongo</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -13283,22 +13283,22 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>69890d253b0d1b03ea61084c</t>
+          <t>696e8199368a5803c07f3bc1</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Cestero</t>
+          <t>Eriksson</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -13310,22 +13310,22 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a358ea99542a303bf19bf7a</t>
+          <t>69752256a68dd603be29f508</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Sangante</t>
+          <t>Hierro</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -13337,17 +13337,17 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>51bcc35c377408301a00000c</t>
+          <t>69890d253b0d1b03ea61084c</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Vecino</t>
+          <t>Cestero</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -13364,22 +13364,22 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>5d43ec6312ba017aeb3ad5ae</t>
+          <t>6a358ea99542a303bf19bf7a</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Sancet</t>
+          <t>Sangante</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>5851e8da3defeb5375f2cb30</t>
+          <t>51bcc35c377408301a00000c</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Vecino</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -13418,17 +13418,17 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>5d58321f489a8e5316ca89d6</t>
+          <t>5d43ec6312ba017aeb3ad5ae</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Iker Losada</t>
+          <t>Sancet</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -13445,22 +13445,22 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>59c2d829bd61e7f10c49a9b6</t>
+          <t>5851e8da3defeb5375f2cb30</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Edu Expósito</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -13472,12 +13472,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>5da39ad5b8e82e5c69ab75f9</t>
+          <t>5d58321f489a8e5316ca89d6</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Valles</t>
+          <t>Iker Losada</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -13499,22 +13499,22 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>5a81f13ce3c1953064f782e0</t>
+          <t>59c2d829bd61e7f10c49a9b6</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Junior Firpo</t>
+          <t>Edu Expósito</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -13526,22 +13526,22 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>5efa4e35ee5a640417710119</t>
+          <t>5da39ad5b8e82e5c69ab75f9</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Jon Pacheco</t>
+          <t>Valles</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -13553,22 +13553,22 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5a81f13ce3c1953064f782e0</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Junior Firpo</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -13580,22 +13580,22 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>60d73641b7fb6703d3e21ba8</t>
+          <t>5efa4e35ee5a640417710119</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Olasagasti</t>
+          <t>Jon Pacheco</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -13607,17 +13607,17 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>5bd4d4dd2549d75a2c65508e</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -13634,22 +13634,22 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>60e72704dfb903607d1f7d87</t>
+          <t>60d73641b7fb6703d3e21ba8</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Dituro</t>
+          <t>Olasagasti</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -13661,17 +13661,17 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>61228f14bee4ec08574d99bf</t>
+          <t>5bd4d4dd2549d75a2c65508e</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Haitam</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -13688,22 +13688,22 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>60e72704dfb903607d1f7d87</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Dituro</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -13715,22 +13715,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>61bd0e030d81623e3a2b0f28</t>
+          <t>61228f14bee4ec08574d99bf</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Rubén Sánchez</t>
+          <t>Haitam</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -13742,17 +13742,17 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>5f80c8e8a9c2e74fca8282e9</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Ruggeri</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -13769,22 +13769,22 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>61dcacebb6d6540425b75dce</t>
+          <t>61bd0e030d81623e3a2b0f28</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Rubén Sánchez</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -13796,22 +13796,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>62b3132cb2a1132d77c95799</t>
+          <t>5f80c8e8a9c2e74fca8282e9</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Arana</t>
+          <t>Ruggeri</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -13823,22 +13823,22 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>61fef82a9b83fa2769ffc896</t>
+          <t>61dcacebb6d6540425b75dce</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Iker Benito</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>64d3c4746167273d0ccc5c52</t>
+          <t>62b3132cb2a1132d77c95799</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Pablo Ramón</t>
+          <t>Arana</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -13877,17 +13877,17 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>62c3721bc057ca2d85a00512</t>
+          <t>61fef82a9b83fa2769ffc896</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Giuliano Simeone</t>
+          <t>Iker Benito</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -13904,22 +13904,22 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>64ea79b9b1931503ca17ef44</t>
+          <t>64d3c4746167273d0ccc5c52</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Dani Requena</t>
+          <t>Pablo Ramón</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -13931,22 +13931,22 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>632f6e29e25c770b961eabe9</t>
+          <t>62c3721bc057ca2d85a00512</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Giuliano Simeone</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -13958,12 +13958,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>64f11152061d1303c4816c1f</t>
+          <t>64ea79b9b1931503ca17ef44</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Tai Abed</t>
+          <t>Dani Requena</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -13985,17 +13985,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>632f6f28d2f4c20bd75d484b</t>
+          <t>632f6e29e25c770b961eabe9</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Carlos Romero</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -14012,17 +14012,17 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>64f4d4b99318fc03ee16e82d</t>
+          <t>64f11152061d1303c4816c1f</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Amatucci</t>
+          <t>Tai Abed</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -14039,22 +14039,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>632f6f28d2f4c20bd75d484b</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Carlos Romero</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -14066,17 +14066,17 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>66ccfe37683d1203dc8a58b3</t>
+          <t>64f4d4b99318fc03ee16e82d</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Alfon</t>
+          <t>Amatucci</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -14093,22 +14093,22 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>66841f9cd8d63f414aab7434</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Pelayo</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -14120,17 +14120,17 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6806b68446e3f90444f1d995</t>
+          <t>66ccfe37683d1203dc8a58b3</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Rafa Rodríguez</t>
+          <t>Alfon</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -14147,17 +14147,17 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>66b8ed0a702b9203b99a1705</t>
+          <t>66841f9cd8d63f414aab7434</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Hugo Rincón</t>
+          <t>Pelayo</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -14174,22 +14174,22 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6876c12606428a0452dc7fa6</t>
+          <t>6806b68446e3f90444f1d995</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Áron Yaakobishvili</t>
+          <t>Rafa Rodríguez</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -14201,22 +14201,22 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>66b8ed0a702b9203b99a1705</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>Hugo Rincón</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -14228,22 +14228,22 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>6876c12606428a0452dc7fa6</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Áron Yaakobishvili</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -14255,22 +14255,22 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>678bea540e424b7573dc9cf3</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Adrián Niño</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -14282,17 +14282,17 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>696c1bb8af58fa040efb6d15</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Zaid Romero</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>67d4acc7fb012703e17d1dc5</t>
+          <t>678bea540e424b7573dc9cf3</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Adrián R.</t>
+          <t>Adrián Niño</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -14336,17 +14336,17 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>697e90b3ff715b03c5df8278</t>
+          <t>696c1bb8af58fa040efb6d15</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Koski</t>
+          <t>Zaid Romero</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -14363,22 +14363,22 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>68251aa7172c6403d639c211</t>
+          <t>67d4acc7fb012703e17d1dc5</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Adrián R.</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -14390,22 +14390,22 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>69810c427602e303cbed6a3e</t>
+          <t>697e90b3ff715b03c5df8278</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Obed Vargas</t>
+          <t>Koski</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -14417,17 +14417,17 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>688fbfc45c7211044690a3d3</t>
+          <t>69810c427602e303cbed6a3e</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Selu Diallo</t>
+          <t>Obed Vargas</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -14444,17 +14444,17 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4d1c7ce284b949d26e34f5</t>
+          <t>688fbfc45c7211044690a3d3</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Sato</t>
+          <t>Selu Diallo</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -14471,22 +14471,22 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6988af503b0d1b03ea60fa11</t>
+          <t>6a4d1c7ce284b949d26e34f5</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Aitor Mañas</t>
+          <t>Sato</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -14498,22 +14498,22 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a39255e9b413b03b20c1fd5</t>
+          <t>6988af503b0d1b03ea60fa11</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>De Haas</t>
+          <t>Aitor Mañas</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -14525,22 +14525,22 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>5989b1729c265fd44b8f102c</t>
+          <t>6a39255e9b413b03b20c1fd5</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Carles Pérez</t>
+          <t>De Haas</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -14552,22 +14552,22 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a6700017a</t>
+          <t>5989b1729c265fd44b8f102c</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Courtois</t>
+          <t>Carles Pérez</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -14579,22 +14579,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>5b43ab6e5c2992ae0bf69a35</t>
+          <t>504e58bb4d8bec9a6700017a</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Gonzalo Villar</t>
+          <t>Courtois</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -14606,22 +14606,22 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000bc</t>
+          <t>5b43ab6e5c2992ae0bf69a35</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Szczesny</t>
+          <t>Gonzalo Villar</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -14633,22 +14633,22 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>5c0eea87e3eca97d26f62cee</t>
+          <t>51cb698301d64ad4700000bc</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Pedrosa</t>
+          <t>Szczesny</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -14660,22 +14660,22 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>58e1616852a7d14c54bb26d3</t>
+          <t>5c0eea87e3eca97d26f62cee</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Carles Aleñá</t>
+          <t>Pedrosa</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -14687,12 +14687,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>5c8bf51dc84b6a5140cdd554</t>
+          <t>58e1616852a7d14c54bb26d3</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Guevara</t>
+          <t>Carles Aleñá</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>5989a27fd094c1ec4bdbf741</t>
+          <t>5c8bf51dc84b6a5140cdd554</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Unai Núñez</t>
+          <t>Guevara</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -14741,22 +14741,22 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>5d430d22b1b9c77b1c9551f7</t>
+          <t>5989a27fd094c1ec4bdbf741</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Nicolas Pépé</t>
+          <t>Unai Núñez</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -14768,22 +14768,22 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>59ff3b0329d7bf994b9e01f0</t>
+          <t>5d430d22b1b9c77b1c9551f7</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Tenaglia</t>
+          <t>Nicolas Pépé</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -14795,17 +14795,17 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>5eef6e9c4fa17f5218f7d433</t>
+          <t>59ff3b0329d7bf994b9e01f0</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Javier López</t>
+          <t>Tenaglia</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -14822,22 +14822,22 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>5a3578e0feceda7e2716a6c7</t>
+          <t>5eef6e9c4fa17f5218f7d433</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrán Torres </t>
+          <t>Javier López</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -14849,22 +14849,22 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>5f32e17633a68903ecffbd1f</t>
+          <t>5a3578e0feceda7e2716a6c7</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t xml:space="preserve">Ferrán Torres </t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -14876,22 +14876,22 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>5a639998e2a0fd3424128d06</t>
+          <t>5f32e17633a68903ecffbd1f</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Brahim Díaz</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -14903,22 +14903,22 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>5fc1512d94ce070e962e3a3c</t>
+          <t>5a639998e2a0fd3424128d06</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Cárdenas</t>
+          <t>Brahim Díaz</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -14930,22 +14930,22 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>5b958b5a57a45c624cf0747d</t>
+          <t>5fc1512d94ce070e962e3a3c</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Andrés Martín</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -14957,22 +14957,22 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>60980a25b7ad5b0920afde9e</t>
+          <t>5b958b5a57a45c624cf0747d</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Carlos Domínguez</t>
+          <t>Andrés Martín</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -14984,22 +14984,22 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>5c437caeb40d97040e679cb2</t>
+          <t>60980a25b7ad5b0920afde9e</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Joaquín Muñoz</t>
+          <t>Carlos Domínguez</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -15011,22 +15011,22 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>617db824fca9f703e07b2a81</t>
+          <t>5c437caeb40d97040e679cb2</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Abde Ezzalzouli</t>
+          <t>Joaquín Muñoz</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -15038,17 +15038,17 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>5d134f035af255065129d598</t>
+          <t>617db824fca9f703e07b2a81</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Nteka</t>
+          <t>Abde Ezzalzouli</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -15065,22 +15065,22 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>62b30b04d367e02dade46984</t>
+          <t>5d134f035af255065129d598</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Iñigo Sainz</t>
+          <t>Nteka</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -15092,22 +15092,22 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>5e23437d616e7d03ba5dc21c</t>
+          <t>62b30b04d367e02dade46984</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Iñigo Sainz</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -15119,22 +15119,22 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>5e23437d616e7d03ba5dc21c</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>63cdb1fff41df804fa60e6f1</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Castrín</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15173,22 +15173,22 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>607325f27b19b30c4fb34081</t>
+          <t>63cdb1fff41df804fa60e6f1</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Urko González</t>
+          <t>Castrín</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15200,17 +15200,17 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>63d8eb7b1d17ae5aff1f4c52</t>
+          <t>607325f27b19b30c4fb34081</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Urko González</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -15227,22 +15227,22 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>62c03520b2a1132d77c957bd</t>
+          <t>63d8eb7b1d17ae5aff1f4c52</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -20187,6 +20187,33 @@
         </is>
       </c>
       <c r="E732" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>51d14b1478d9b68505000018</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Abdoulaye Faye</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E736"/>
+  <dimension ref="A1:E738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3050,12 +3050,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>69d1843021ab3804095dc5d2</t>
+          <t>69daa74298d9eb0426259b22</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Boñar</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3077,12 +3077,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>69daa74298d9eb0426259b22</t>
+          <t>69daa6da17877004192cea21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Boñar</t>
+          <t>Belaid</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>69daa6da17877004192cea21</t>
+          <t>69daa71455f89f041388274a</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Belaid</t>
+          <t>Dani Martínez</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3131,12 +3131,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>69daa71455f89f041388274a</t>
+          <t>6687123799f9bf415ff44157</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dani Martínez</t>
+          <t>Puric</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3158,12 +3158,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6687123799f9bf415ff44157</t>
+          <t>69f632503caa6b0472477da2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Puric</t>
+          <t>Iker Luque</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3185,12 +3185,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>69f632503caa6b0472477da2</t>
+          <t>69f632161fe2c90424d568b4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Iker Luque</t>
+          <t>Cubo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3212,17 +3212,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>69f632161fe2c90424d568b4</t>
+          <t>6a06409cd60a6e0400dd5242</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cubo</t>
+          <t>Carrera</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6a06409cd60a6e0400dd5242</t>
+          <t>6a1221dac0afe2057c5f8e0c</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Carrera</t>
+          <t>Ochieng</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3266,12 +3266,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6a1221dac0afe2057c5f8e0c</t>
+          <t>6a122197fd42ba053658e853</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ochieng</t>
+          <t>Beitia</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3293,22 +3293,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6a122197fd42ba053658e853</t>
+          <t>666828c79fdd6e041049a44d</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Beitia</t>
+          <t>Javi Serrano</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3320,22 +3320,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>666828c79fdd6e041049a44d</t>
+          <t>51d70ed7a7178a7654000012</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Javi Serrano</t>
+          <t>Mojica</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3347,22 +3347,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>51d70ed7a7178a7654000012</t>
+          <t>504f647e4d8bec9a67000484</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mojica</t>
+          <t>Stuani</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3374,12 +3374,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>504f647e4d8bec9a67000484</t>
+          <t>5313988280c359915f000011</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Stuani</t>
+          <t>Portu</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3401,12 +3401,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5313988280c359915f000011</t>
+          <t>51cab26c01d64ad470000096</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Portu</t>
+          <t>Gazzaniga</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3428,22 +3428,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>51cab26c01d64ad470000096</t>
+          <t>5210908da776cc826b000067</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Gazzaniga</t>
+          <t>Darder</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3455,22 +3455,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5210908da776cc826b000067</t>
+          <t>54c509f75d97b9070200178c</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Darder</t>
+          <t>Dani Calvo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3482,22 +3482,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>54c509f75d97b9070200178c</t>
+          <t>57583b4733dbe3424c05e8ee</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dani Calvo</t>
+          <t>Luis Milla</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>6662aa5981b2080416a23781</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3509,22 +3509,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>57583b4733dbe3424c05e8ee</t>
+          <t>521b5f939f2adc783700001e</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Luis Milla</t>
+          <t>David Costas</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>6662aa5981b2080416a23781</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3536,17 +3536,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>521b5f939f2adc783700001e</t>
+          <t>520263c1ed2e70cb370000c1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>David Costas</t>
+          <t>Raíllo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3563,22 +3563,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>520263c1ed2e70cb370000c1</t>
+          <t>504f65684d8bec9a6700072d</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Raíllo</t>
+          <t>Griezmann</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3590,22 +3590,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>504f65684d8bec9a6700072d</t>
+          <t>62fd1a08e88c090690b05916</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Griezmann</t>
+          <t>Nianzou</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3617,22 +3617,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>62fd1a08e88c090690b05916</t>
+          <t>66cf964ebd0d6403c8b5d5ad</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nianzou</t>
+          <t>Viñas</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520025dc19cbe47807000087</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3644,17 +3644,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>66cf964ebd0d6403c8b5d5ad</t>
+          <t>63f14fbb79f25a5b3f34fedd</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Viñas</t>
+          <t>Álvaro Rodríguez</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>520025dc19cbe47807000087</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3671,22 +3671,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>63f14fbb79f25a5b3f34fedd</t>
+          <t>56116ea6ffa60f6504776520</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Álvaro Rodríguez</t>
+          <t>Pedraza</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b1aac753cd14971700002e</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3698,17 +3698,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>56116ea6ffa60f6504776520</t>
+          <t>51b8ab26e401a15f2c00016a</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Pedraza</t>
+          <t>Carvajal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>51b1aac753cd14971700002e</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>51b8ab26e401a15f2c00016a</t>
+          <t>5fbe33c11fd5fa0e8491689f</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Carvajal</t>
+          <t>Mingueza</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3752,22 +3752,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5fbe33c11fd5fa0e8491689f</t>
+          <t>67772046474b6075b3a81ef3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mingueza</t>
+          <t>Krapyvtsov</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3779,12 +3779,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>67772046474b6075b3a81ef3</t>
+          <t>667ddd02cf0d0c4167933890</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Krapyvtsov</t>
+          <t>Abel Ruiz</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3806,12 +3806,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>667ddd02cf0d0c4167933890</t>
+          <t>668e7743c34e5603e02bf624</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Abel Ruiz</t>
+          <t>Misehouy</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>668e7743c34e5603e02bf624</t>
+          <t>64a0a08ba58cb1732757ad81</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Misehouy</t>
+          <t>Reina</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3860,12 +3860,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>64a0a08ba58cb1732757ad81</t>
+          <t>64a67bacafd9eb7360360e75</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Reina</t>
+          <t>Ilyas Chaira</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>64a67bacafd9eb7360360e75</t>
+          <t>66b4b8f16e037203f626839f</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ilyas Chaira</t>
+          <t>Izeta</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3914,22 +3914,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>66b4b8f16e037203f626839f</t>
+          <t>66b8fc5699635f03debf8fe8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Izeta</t>
+          <t>Parada</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3941,17 +3941,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>66b8fc5699635f03debf8fe8</t>
+          <t>5ee8f3b114cfa703f145c050</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Parada</t>
+          <t>Francés</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3968,22 +3968,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5ee8f3b114cfa703f145c050</t>
+          <t>57a63dc00aba5e3906c78493</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Francés</t>
+          <t>Escandell</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -3995,12 +3995,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>57a63dc00aba5e3906c78493</t>
+          <t>5995a8857c7bb19d3a5d41cd</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Escandell</t>
+          <t>Nacho Vidal</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4022,22 +4022,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5995a8857c7bb19d3a5d41cd</t>
+          <t>5f4fd2e6c5c6f903e7c2522e</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nacho Vidal</t>
+          <t>Van de Beek</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4049,22 +4049,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5f4fd2e6c5c6f903e7c2522e</t>
+          <t>6797e70083b5f103b7013774</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Van de Beek</t>
+          <t>Akor Adams</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4076,17 +4076,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6797e70083b5f103b7013774</t>
+          <t>5f614957d59f315e1fc77bd2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Akor Adams</t>
+          <t>Muriqi</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>5220ce9fc90c7ea70b000047</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4103,22 +4103,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5f614957d59f315e1fc77bd2</t>
+          <t>61efea4ec6dfbe0a4fa10b18</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Muriqi</t>
+          <t>Eray Cömert</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>5220ce9fc90c7ea70b000047</t>
+          <t>52026c99fdbb14c13700007f</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4130,22 +4130,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>61efea4ec6dfbe0a4fa10b18</t>
+          <t>6861c08a7275493329a95613</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Eray Cömert</t>
+          <t>Dominguès</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>52026c99fdbb14c13700007f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6861c08a7275493329a95613</t>
+          <t>521ddaa240f3fd66010001fa</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dominguès</t>
+          <t>Abdón Prats</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4184,12 +4184,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>521ddaa240f3fd66010001fa</t>
+          <t>5d69113cf91a3f7778179cb7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Abdón Prats</t>
+          <t>Antonio Sánchez</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4211,17 +4211,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5d69113cf91a3f7778179cb7</t>
+          <t>5f36db010b759303ff680104</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Antonio Sánchez</t>
+          <t xml:space="preserve">Iván Martín </t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,12 +4238,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5f36db010b759303ff680104</t>
+          <t>6060aa1a7a64b003da0efc7d</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Martín </t>
+          <t>Arnau Martínez</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4265,22 +4265,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6060aa1a7a64b003da0efc7d</t>
+          <t>61112696dfb903607d1f7e45</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Arnau Martínez</t>
+          <t>Haissem Hassan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,17 +4292,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>61112696dfb903607d1f7e45</t>
+          <t>63092ba34c71a52ba37b8165</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Haissem Hassan</t>
+          <t>Joel Roca</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4319,12 +4319,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>63092ba34c71a52ba37b8165</t>
+          <t>63c6945172c559051c25d9fa</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Joel Roca</t>
+          <t>Tsygankov</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4346,12 +4346,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>63c6945172c559051c25d9fa</t>
+          <t>57b94cfee3480bb6049eb14b</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Tsygankov</t>
+          <t>Fran Beltrán</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4373,22 +4373,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>57b94cfee3480bb6049eb14b</t>
+          <t>587413fa39af105c4b075f23</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Fran Beltrán</t>
+          <t>Toni Lato</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4400,12 +4400,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>587413fa39af105c4b075f23</t>
+          <t>5f5a930b58df197b1823bfe7</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Toni Lato</t>
+          <t>Samú Costa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,17 +4427,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5f5a930b58df197b1823bfe7</t>
+          <t>64d803c883596124e55c064f</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Samú Costa</t>
+          <t>Unai Gómez</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4454,22 +4454,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>64d803c883596124e55c064f</t>
+          <t>6689c562e0157a03f87fbf0e</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Unai Gómez</t>
+          <t>Morey</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4481,22 +4481,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6689c562e0157a03f87fbf0e</t>
+          <t>67575e411a57f003d0b21843</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Morey</t>
+          <t>Coba da Costa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4508,22 +4508,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>67575e411a57f003d0b21843</t>
+          <t>51c1fdeac7694f5f66000051</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Coba da Costa</t>
+          <t>David López</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4535,17 +4535,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>51c1fdeac7694f5f66000051</t>
+          <t>5b59e02c66831ded570d44f4</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>David López</t>
+          <t>Valjent</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4562,12 +4562,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5b59e02c66831ded570d44f4</t>
+          <t>5b786a5d95ea0b2b07e4e66e</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Valjent</t>
+          <t>Morlanes</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4589,22 +4589,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5b786a5d95ea0b2b07e4e66e</t>
+          <t>5c0416954c47343bad939db8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Morlanes</t>
+          <t>Valery Fernández</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d4</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5c0416954c47343bad939db8</t>
+          <t>62e39ff011f4242dbd725314</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Valery Fernández</t>
+          <t>Pablo Torre</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d4</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,12 +4643,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>62e39ff011f4242dbd725314</t>
+          <t>66b352197fc6ff03fb06fb13</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Pablo Torre</t>
+          <t>D. López</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4670,17 +4670,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>66b352197fc6ff03fb06fb13</t>
+          <t>67310caf29e197051e04f422</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>D. López</t>
+          <t>Ferrán Ruiz</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4697,17 +4697,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>67310caf29e197051e04f422</t>
+          <t>6695372399e2e504052cbbae</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ferrán Ruiz</t>
+          <t>Rahim</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4724,22 +4724,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6695372399e2e504052cbbae</t>
+          <t>65b12f7b992bcf53bfe2fc31</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Rahim</t>
+          <t>Moldovan</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4751,17 +4751,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>65b12f7b992bcf53bfe2fc31</t>
+          <t>66d61f2aed648e0b1ac63f1a</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Moldovan</t>
+          <t>Bergström</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4778,22 +4778,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>66d61f2aed648e0b1ac63f1a</t>
+          <t>5d5570f69bb8253fe4f452d6</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Bergström</t>
+          <t>Ahijado</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,12 +4805,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5d5570f69bb8253fe4f452d6</t>
+          <t>66d81870433f040b000aa40c</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ahijado</t>
+          <t>Luka Ilic</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4832,22 +4832,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>66d81870433f040b000aa40c</t>
+          <t>57c73a7a803dc6bd7be02981</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Luka Ilic</t>
+          <t>Pau López</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4859,22 +4859,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>57c73a7a803dc6bd7be02981</t>
+          <t>56d314416116845b08e61bed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Pau López</t>
+          <t>Rashford</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51d19d0f78d9b6850500003e</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4886,22 +4886,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>56d314416116845b08e61bed</t>
+          <t>68951eec4e36d6040c695ed8</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Rashford</t>
+          <t>Santamaria</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>51d19d0f78d9b6850500003e</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>68951eec4e36d6040c695ed8</t>
+          <t>62c5da44fbbaa82d71999775</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Santamaria</t>
+          <t>Witsel</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4940,22 +4940,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>62c5da44fbbaa82d71999775</t>
+          <t>65a2f7b8b94b7303dce5ccac</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Witsel</t>
+          <t>Marco Esteban</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4967,12 +4967,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>65a2f7b8b94b7303dce5ccac</t>
+          <t>689fb8cb06428a0452dc8034</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Marco Esteban</t>
+          <t>Omar Falah</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4994,12 +4994,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>689fb8cb06428a0452dc8034</t>
+          <t>5b6cc28068b47b496279f860</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Omar Falah</t>
+          <t>Dendoncker</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5021,22 +5021,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5b6cc28068b47b496279f860</t>
+          <t>53ac3e6c1933f2de6f0003fc</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dendoncker</t>
+          <t>Álex Moreno</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5048,22 +5048,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>53ac3e6c1933f2de6f0003fc</t>
+          <t>5f43f5bf0b759303ff680853</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Álex Moreno</t>
+          <t>Ramazani</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>57a1235f445c20291844c133</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5075,17 +5075,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5f43f5bf0b759303ff680853</t>
+          <t>68b0df5c11ed3a059c4912a3</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ramazani</t>
+          <t>Virgili</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>57a1235f445c20291844c133</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5102,22 +5102,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>68b0df5c11ed3a059c4912a3</t>
+          <t>68b37c6461185205e8c364db</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Virgili</t>
+          <t>Ounahi</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5129,12 +5129,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>68b37c6461185205e8c364db</t>
+          <t>68b59fba05c30a03fb36d382</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ounahi</t>
+          <t>Vanat</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5156,12 +5156,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>68b59fba05c30a03fb36d382</t>
+          <t>5c323b46bef16503ec960e1c</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Vanat</t>
+          <t>Bryan Gil</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5183,12 +5183,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5c323b46bef16503ec960e1c</t>
+          <t>68f3b8b9dd3614500b418a49</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Bryan Gil</t>
+          <t>Lass</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5210,22 +5210,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>68f3b8b9dd3614500b418a49</t>
+          <t>52024320737b88c937000019</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Lass</t>
+          <t xml:space="preserve"> João Cancelo</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>52024320737b88c937000019</t>
+          <t>696a39e9af58fa040efb5372</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> João Cancelo</t>
+          <t>Kalumba</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5264,17 +5264,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>696a39e9af58fa040efb5372</t>
+          <t>66a3d3797fc6ff03fb06fadf</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kalumba</t>
+          <t>Echeverri</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51d197b30719708a05000037</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5291,22 +5291,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fadf</t>
+          <t>6977e776fee4e803e0e8bed5</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Echeverri</t>
+          <t>Arango</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>51d197b30719708a05000037</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5318,22 +5318,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6977e776fee4e803e0e8bed5</t>
+          <t>675366baf7be6b107f01b952</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Arango</t>
+          <t>Fer López</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>57a12447445c20291844c142</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5345,17 +5345,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>675366baf7be6b107f01b952</t>
+          <t>68a0ebed3a1cb503e4684dca</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Fer López</t>
+          <t>Jan  Salas</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>57a12447445c20291844c142</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5372,17 +5372,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>68a0ebed3a1cb503e4684dca</t>
+          <t>6a04f3f3f8f6ef041e55261c</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Jan  Salas</t>
+          <t>Damián</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5399,22 +5399,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6a04f3f3f8f6ef041e55261c</t>
+          <t>6a04f502781278043f2eda16</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Damián</t>
+          <t>Orejuela</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5426,22 +5426,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>6a04f502781278043f2eda16</t>
+          <t>61844713165d9f09c3eecd07</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Orejuela</t>
+          <t>Artero</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5453,17 +5453,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>61844713165d9f09c3eecd07</t>
+          <t>61c3b14eb4f96c073bf94ce7</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Artero</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5480,17 +5480,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>61c3b14eb4f96c073bf94ce7</t>
+          <t>674b7a94c9efc910567f19b6</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5507,22 +5507,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>674b7a94c9efc910567f19b6</t>
+          <t>66cfa272b46ff704160ad00e</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Adrián Pica</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5534,22 +5534,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>66cfa272b46ff704160ad00e</t>
+          <t>686feb558bef76044eadf791</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Adrián Pica</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5561,22 +5561,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>686feb558bef76044eadf791</t>
+          <t>6683c6e90ab8ba417f3276b6</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Unai Ropero</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5588,17 +5588,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>6683c6e90ab8ba417f3276b6</t>
+          <t>67597e6b317cba0418bce297</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Unai Ropero</t>
+          <t>Dani Luna</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>67597e6b317cba0418bce297</t>
+          <t>66d39b3d58f2de32117efa18</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Dani Luna</t>
+          <t>Domenech</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5642,17 +5642,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>66d39b3d58f2de32117efa18</t>
+          <t>57b94a3c7ce1feed040b24e3</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Domenech</t>
+          <t>Jacobo González</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>57b94a3c7ce1feed040b24e3</t>
+          <t>64b1c502c35fcb3cfd3ed505</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Jacobo González</t>
+          <t>Youness</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5696,12 +5696,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>64b1c502c35fcb3cfd3ed505</t>
+          <t>6865adefd4d22b330615f7ca</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Youness</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5723,12 +5723,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>6865adefd4d22b330615f7ca</t>
+          <t>60e6e2841a405a604ca8c2d7</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Luengo</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>60e6e2841a405a604ca8c2d7</t>
+          <t>669274f3ce303803d6f77330</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Luengo</t>
+          <t>Paraschiv</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -5777,12 +5777,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>669274f3ce303803d6f77330</t>
+          <t>6584aa689b9f5d700573fd05</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Paraschiv</t>
+          <t>Cardero</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -5804,17 +5804,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6584aa689b9f5d700573fd05</t>
+          <t>697be226df6332040670c6c1</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Cardero</t>
+          <t>Izan González</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>697be226df6332040670c6c1</t>
+          <t>6a35c168152d0603c64c029a</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Izan González</t>
+          <t>Pyshchur</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6a35c168152d0603c64c029a</t>
+          <t>68a9e8aab479f05404a946c8</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Pyshchur</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5885,12 +5885,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>68a9e8aab479f05404a946c8</t>
+          <t>6713fdc9a1b917176a03238a</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Min-su Kim</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5912,12 +5912,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>6713fdc9a1b917176a03238a</t>
+          <t>66c9b0acf119260402e26288</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Min-su Kim</t>
+          <t>Asprilla</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5939,12 +5939,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>66c9b0acf119260402e26288</t>
+          <t>65f5fc5000ffc34f05f1cb1f</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Asprilla</t>
+          <t>Jastin</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5966,12 +5966,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>65f5fc5000ffc34f05f1cb1f</t>
+          <t>65ad994d76a3e353be71263f</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Jastin</t>
+          <t>Antal Yaakobishvili</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5993,17 +5993,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>65ad994d76a3e353be71263f</t>
+          <t>63053ef3f14610075abd00f0</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Antal Yaakobishvili</t>
+          <t>Özkacar</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6020,22 +6020,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>63053ef3f14610075abd00f0</t>
+          <t>6861890daedcdd33075dd01d</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Özkacar</t>
+          <t>Adri Fuentes</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6047,17 +6047,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6861890daedcdd33075dd01d</t>
+          <t>6795426c91d9bd03c793c426</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Adri Fuentes</t>
+          <t>Diego Gómez</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6074,22 +6074,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6795426c91d9bd03c793c426</t>
+          <t>63bb149eba53bb03cdfc2e9f</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Diego Gómez</t>
+          <t>Cabanzón</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6101,17 +6101,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>63bb149eba53bb03cdfc2e9f</t>
+          <t>64fb90eebc6e0003e0366f4f</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cabanzón</t>
+          <t>Roca</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6128,22 +6128,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>64fb90eebc6e0003e0366f4f</t>
+          <t>521b69bf359d42743700007f</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Roca</t>
+          <t>Carlos Fernández</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6155,22 +6155,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>521b69bf359d42743700007f</t>
+          <t>6305da4d46d783071421441c</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Carlos Fernández</t>
+          <t>Arnau Tenas</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6182,22 +6182,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6305da4d46d783071421441c</t>
+          <t>5cfc2be98721525ead8d94b1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Arnau Tenas</t>
+          <t>Gragera</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6209,22 +6209,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5cfc2be98721525ead8d94b1</t>
+          <t>64be9241b6533c3d2112572f</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Gragera</t>
+          <t>Petxarroman</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6236,22 +6236,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>64be9241b6533c3d2112572f</t>
+          <t>65f7126c17c8f74f39434408</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Petxarroman</t>
+          <t>Damián Rodríguez</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6263,22 +6263,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>65f7126c17c8f74f39434408</t>
+          <t>61da0a69b6d6540425b749e4</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Damián Rodríguez</t>
+          <t>Bouldini</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6290,22 +6290,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>61da0a69b6d6540425b749e4</t>
+          <t>5590e843b804493642903daa</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Bouldini</t>
+          <t>Vesga</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6317,22 +6317,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5590e843b804493642903daa</t>
+          <t>690f6102072c5e03d67ac3e5</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Vesga</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -6344,22 +6344,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>690f6102072c5e03d67ac3e5</t>
+          <t>696184347cc74203effd6ff6</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Mestanza</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -6371,17 +6371,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>696184347cc74203effd6ff6</t>
+          <t>66a3c8069e452303b3fc0b22</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Mestanza</t>
+          <t>Albarracín</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6398,17 +6398,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>66a3c8069e452303b3fc0b22</t>
+          <t>69ab5b4653966303fb66b781</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Albarracín</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6425,12 +6425,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>69ab5b4653966303fb66b781</t>
+          <t>68251aa7172c6403d639c211</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6452,17 +6452,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>68251aa7172c6403d639c211</t>
+          <t>62c03520b2a1132d77c957bd</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6479,22 +6479,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>62c03520b2a1132d77c957bd</t>
+          <t>51b9d964e401a15f2c000174</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Ter Stegen</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6506,22 +6506,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>51b9d964e401a15f2c000174</t>
+          <t>57bb7cea45e6bed0520a420a</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ter Stegen</t>
+          <t>Rafa Mir</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6533,22 +6533,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>57bb7cea45e6bed0520a420a</t>
+          <t>57b5c2d87e2ec2df1922966f</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Rafa Mir</t>
+          <t>Elgezabal</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6560,22 +6560,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>57b5c2d87e2ec2df1922966f</t>
+          <t>6757ff71d2717703ca746142</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Elgezabal</t>
+          <t>Cabanes</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -17954,22 +17954,22 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6757ff71d2717703ca746142</t>
+          <t>676889368e803803f4d3ae2f</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Cabanes</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -17981,17 +17981,17 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>676889368e803803f4d3ae2f</t>
+          <t>68c5f54d83815b05817ba3bd</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Ángel Recio</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -18008,22 +18008,22 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>68c5f54d83815b05817ba3bd</t>
+          <t>690c69e2c2cdbf03b2f132e8</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Ángel Recio</t>
+          <t>Selton</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -18035,17 +18035,17 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>690c69e2c2cdbf03b2f132e8</t>
+          <t>6a35925b33c8f103cdc11d15</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Selton</t>
+          <t>Bardeli</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -18062,22 +18062,22 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a35925b33c8f103cdc11d15</t>
+          <t>595a41faa79c0bc13fef9941</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Bardeli</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -18089,22 +18089,22 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>595a41faa79c0bc13fef9941</t>
+          <t>5965241adff2c6ba74e48df7</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Febas</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -18116,17 +18116,17 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>5965241adff2c6ba74e48df7</t>
+          <t>596fc4490ef6710375cfbc85</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Febas</t>
+          <t>Javi Muñoz</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -18143,22 +18143,22 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>596fc4490ef6710375cfbc85</t>
+          <t>596fe00fc6269ff074e8eed3</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Javi Muñoz</t>
+          <t>Sivera</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -18170,22 +18170,22 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>596fe00fc6269ff074e8eed3</t>
+          <t>599893cd0999c98e0c5fa382</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Sivera</t>
+          <t>Berrocal</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -18197,22 +18197,22 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>599893cd0999c98e0c5fa382</t>
+          <t>5b34abe685664b531d0b6277</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Berrocal</t>
+          <t>Jorge De Frutos</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -18224,12 +18224,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>5b34abe685664b531d0b6277</t>
+          <t>5cdf2e37121b5404171c6fad</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Jorge De Frutos</t>
+          <t>Pedro Díaz</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -18251,22 +18251,22 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>5cdf2e37121b5404171c6fad</t>
+          <t>5d0235d88721525ead8d96db</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Pedro Díaz</t>
+          <t>Militao</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -18278,12 +18278,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>5d0235d88721525ead8d96db</t>
+          <t>5d0236a3167d9e5eb611db9b</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Militao</t>
+          <t>Rodrygo</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -18305,22 +18305,22 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>5d0236a3167d9e5eb611db9b</t>
+          <t>5d17ceb62cef430674ec2674</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Rodrygo</t>
+          <t>Isi Palazón</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -18332,22 +18332,22 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>5d17ceb62cef430674ec2674</t>
+          <t>5f04e39ee9102e0410faa4fb</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Isi Palazón</t>
+          <t>Víctor García</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -18359,17 +18359,17 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>5f04e39ee9102e0410faa4fb</t>
+          <t>62ab326f996d511b380d0d7a</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Víctor García</t>
+          <t>Álex Pastor</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -18386,17 +18386,17 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>62ab326f996d511b380d0d7a</t>
+          <t>62f12359f1b09a7dd27ba96c</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Álex Pastor</t>
+          <t>Juanlu</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -18413,22 +18413,22 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>62f12359f1b09a7dd27ba96c</t>
+          <t>634c7b36bea7cf1bc21c0076</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Juanlu</t>
+          <t>Juan Cruz</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -18440,17 +18440,17 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>634c7b36bea7cf1bc21c0076</t>
+          <t>63fb9deb1d17ae5aff200834</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Juan Cruz</t>
+          <t>Hugo Sotelo</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -18467,17 +18467,17 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>63fb9deb1d17ae5aff200834</t>
+          <t>6551104e5a61972b4cdf05d3</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Hugo Sotelo</t>
+          <t>Tomás Mendes</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -18494,22 +18494,22 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6551104e5a61972b4cdf05d3</t>
+          <t>65ff69ffaa35cf4f4218da3e</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Tomás Mendes</t>
+          <t>Pau Navarro</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -18521,22 +18521,22 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>65ff69ffaa35cf4f4218da3e</t>
+          <t>6671ab8611ff341c4c5eac0d</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Pau Navarro</t>
+          <t>Chidera Ejuke</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -18548,22 +18548,22 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6671ab8611ff341c4c5eac0d</t>
+          <t>66b489b3c34e5603e02c025a</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Chidera Ejuke</t>
+          <t>Nobel Mendy</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -18575,17 +18575,17 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>66b489b3c34e5603e02c025a</t>
+          <t>66b54c2be0157a03f87fcb90</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Nobel Mendy</t>
+          <t>Puga</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -18602,17 +18602,17 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>66b54c2be0157a03f87fcb90</t>
+          <t>66bfad063bdc581a0f65ead1</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Puga</t>
+          <t>Javi Rodríguez</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -18629,17 +18629,17 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>66bfad063bdc581a0f65ead1</t>
+          <t>66c11e2cdad1bc1a1cff9a81</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Javi Rodríguez</t>
+          <t>Gerard Martín</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -18656,22 +18656,22 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>66c11e2cdad1bc1a1cff9a81</t>
+          <t>67804e6ab11a5e759942b02f</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Gerard Martín</t>
+          <t>Kervin Arriaga</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -18683,12 +18683,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>67804e6ab11a5e759942b02f</t>
+          <t>680529fb802b9e0450bb226a</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Kervin Arriaga</t>
+          <t>Eyong</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -18710,22 +18710,22 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>680529fb802b9e0450bb226a</t>
+          <t>68679d128486ff33404f2eef</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Eyong</t>
+          <t>Davinchi</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -18737,22 +18737,22 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>68679d128486ff33404f2eef</t>
+          <t>68b22bf68eb5b005b415a5c6</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Davinchi</t>
+          <t>Oluwaseyi</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -18764,12 +18764,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>68b22bf68eb5b005b415a5c6</t>
+          <t>6990b007612d5404638c8cfe</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Oluwaseyi</t>
+          <t>Hugo López</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -18791,17 +18791,17 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6990b007612d5404638c8cfe</t>
+          <t>6a35b978f1bdb603db6fc1b1</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Hugo López</t>
+          <t>Ateya</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -18818,17 +18818,17 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a35b978f1bdb603db6fc1b1</t>
+          <t>6a4f529258624805c6d283eb</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Ateya</t>
+          <t>Moscardo</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -18845,22 +18845,22 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4f529258624805c6d283eb</t>
+          <t>504f65184d8bec9a67000601</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Moscardo</t>
+          <t>Juanmi</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -18872,22 +18872,22 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a67000601</t>
+          <t>52146427dbf8b74f0200005d</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Juanmi</t>
+          <t>Einar Galilea</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -18899,22 +18899,22 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>52146427dbf8b74f0200005d</t>
+          <t>596110f0f7e346dd7f32a188</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Einar Galilea</t>
+          <t>Cucho</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -18926,22 +18926,22 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>596110f0f7e346dd7f32a188</t>
+          <t>59c419ed548e551c0db5b308</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Cucho</t>
+          <t>Gorosabel</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -18953,22 +18953,22 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>59c419ed548e551c0db5b308</t>
+          <t>5b58ada3c1287fe25740991c</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Gorosabel</t>
+          <t>Benavídez</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -18980,17 +18980,17 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>5b58ada3c1287fe25740991c</t>
+          <t>5d5870e8489a8e5316ca8fc0</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Benavídez</t>
+          <t>Moncayola</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -19007,17 +19007,17 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>5d5870e8489a8e5316ca8fc0</t>
+          <t>5d75a464aad24661e8b1679f</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Moncayola</t>
+          <t>Riki</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -19034,22 +19034,22 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>5d75a464aad24661e8b1679f</t>
+          <t>5df53e5007000504461ce182</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Riki</t>
+          <t>Manu Sánchez</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -19061,22 +19061,22 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>5df53e5007000504461ce182</t>
+          <t>5f0cbbb3075d9b03e1b24de9</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Manu Sánchez</t>
+          <t>Baena</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -19088,17 +19088,17 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>5f0cbbb3075d9b03e1b24de9</t>
+          <t>5f70efc9b69ba04a25453f2c</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Baena</t>
+          <t>Jofre</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -19115,22 +19115,22 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>5f70efc9b69ba04a25453f2c</t>
+          <t>6126993bb52ba2079fdc7828</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Sorloth</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -19142,17 +19142,17 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6126993bb52ba2079fdc7828</t>
+          <t>61be5d8bd58cb63e086bb365</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Sorloth</t>
+          <t>Iván Romero</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -19169,22 +19169,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>61be5d8bd58cb63e086bb365</t>
+          <t>628135edd1a6e308e48ee195</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Iván Romero</t>
+          <t>John Donald</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -19196,22 +19196,22 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>628135edd1a6e308e48ee195</t>
+          <t>64d1243213c6a63ccc321949</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>John Donald</t>
+          <t>Campos</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -19223,22 +19223,22 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>64d1243213c6a63ccc321949</t>
+          <t>66a3c7736e037203f626834e</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Campos</t>
+          <t>Thiago Fernández</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -19250,22 +19250,22 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>66a3c7736e037203f626834e</t>
+          <t>66b3e34ece303803d6f77533</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Thiago Fernández</t>
+          <t>Javi Rueda</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -19277,22 +19277,22 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>66b3e34ece303803d6f77533</t>
+          <t>66c0c8fb8107211a38038907</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Javi Rueda</t>
+          <t>Ochoa</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -19304,22 +19304,22 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>66c0c8fb8107211a38038907</t>
+          <t>672f816c29e197051e04e8e4</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Ochoa</t>
+          <t>Asencio</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -19331,17 +19331,17 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>672f816c29e197051e04e8e4</t>
+          <t>68c5f5d55bd165052e271611</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Asencio</t>
+          <t>Ángel Pérez</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -19358,17 +19358,17 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>68c5f5d55bd165052e271611</t>
+          <t>5d02362afe811c5ea82295cb</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Ángel Pérez</t>
+          <t>Mendy</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -19385,17 +19385,17 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>5d02362afe811c5ea82295cb</t>
+          <t>5d547cd98517403fd8fab746</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Mendy</t>
+          <t>Maras</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -19412,22 +19412,22 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>5d547cd98517403fd8fab746</t>
+          <t>5df6b2179cb8ff03f65a7529</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Maras</t>
+          <t>Agoumé</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -19439,22 +19439,22 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>5df6b2179cb8ff03f65a7529</t>
+          <t>5f6fae0738429649dbf263d6</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Agoumé</t>
+          <t>Boyomo</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -19466,22 +19466,22 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>5f6fae0738429649dbf263d6</t>
+          <t>5f7c91e784180b4fc44cd0ee</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Boyomo</t>
+          <t>Raphinha</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -19493,17 +19493,17 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>5f7c91e784180b4fc44cd0ee</t>
+          <t>6119779ee1a5c851b55b3daf</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Raphinha</t>
+          <t>Lobete</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -19520,22 +19520,22 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6119779ee1a5c851b55b3daf</t>
+          <t>614cc15d3916210732959cc3</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Lobete</t>
+          <t>Robert Navarro</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -19547,22 +19547,22 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>614cc15d3916210732959cc3</t>
+          <t>62815d9a69462008f11c18c0</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Robert Navarro</t>
+          <t>Primo</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -19574,22 +19574,22 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>62815d9a69462008f11c18c0</t>
+          <t>64725d78b20752040bc73eb8</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Primo</t>
+          <t>Bueno</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -19601,17 +19601,17 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>64725d78b20752040bc73eb8</t>
+          <t>6498c43514d4a21e404fd904</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Bueno</t>
+          <t>Álex Sancris</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -19628,17 +19628,17 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6498c43514d4a21e404fd904</t>
+          <t>64b9b83013c6a63ccc32191b</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Álex Sancris</t>
+          <t>Carlos Dotor</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -19655,17 +19655,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>64b9b83013c6a63ccc32191b</t>
+          <t>64eb8df805eacc03e7172e29</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Carlos Dotor</t>
+          <t>Fermín</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -19682,17 +19682,17 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>64eb8df805eacc03e7172e29</t>
+          <t>6647cad9bd5be20441bcc95c</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Fermín</t>
+          <t>Boayar</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -19709,22 +19709,22 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6647cad9bd5be20441bcc95c</t>
+          <t>66998d319e452303b3fc0ae8</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Boayar</t>
+          <t>Moussa Diarra</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -19736,17 +19736,17 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>66998d319e452303b3fc0ae8</t>
+          <t>66a3d3797fc6ff03fb06fad9</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Moussa Diarra</t>
+          <t>Gattoni</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -19763,22 +19763,22 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fad9</t>
+          <t>679505f4ea489a03b4fb00dc</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Gattoni</t>
+          <t>Pablo García</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -19790,17 +19790,17 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>679505f4ea489a03b4fb00dc</t>
+          <t>679e3ac197b9af042545f308</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Pablo García</t>
+          <t>Sannadi</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -19817,22 +19817,22 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>679e3ac197b9af042545f308</t>
+          <t>6869922fd4d22b330615f9fe</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Sannadi</t>
+          <t>Iker Córdoba</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
@@ -19844,12 +19844,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6869922fd4d22b330615f9fe</t>
+          <t>68966a3623f462042dbe3298</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Iker Córdoba</t>
+          <t>Ugrinic</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -19871,22 +19871,22 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>68966a3623f462042dbe3298</t>
+          <t>68adba775730b11c3098162a</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Ugrinic</t>
+          <t>Riedel</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -19898,17 +19898,17 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>68adba775730b11c3098162a</t>
+          <t>6992250a399cbe048cfd966e</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Riedel</t>
+          <t>Nacho Pérez</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -19925,22 +19925,22 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6992250a399cbe048cfd966e</t>
+          <t>5c3a22fd2eb0f60409307e95</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Nacho Pérez</t>
+          <t>Kang-in Lee</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -19952,17 +19952,17 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>5c3a22fd2eb0f60409307e95</t>
+          <t>62d7299dfbbaa82d7199978f</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Kang-in Lee</t>
+          <t>Dubasin</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -19979,22 +19979,22 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>62d7299dfbbaa82d7199978f</t>
+          <t>5f79bdeb02358a040ca3ed7c</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Dubasin</t>
+          <t>Miguel Rodríguez</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -20006,17 +20006,17 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>5f79bdeb02358a040ca3ed7c</t>
+          <t>5e2c95e681b4f252c1de887c</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Miguel Rodríguez</t>
+          <t>Fer Niño</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -20033,22 +20033,22 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>5e2c95e681b4f252c1de887c</t>
+          <t>69a37b194f0be803ae3e49e7</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Fer Niño</t>
+          <t>Julio Díaz</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -20060,22 +20060,22 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>69a37b194f0be803ae3e49e7</t>
+          <t>6a6b5de91c339705c4749fdc</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Julio Díaz</t>
+          <t>Zabiri</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
@@ -20087,22 +20087,22 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a6b5de91c339705c4749fdc</t>
+          <t>55ad2871332f681702ac1350</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Zabiri</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -20114,12 +20114,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>55ad2871332f681702ac1350</t>
+          <t>6a6f41d86767b305a9938268</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Musuayi</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -20141,22 +20141,22 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a6f41d86767b305a9938268</t>
+          <t>51d14b1478d9b68505000018</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Musuayi</t>
+          <t>Abdoulaye Faye</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -20168,22 +20168,22 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>51d14b1478d9b68505000018</t>
+          <t>5774b5ed27ae4bd9135ae2ec</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Abdoulaye Faye</t>
+          <t>Gulácsi</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -20195,22 +20195,22 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>5774b5ed27ae4bd9135ae2ec</t>
+          <t>64f094c1e6bb420409b10378</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Gulácsi</t>
+          <t>Sazonov</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -20222,17 +20222,17 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>64f094c1e6bb420409b10378</t>
+          <t>698127b6163f5f03fb3b4153</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Sazonov</t>
+          <t>Pedro Felipe</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -20249,22 +20249,22 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>698127b6163f5f03fb3b4153</t>
+          <t>6a7363a8db5fee059d38f030</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Pedro Felipe</t>
+          <t>Macià</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -20276,25 +20276,79 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a7363a8db5fee059d38f030</t>
+          <t>67f44ff6e3c6fe0422013801</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Macià</t>
+          <t>Diomande</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>69d1843021ab3804095dc5d2</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Morcillo</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>51b889b1e401a15f2c0000f0</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>6a73c52ac6d839058e96579c</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Hugo González</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E743"/>
+  <dimension ref="A1:E745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20489,6 +20489,60 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>6a7817791d7836057d9e19a6</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Guillén</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d5</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>6a781745af66ad05af1c1054</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Miguel Sierra</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d5</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E748"/>
+  <dimension ref="A1:E749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6911,22 +6911,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>61fef82a9b83fa2769ffc896</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Iker Benito</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6938,17 +6938,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6965,22 +6965,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6992,22 +6992,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5591624ea1736b3a42844561</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Villalibre</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -7019,22 +7019,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>52017ff1cf55e01b3400002e</t>
+          <t>5591624ea1736b3a42844561</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Villalibre</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -7046,17 +7046,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>52017ff1cf55e01b3400002e</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7073,22 +7073,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -7100,17 +7100,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5202890bd7a595bd3700007b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán </t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7127,17 +7127,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>5202890bd7a595bd3700007b</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t xml:space="preserve">Germán </t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7154,12 +7154,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7181,22 +7181,22 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7208,17 +7208,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7235,17 +7235,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7262,17 +7262,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005a6</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ximo Navarro</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7289,17 +7289,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>504f65024d8bec9a670005a6</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Ximo Navarro</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7316,22 +7316,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -7343,22 +7343,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -7370,22 +7370,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7397,22 +7397,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7424,17 +7424,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7451,22 +7451,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -7478,22 +7478,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -7505,22 +7505,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7532,17 +7532,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7559,22 +7559,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>520d0d314386b4816b000029</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Alfonso Herrero</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7586,22 +7586,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>520d0d314386b4816b000029</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Alfonso Herrero</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7640,22 +7640,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -7667,22 +7667,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -7694,22 +7694,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -7721,12 +7721,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7748,22 +7748,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7775,22 +7775,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7802,22 +7802,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -7829,22 +7829,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>51d71d02a7178a7654000017</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Aubameyang</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -7856,22 +7856,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>51d71d02a7178a7654000017</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Aubameyang</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -7883,22 +7883,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7910,22 +7910,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7937,22 +7937,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -7964,22 +7964,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -7991,22 +7991,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -8018,22 +8018,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8045,22 +8045,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8072,22 +8072,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,22 +8126,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>52167e295d086a6726000238</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Jurado</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8153,22 +8153,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>52167e295d086a6726000238</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Jurado</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8180,12 +8180,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8234,17 +8234,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,22 +8315,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8369,22 +8369,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,22 +8504,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -8531,17 +8531,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>53a01453b33bed3b010002b1</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Denis Suárez</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8558,22 +8558,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>53a01453b33bed3b010002b1</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Denis Suárez</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,22 +8585,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,22 +8612,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8639,17 +8639,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8666,22 +8666,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,22 +8693,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8720,12 +8720,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,22 +8774,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8801,17 +8801,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8828,22 +8828,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,22 +8855,22 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>57e816de3c438763749abb90</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Álvaro Fernández</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>57e816de3c438763749abb90</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Álvaro Fernández</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,17 +8909,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8936,12 +8936,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -8963,22 +8963,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -8990,22 +8990,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -9017,17 +9017,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9044,17 +9044,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9071,22 +9071,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -9098,22 +9098,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,22 +9125,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,22 +9206,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>61c0ff53122e933e3d15a643</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Iranzo</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,22 +9233,22 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>61c0ff53122e933e3d15a643</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Iranzo</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -9260,22 +9260,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,22 +9287,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -9314,17 +9314,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9341,22 +9341,22 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,17 +9395,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>64c039a313c6a63ccc321929</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Luismi Cruz</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,22 +9422,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>64c039a313c6a63ccc321929</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Luismi Cruz</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9449,22 +9449,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -9476,17 +9476,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>66802f240c14414136e408c3</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mella</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,22 +9530,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>66802f240c14414136e408c3</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Mella</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9557,17 +9557,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,22 +9611,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,22 +9665,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9692,22 +9692,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -9719,22 +9719,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,22 +9773,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,22 +9800,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,17 +9854,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9881,17 +9881,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>6a4d1bfcae633549bd0f0744</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9908,17 +9908,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>65b23452ad8bc354111e6659</t>
+          <t>6a4d1bfcae633549bd0f0744</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Adama Boiro</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>65b23452ad8bc354111e6659</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Adama Boiro</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>668011e40ab8ba417f327193</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Dani Sánchez</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,22 +9989,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>668011e40ab8ba417f327193</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Dani Sánchez</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10016,22 +10016,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>66cfa0f08be9a7041ad309f9</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Jon Martín</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>66cfa0f08be9a7041ad309f9</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Jon Martín</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,22 +10070,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10097,22 +10097,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>69ab5b84a3657e03f770ab51</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Manuel Ángel</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10124,22 +10124,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>69ab5b84a3657e03f770ab51</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>Manuel Ángel</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10151,17 +10151,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>6a621c32c6d839058e965748</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>6a621c32c6d839058e965748</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,22 +10232,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10259,22 +10259,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10286,17 +10286,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10313,12 +10313,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,22 +10421,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10448,22 +10448,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5f78e79033215d0412a634a7</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Larrubia</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>602826e66e7e166c3abf1ec0</t>
+          <t>5f78e79033215d0412a634a7</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Miguel Rubio</t>
+          <t>Larrubia</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,22 +10502,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>602826e66e7e166c3abf1ec0</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Miguel Rubio</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -10529,22 +10529,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -10556,17 +10556,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10583,22 +10583,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -10610,22 +10610,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>614743ace216464c91a29186</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Owono</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>614743ace216464c91a29186</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Owono</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,17 +10664,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10691,22 +10691,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,17 +10718,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10745,17 +10745,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>62e0f3d5fbbaa82d719997a2</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Quagliata</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10772,17 +10772,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>62e0f3d5fbbaa82d719997a2</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Quagliata</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,17 +10826,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>630f3695b0b3fe076438ce57</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Yvan Neyou</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10853,17 +10853,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>630d3c68b640225ddc5861c9</t>
+          <t>630f3695b0b3fe076438ce57</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Fran Pérez</t>
+          <t>Yvan Neyou</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10880,17 +10880,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>630d3c68b640225ddc5861c9</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Fran Pérez</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10907,22 +10907,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>64d2b9156167273d0ccc5c4f</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Facundo González</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10934,22 +10934,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d2b9156167273d0ccc5c4f</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Facundo González</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10961,22 +10961,22 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>65871ef403b798703d8c7dd6</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Kambwala</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -10988,17 +10988,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>65871ef403b798703d8c7dd6</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Kambwala</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11015,22 +11015,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -11042,22 +11042,22 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -11069,22 +11069,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -11096,22 +11096,22 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -11123,22 +11123,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -11150,22 +11150,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -11177,22 +11177,22 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -11204,17 +11204,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11231,17 +11231,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -11258,22 +11258,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>66ba79564942001a16eafbb7</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Dani Martín</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -11285,22 +11285,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>66802cdbfd03ab41756b1dc9</t>
+          <t>66ba79564942001a16eafbb7</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Dani Barcia</t>
+          <t>Dani Martín</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -11312,17 +11312,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>66802cdbfd03ab41756b1dc9</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Dani Barcia</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,22 +11420,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -11447,22 +11447,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6865a9767775a433449e9c85</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Noubi</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -11474,22 +11474,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>6865a9767775a433449e9c85</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Noubi</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -11501,12 +11501,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6866a463588465330dd378d1</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Rupérez</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -11528,17 +11528,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>6866a463588465330dd378d1</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>Rupérez</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11555,17 +11555,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11582,22 +11582,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>679d3d34fdee6403d89449fe</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Eddahchouri</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -11609,22 +11609,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>68ebfeadaff4d55004ae1572</t>
+          <t>679d3d34fdee6403d89449fe</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Rafita</t>
+          <t>Eddahchouri</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -11636,22 +11636,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>68ebfeadaff4d55004ae1572</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Rafita</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -11663,12 +11663,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6935bcd342796103f7ed41db</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -11690,22 +11690,22 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>6935bcd342796103f7ed41db</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>695a877f1b6b9103c47320ef</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -11744,22 +11744,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>695a877f1b6b9103c47320ef</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -11771,22 +11771,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4d1b4e2ae0d649eac3a152</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Bernal</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -11798,17 +11798,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>6a4d1b4e2ae0d649eac3a152</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Bernal</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -11825,17 +11825,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -11852,22 +11852,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11879,17 +11879,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5989a4391f9fb9af4ba1b806</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Calero</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -11906,22 +11906,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>5e499be66e12ab0422cc40fb</t>
+          <t>5989a4391f9fb9af4ba1b806</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Unai Vencedor</t>
+          <t>Calero</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,22 +11933,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5e499be66e12ab0422cc40fb</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Unai Vencedor</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -11960,17 +11960,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -11987,22 +11987,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>5a23f0b68a9f96c2332504ab</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Raba</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -12014,22 +12014,22 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>5a23f0b68a9f96c2332504ab</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Raba</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -12041,22 +12041,22 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -12068,17 +12068,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12095,22 +12095,22 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -12122,17 +12122,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -12149,22 +12149,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12176,12 +12176,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12203,22 +12203,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12230,22 +12230,22 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>62b30b7011f4242dbd7252b0</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Mantilla</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12284,22 +12284,22 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>62b30b7011f4242dbd7252b0</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Mantilla</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12311,22 +12311,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>62f826f93355b0168987308d</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12338,22 +12338,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>62f826f93355b0168987308d</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -12365,12 +12365,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -12419,17 +12419,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12446,17 +12446,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12473,17 +12473,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12500,22 +12500,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6461127d49e91a03fb017cda</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Carlos Martín</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -12527,22 +12527,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>6461127d49e91a03fb017cda</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Carlos Martín</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -12554,22 +12554,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -12581,17 +12581,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>62ae4ce2c057ca2d85a004e2</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Hjulmand</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12608,22 +12608,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>655be3da0cc5192b1a75785c</t>
+          <t>62ae4ce2c057ca2d85a004e2</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Xavi Grande</t>
+          <t>Hjulmand</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -12635,22 +12635,22 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>630e1e745328c70716999d1d</t>
+          <t>655be3da0cc5192b1a75785c</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Xavi Grande</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -12662,22 +12662,22 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>631ca92becf9a206fe07abea</t>
+          <t>630e1e745328c70716999d1d</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Kike Salas</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -12689,22 +12689,22 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>63a8cd87bfb65a271f11db10</t>
+          <t>631ca92becf9a206fe07abea</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Carlos Álvarez</t>
+          <t>Kike Salas</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -12716,22 +12716,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>63a8cd87bfb65a271f11db10</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Carlos Álvarez</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -12743,22 +12743,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -12770,22 +12770,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -12797,22 +12797,22 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -12824,12 +12824,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12851,22 +12851,22 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>66802e7e654982413588730f</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Rubén López</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -12878,22 +12878,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>668015b50ab8ba417f327194</t>
+          <t>66802e7e654982413588730f</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Roberto Fernández</t>
+          <t>Rubén López</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -12905,12 +12905,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>66905806702b9203b99a1357</t>
+          <t>668015b50ab8ba417f327194</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Álex Calatrava</t>
+          <t>Roberto Fernández</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -12932,17 +12932,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>66802dd799f9bf415ff4350c</t>
+          <t>66905806702b9203b99a1357</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Diego Villares</t>
+          <t>Álex Calatrava</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -12959,12 +12959,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>66802fd539012a413c5d995f</t>
+          <t>66802dd799f9bf415ff4350c</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Yeremay Hernández</t>
+          <t>Diego Villares</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -12986,22 +12986,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>66f98191043342085bbcc7ce</t>
+          <t>66802fd539012a413c5d995f</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Peio Canales</t>
+          <t>Yeremay Hernández</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13013,22 +13013,22 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>66f98191043342085bbcc7ce</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -13040,17 +13040,17 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6865791adf31913331fecaf7</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Hartman</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -13067,22 +13067,22 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>66c72a0476de1f03e6d2b55a</t>
+          <t>6865791adf31913331fecaf7</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Hartman</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -13094,22 +13094,22 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>688318293777f6041274556c</t>
+          <t>66c72a0476de1f03e6d2b55a</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Hancko</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -13121,22 +13121,22 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6861bef57775a433449e9581</t>
+          <t>688318293777f6041274556c</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Jutglà</t>
+          <t>Hancko</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -13148,22 +13148,22 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>68a21b2501a094041b51ad5b</t>
+          <t>6861bef57775a433449e9581</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Bekhoucha</t>
+          <t>Jutglà</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -13175,22 +13175,22 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>68a21b2501a094041b51ad5b</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Bekhoucha</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -13202,22 +13202,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>68a234d9a9a91a0415a3788b</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Rego</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -13229,22 +13229,22 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>68780dec5c7211044690a3a9</t>
+          <t>68a234d9a9a91a0415a3788b</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Yusi</t>
+          <t>Rego</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -13256,17 +13256,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>68a9fc4cd20bb9540efa8666</t>
+          <t>68780dec5c7211044690a3a9</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Manu Fernández</t>
+          <t>Yusi</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -13283,22 +13283,22 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>68a0bcdf773d7404220761b2</t>
+          <t>68a9fc4cd20bb9540efa8666</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sergio M. </t>
+          <t>Manu Fernández</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -13310,22 +13310,22 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>68b5a03548ead604163e6894</t>
+          <t>68a0bcdf773d7404220761b2</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Eto'o</t>
+          <t xml:space="preserve">Sergio M. </t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -13337,22 +13337,22 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>68adbb77d1d08d1c1f1228ce</t>
+          <t>68b5a03548ead604163e6894</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Hinojo</t>
+          <t>Eto'o</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -13364,22 +13364,22 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>68b5ed22026ac303d72e012e</t>
+          <t>68adbb77d1d08d1c1f1228ce</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Puerta</t>
+          <t>Hinojo</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -13391,17 +13391,17 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>68b486b8882e4a05b2d43111</t>
+          <t>68b5ed22026ac303d72e012e</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Román</t>
+          <t>Puerta</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13418,22 +13418,22 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6960f922cd59040409e50fd9</t>
+          <t>68b486b8882e4a05b2d43111</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Guliashvili</t>
+          <t>Román</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -13445,17 +13445,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6946c6f73a8ebd03f25fc9a3</t>
+          <t>6960f922cd59040409e50fd9</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Nsongo</t>
+          <t>Guliashvili</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -13472,22 +13472,22 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>696e8199368a5803c07f3bc1</t>
+          <t>6946c6f73a8ebd03f25fc9a3</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Eriksson</t>
+          <t>Nsongo</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -13499,22 +13499,22 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>69752256a68dd603be29f508</t>
+          <t>696e8199368a5803c07f3bc1</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Hierro</t>
+          <t>Eriksson</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -13526,22 +13526,22 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>69890d253b0d1b03ea61084c</t>
+          <t>69752256a68dd603be29f508</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Cestero</t>
+          <t>Hierro</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -13553,22 +13553,22 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a358ea99542a303bf19bf7a</t>
+          <t>69890d253b0d1b03ea61084c</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Sangante</t>
+          <t>Cestero</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -13580,22 +13580,22 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>51bcc35c377408301a00000c</t>
+          <t>6a358ea99542a303bf19bf7a</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Vecino</t>
+          <t>Sangante</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -13607,17 +13607,17 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>5d43ec6312ba017aeb3ad5ae</t>
+          <t>51bcc35c377408301a00000c</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Sancet</t>
+          <t>Vecino</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -13634,22 +13634,22 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>5851e8da3defeb5375f2cb30</t>
+          <t>5d43ec6312ba017aeb3ad5ae</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Sancet</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -13661,22 +13661,22 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>5d58321f489a8e5316ca89d6</t>
+          <t>5851e8da3defeb5375f2cb30</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Iker Losada</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -13688,17 +13688,17 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>59c2d829bd61e7f10c49a9b6</t>
+          <t>5d58321f489a8e5316ca89d6</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Edu Expósito</t>
+          <t>Iker Losada</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -13715,22 +13715,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>5da39ad5b8e82e5c69ab75f9</t>
+          <t>59c2d829bd61e7f10c49a9b6</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Valles</t>
+          <t>Edu Expósito</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -13742,12 +13742,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>5a81f13ce3c1953064f782e0</t>
+          <t>5da39ad5b8e82e5c69ab75f9</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Junior Firpo</t>
+          <t>Valles</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -13769,17 +13769,17 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>5efa4e35ee5a640417710119</t>
+          <t>5a81f13ce3c1953064f782e0</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Jon Pacheco</t>
+          <t>Junior Firpo</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -13796,22 +13796,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5efa4e35ee5a640417710119</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Jon Pacheco</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -13823,22 +13823,22 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>60d73641b7fb6703d3e21ba8</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Olasagasti</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>5bd4d4dd2549d75a2c65508e</t>
+          <t>60d73641b7fb6703d3e21ba8</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Julián Álvarez</t>
+          <t>Olasagasti</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -13877,22 +13877,22 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>60e72704dfb903607d1f7d87</t>
+          <t>5bd4d4dd2549d75a2c65508e</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Dituro</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -13904,22 +13904,22 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>61228f14bee4ec08574d99bf</t>
+          <t>60e72704dfb903607d1f7d87</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Haitam</t>
+          <t>Dituro</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -13931,22 +13931,22 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>61228f14bee4ec08574d99bf</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Haitam</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -13958,17 +13958,17 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>61bd0e030d81623e3a2b0f28</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Rubén Sánchez</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -13985,17 +13985,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>5f80c8e8a9c2e74fca8282e9</t>
+          <t>61bd0e030d81623e3a2b0f28</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Ruggeri</t>
+          <t>Rubén Sánchez</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -14012,22 +14012,22 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>61dcacebb6d6540425b75dce</t>
+          <t>5f80c8e8a9c2e74fca8282e9</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Ruggeri</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -14039,22 +14039,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>62b3132cb2a1132d77c95799</t>
+          <t>61dcacebb6d6540425b75dce</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Arana</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -14066,22 +14066,22 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>61fef82a9b83fa2769ffc896</t>
+          <t>62b3132cb2a1132d77c95799</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Iker Benito</t>
+          <t>Arana</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -20619,6 +20619,33 @@
         </is>
       </c>
       <c r="E748" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>6a7eecdb4cdb8203d4a7ba99</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Yeboah</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d1</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>defensa</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E761"/>
+  <dimension ref="A1:E762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4130,12 +4130,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5f36db010b759303ff680104</t>
+          <t>6060aa1a7a64b003da0efc7d</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iván Martín </t>
+          <t>Arnau Martínez</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4157,22 +4157,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6060aa1a7a64b003da0efc7d</t>
+          <t>61112696dfb903607d1f7e45</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Arnau Martínez</t>
+          <t>Haissem Hassan</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4184,17 +4184,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>61112696dfb903607d1f7e45</t>
+          <t>63092ba34c71a52ba37b8165</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Haissem Hassan</t>
+          <t>Joel Roca</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4211,12 +4211,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>63092ba34c71a52ba37b8165</t>
+          <t>63c6945172c559051c25d9fa</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Joel Roca</t>
+          <t>Tsygankov</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4238,12 +4238,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>63c6945172c559051c25d9fa</t>
+          <t>57b94cfee3480bb6049eb14b</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tsygankov</t>
+          <t>Fran Beltrán</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4265,22 +4265,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>57b94cfee3480bb6049eb14b</t>
+          <t>587413fa39af105c4b075f23</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Fran Beltrán</t>
+          <t>Toni Lato</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4292,12 +4292,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>587413fa39af105c4b075f23</t>
+          <t>5f5a930b58df197b1823bfe7</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Toni Lato</t>
+          <t>Samú Costa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4319,17 +4319,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5f5a930b58df197b1823bfe7</t>
+          <t>64d803c883596124e55c064f</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Samú Costa</t>
+          <t>Unai Gómez</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4346,22 +4346,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>64d803c883596124e55c064f</t>
+          <t>6689c562e0157a03f87fbf0e</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Unai Gómez</t>
+          <t>Morey</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4373,22 +4373,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6689c562e0157a03f87fbf0e</t>
+          <t>67575e411a57f003d0b21843</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Morey</t>
+          <t>Coba da Costa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4400,22 +4400,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>67575e411a57f003d0b21843</t>
+          <t>51c1fdeac7694f5f66000051</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Coba da Costa</t>
+          <t>David López</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4427,17 +4427,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>51c1fdeac7694f5f66000051</t>
+          <t>5b59e02c66831ded570d44f4</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>David López</t>
+          <t>Valjent</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4454,12 +4454,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5b59e02c66831ded570d44f4</t>
+          <t>5b786a5d95ea0b2b07e4e66e</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Valjent</t>
+          <t>Morlanes</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4481,22 +4481,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5b786a5d95ea0b2b07e4e66e</t>
+          <t>5c0416954c47343bad939db8</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Morlanes</t>
+          <t>Valery Fernández</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d4</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4508,22 +4508,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5c0416954c47343bad939db8</t>
+          <t>62e39ff011f4242dbd725314</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Valery Fernández</t>
+          <t>Pablo Torre</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d4</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4535,12 +4535,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>62e39ff011f4242dbd725314</t>
+          <t>66b352197fc6ff03fb06fb13</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Pablo Torre</t>
+          <t>D. López</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4562,17 +4562,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>66b352197fc6ff03fb06fb13</t>
+          <t>67310caf29e197051e04f422</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>D. López</t>
+          <t>Ferrán Ruiz</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4589,17 +4589,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>67310caf29e197051e04f422</t>
+          <t>6695372399e2e504052cbbae</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ferrán Ruiz</t>
+          <t>Rahim</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6695372399e2e504052cbbae</t>
+          <t>65b12f7b992bcf53bfe2fc31</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rahim</t>
+          <t>Moldovan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4643,17 +4643,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>65b12f7b992bcf53bfe2fc31</t>
+          <t>66d61f2aed648e0b1ac63f1a</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Moldovan</t>
+          <t>Bergström</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4670,22 +4670,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>66d61f2aed648e0b1ac63f1a</t>
+          <t>5d5570f69bb8253fe4f452d6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Bergström</t>
+          <t>Ahijado</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4697,12 +4697,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5d5570f69bb8253fe4f452d6</t>
+          <t>66d81870433f040b000aa40c</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ahijado</t>
+          <t>Luka Ilic</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4724,22 +4724,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>66d81870433f040b000aa40c</t>
+          <t>57c73a7a803dc6bd7be02981</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Luka Ilic</t>
+          <t>Pau López</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4751,22 +4751,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>57c73a7a803dc6bd7be02981</t>
+          <t>56d314416116845b08e61bed</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pau López</t>
+          <t>Rashford</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51d19d0f78d9b6850500003e</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4778,22 +4778,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>56d314416116845b08e61bed</t>
+          <t>68951eec4e36d6040c695ed8</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Rashford</t>
+          <t>Santamaria</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>51d19d0f78d9b6850500003e</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4805,17 +4805,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>68951eec4e36d6040c695ed8</t>
+          <t>62c5da44fbbaa82d71999775</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Santamaria</t>
+          <t>Witsel</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4832,22 +4832,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>62c5da44fbbaa82d71999775</t>
+          <t>65a2f7b8b94b7303dce5ccac</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Witsel</t>
+          <t>Marco Esteban</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4859,12 +4859,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>65a2f7b8b94b7303dce5ccac</t>
+          <t>689fb8cb06428a0452dc8034</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Marco Esteban</t>
+          <t>Omar Falah</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4886,12 +4886,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>689fb8cb06428a0452dc8034</t>
+          <t>5b6cc28068b47b496279f860</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Omar Falah</t>
+          <t>Dendoncker</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4913,22 +4913,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5b6cc28068b47b496279f860</t>
+          <t>53ac3e6c1933f2de6f0003fc</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Dendoncker</t>
+          <t>Álex Moreno</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4940,22 +4940,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>53ac3e6c1933f2de6f0003fc</t>
+          <t>5f43f5bf0b759303ff680853</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Álex Moreno</t>
+          <t>Ramazani</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>57a1235f445c20291844c133</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4967,17 +4967,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5f43f5bf0b759303ff680853</t>
+          <t>68b0df5c11ed3a059c4912a3</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ramazani</t>
+          <t>Virgili</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>57a1235f445c20291844c133</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4994,22 +4994,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>68b0df5c11ed3a059c4912a3</t>
+          <t>68b37c6461185205e8c364db</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Virgili</t>
+          <t>Ounahi</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5021,12 +5021,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>68b37c6461185205e8c364db</t>
+          <t>68b59fba05c30a03fb36d382</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ounahi</t>
+          <t>Vanat</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5048,12 +5048,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>68b59fba05c30a03fb36d382</t>
+          <t>5c323b46bef16503ec960e1c</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Vanat</t>
+          <t>Bryan Gil</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5075,12 +5075,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5c323b46bef16503ec960e1c</t>
+          <t>68f3b8b9dd3614500b418a49</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Bryan Gil</t>
+          <t>Lass</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,22 +5102,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>68f3b8b9dd3614500b418a49</t>
+          <t>52024320737b88c937000019</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Lass</t>
+          <t xml:space="preserve"> João Cancelo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>50819964ffd960540d0014ed</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5129,22 +5129,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>52024320737b88c937000019</t>
+          <t>696a39e9af58fa040efb5372</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> João Cancelo</t>
+          <t>Kalumba</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>50819964ffd960540d0014ed</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5156,17 +5156,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>696a39e9af58fa040efb5372</t>
+          <t>66a3d3797fc6ff03fb06fadf</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Kalumba</t>
+          <t>Echeverri</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51d197b30719708a05000037</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5183,22 +5183,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fadf</t>
+          <t>6977e776fee4e803e0e8bed5</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Echeverri</t>
+          <t>Arango</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>51d197b30719708a05000037</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5210,22 +5210,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6977e776fee4e803e0e8bed5</t>
+          <t>675366baf7be6b107f01b952</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Arango</t>
+          <t>Fer López</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>57a12447445c20291844c142</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5237,17 +5237,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>675366baf7be6b107f01b952</t>
+          <t>68a0ebed3a1cb503e4684dca</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fer López</t>
+          <t>Jan  Salas</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>57a12447445c20291844c142</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5264,17 +5264,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>68a0ebed3a1cb503e4684dca</t>
+          <t>6a04f3f3f8f6ef041e55261c</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jan  Salas</t>
+          <t>Damián</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5291,22 +5291,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6a04f3f3f8f6ef041e55261c</t>
+          <t>6a04f502781278043f2eda16</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Damián</t>
+          <t>Orejuela</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5318,22 +5318,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6a04f502781278043f2eda16</t>
+          <t>61844713165d9f09c3eecd07</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Orejuela</t>
+          <t>Artero</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5345,17 +5345,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>61844713165d9f09c3eecd07</t>
+          <t>61c3b14eb4f96c073bf94ce7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Artero</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5372,17 +5372,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>61c3b14eb4f96c073bf94ce7</t>
+          <t>674b7a94c9efc910567f19b6</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5399,22 +5399,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>674b7a94c9efc910567f19b6</t>
+          <t>66cfa272b46ff704160ad00e</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Adrián Pica</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5426,22 +5426,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>66cfa272b46ff704160ad00e</t>
+          <t>686feb558bef76044eadf791</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Adrián Pica</t>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5453,22 +5453,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>686feb558bef76044eadf791</t>
+          <t>6683c6e90ab8ba417f3276b6</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Guilherme</t>
+          <t>Unai Ropero</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5480,17 +5480,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6683c6e90ab8ba417f3276b6</t>
+          <t>67597e6b317cba0418bce297</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Unai Ropero</t>
+          <t>Dani Luna</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>67597e6b317cba0418bce297</t>
+          <t>66d39b3d58f2de32117efa18</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dani Luna</t>
+          <t>Domenech</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5534,17 +5534,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>66d39b3d58f2de32117efa18</t>
+          <t>57b94a3c7ce1feed040b24e3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Domenech</t>
+          <t>Jacobo González</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5561,12 +5561,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>57b94a3c7ce1feed040b24e3</t>
+          <t>64b1c502c35fcb3cfd3ed505</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Jacobo González</t>
+          <t>Youness</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5588,12 +5588,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>64b1c502c35fcb3cfd3ed505</t>
+          <t>6865adefd4d22b330615f7ca</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Youness</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6865adefd4d22b330615f7ca</t>
+          <t>60e6e2841a405a604ca8c2d7</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Luengo</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5642,12 +5642,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>60e6e2841a405a604ca8c2d7</t>
+          <t>669274f3ce303803d6f77330</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Luengo</t>
+          <t>Paraschiv</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>669274f3ce303803d6f77330</t>
+          <t>6584aa689b9f5d700573fd05</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Paraschiv</t>
+          <t>Cardero</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5696,17 +5696,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>6584aa689b9f5d700573fd05</t>
+          <t>697be226df6332040670c6c1</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Cardero</t>
+          <t>Izan González</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5723,12 +5723,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>697be226df6332040670c6c1</t>
+          <t>6a35c168152d0603c64c029a</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Izan González</t>
+          <t>Pyshchur</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6a35c168152d0603c64c029a</t>
+          <t>68a9e8aab479f05404a946c8</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Pyshchur</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5777,12 +5777,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>68a9e8aab479f05404a946c8</t>
+          <t>6713fdc9a1b917176a03238a</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Min-su Kim</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5804,12 +5804,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6713fdc9a1b917176a03238a</t>
+          <t>66c9b0acf119260402e26288</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Min-su Kim</t>
+          <t>Asprilla</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>66c9b0acf119260402e26288</t>
+          <t>65f5fc5000ffc34f05f1cb1f</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Asprilla</t>
+          <t>Jastin</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>65f5fc5000ffc34f05f1cb1f</t>
+          <t>65ad994d76a3e353be71263f</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Jastin</t>
+          <t>Antal Yaakobishvili</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -5885,17 +5885,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>65ad994d76a3e353be71263f</t>
+          <t>63053ef3f14610075abd00f0</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Antal Yaakobishvili</t>
+          <t>Özkacar</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5912,22 +5912,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>63053ef3f14610075abd00f0</t>
+          <t>6861890daedcdd33075dd01d</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Özkacar</t>
+          <t>Adri Fuentes</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5939,17 +5939,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6861890daedcdd33075dd01d</t>
+          <t>6795426c91d9bd03c793c426</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Adri Fuentes</t>
+          <t>Diego Gómez</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5966,22 +5966,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6795426c91d9bd03c793c426</t>
+          <t>63bb149eba53bb03cdfc2e9f</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Diego Gómez</t>
+          <t>Cabanzón</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5993,17 +5993,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>63bb149eba53bb03cdfc2e9f</t>
+          <t>64fb90eebc6e0003e0366f4f</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Cabanzón</t>
+          <t>Roca</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6020,22 +6020,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>64fb90eebc6e0003e0366f4f</t>
+          <t>521b69bf359d42743700007f</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Roca</t>
+          <t>Carlos Fernández</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6047,22 +6047,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>521b69bf359d42743700007f</t>
+          <t>6305da4d46d783071421441c</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Carlos Fernández</t>
+          <t>Arnau Tenas</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -6074,22 +6074,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6305da4d46d783071421441c</t>
+          <t>5cfc2be98721525ead8d94b1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Arnau Tenas</t>
+          <t>Gragera</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5cfc2be98721525ead8d94b1</t>
+          <t>64be9241b6533c3d2112572f</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Gragera</t>
+          <t>Petxarroman</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -6128,22 +6128,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>64be9241b6533c3d2112572f</t>
+          <t>65f7126c17c8f74f39434408</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Petxarroman</t>
+          <t>Damián Rodríguez</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -6155,22 +6155,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>65f7126c17c8f74f39434408</t>
+          <t>61da0a69b6d6540425b749e4</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Damián Rodríguez</t>
+          <t>Bouldini</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6182,22 +6182,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>61da0a69b6d6540425b749e4</t>
+          <t>5590e843b804493642903daa</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Bouldini</t>
+          <t>Vesga</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6209,22 +6209,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5590e843b804493642903daa</t>
+          <t>690f6102072c5e03d67ac3e5</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vesga</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6236,22 +6236,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>690f6102072c5e03d67ac3e5</t>
+          <t>696184347cc74203effd6ff6</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Mestanza</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6263,17 +6263,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>696184347cc74203effd6ff6</t>
+          <t>66a3c8069e452303b3fc0b22</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mestanza</t>
+          <t>Albarracín</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6290,17 +6290,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>66a3c8069e452303b3fc0b22</t>
+          <t>69ab5b4653966303fb66b781</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Albarracín</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6317,12 +6317,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>69ab5b4653966303fb66b781</t>
+          <t>68251aa7172c6403d639c211</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -6344,17 +6344,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>68251aa7172c6403d639c211</t>
+          <t>62c03520b2a1132d77c957bd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Camara</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6371,22 +6371,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>62c03520b2a1132d77c957bd</t>
+          <t>51b9d964e401a15f2c000174</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Camara</t>
+          <t>Ter Stegen</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -6398,22 +6398,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>51b9d964e401a15f2c000174</t>
+          <t>57bb7cea45e6bed0520a420a</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ter Stegen</t>
+          <t>Rafa Mir</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6425,22 +6425,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>57bb7cea45e6bed0520a420a</t>
+          <t>57b5c2d87e2ec2df1922966f</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Rafa Mir</t>
+          <t>Elgezabal</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6452,22 +6452,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>57b5c2d87e2ec2df1922966f</t>
+          <t>6757ff71d2717703ca746142</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Elgezabal</t>
+          <t>Cabanes</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6479,22 +6479,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6757ff71d2717703ca746142</t>
+          <t>5895c85a1b85076162dab6ac</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Cabanes</t>
+          <t>Sow</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6506,17 +6506,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5895c85a1b85076162dab6ac</t>
+          <t>68618ca465100f3368c8f658</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Sow</t>
+          <t>Jairo Noriega</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6533,22 +6533,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>68618ca465100f3368c8f658</t>
+          <t>62b3135fa81ab52db02ea690</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jairo Noriega</t>
+          <t>Forés</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6560,22 +6560,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>62b3135fa81ab52db02ea690</t>
+          <t>66a3d3797fc6ff03fb06fae3</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Forés</t>
+          <t>Mastantuono</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6587,22 +6587,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fae3</t>
+          <t>62f12359f1b09a7dd27ba96c</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mastantuono</t>
+          <t>Juanlu</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -6614,22 +6614,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>62f12359f1b09a7dd27ba96c</t>
+          <t>5b6e2823a2736a321a4d1003</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Juanlu</t>
+          <t>Almada</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -6641,17 +6641,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5b6e2823a2736a321a4d1003</t>
+          <t>54026d04e8a4c9292a0001db</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Almada</t>
+          <t>Joan Jordan</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6668,22 +6668,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>54026d04e8a4c9292a0001db</t>
+          <t>60980a25b7ad5b0920afde9e</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Joan Jordan</t>
+          <t>Carlos Domínguez</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6695,22 +6695,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>60980a25b7ad5b0920afde9e</t>
+          <t>6990b007612d5404638c8cfe</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Carlos Domínguez</t>
+          <t>Hugo López</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6722,22 +6722,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>6990b007612d5404638c8cfe</t>
+          <t>5d9a575c370ecd5c7486de5c</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Hugo López</t>
+          <t>Ronald Araújo</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6749,17 +6749,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5d9a575c370ecd5c7486de5c</t>
+          <t>577743d027ae4bd9135ae3d8</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ronald Araújo</t>
+          <t>Nahuel Molina</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6776,17 +6776,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>577743d027ae4bd9135ae3d8</t>
+          <t>5f3d059a3e2aea03b6fe0456</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Nahuel Molina</t>
+          <t>Pep Chavarría</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5f3d059a3e2aea03b6fe0456</t>
+          <t>66b489b3c34e5603e02c025a</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Pep Chavarría</t>
+          <t>Nobel Mendy</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6830,17 +6830,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>66b489b3c34e5603e02c025a</t>
+          <t>66a3d3797fc6ff03fb06fad9</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Nobel Mendy</t>
+          <t>Gattoni</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6857,17 +6857,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06fad9</t>
+          <t>5d547cd98517403fd8fab746</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Gattoni</t>
+          <t>Maras</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6884,22 +6884,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5d547cd98517403fd8fab746</t>
+          <t>61fef82a9b83fa2769ffc896</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Maras</t>
+          <t>Iker Benito</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6911,22 +6911,22 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>61fef82a9b83fa2769ffc896</t>
+          <t>5a3578e0feceda7e2716a6c7</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Iker Benito</t>
+          <t xml:space="preserve">Ferrán Torres </t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6938,22 +6938,22 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5a3578e0feceda7e2716a6c7</t>
+          <t>5eef6e9c4fa17f5218f7d433</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrán Torres </t>
+          <t>Javier López</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6965,22 +6965,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5eef6e9c4fa17f5218f7d433</t>
+          <t>67804e6ab11a5e759942b02f</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Javier López</t>
+          <t>Kervin Arriaga</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6992,22 +6992,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>67804e6ab11a5e759942b02f</t>
+          <t>66998d319e452303b3fc0ae8</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kervin Arriaga</t>
+          <t>Moussa Diarra</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -7019,17 +7019,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>66998d319e452303b3fc0ae8</t>
+          <t>5f80c8e8a9c2e74fca8282e9</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Moussa Diarra</t>
+          <t>Ruggeri</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7046,22 +7046,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5f80c8e8a9c2e74fca8282e9</t>
+          <t>6876c12606428a0452dc7fa6</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ruggeri</t>
+          <t>Áron Yaakobishvili</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -17819,22 +17819,22 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6876c12606428a0452dc7fa6</t>
+          <t>68c5f5d55bd165052e271611</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Áron Yaakobishvili</t>
+          <t>Ángel Pérez</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -17846,22 +17846,22 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>68c5f5d55bd165052e271611</t>
+          <t>69810c427602e303cbed6a3e</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Ángel Pérez</t>
+          <t>Obed Vargas</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -17873,17 +17873,17 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>69810c427602e303cbed6a3e</t>
+          <t>6a35ba801636ff03e132961e</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Obed Vargas</t>
+          <t>Gijselhart</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -17900,22 +17900,22 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a35ba801636ff03e132961e</t>
+          <t>5f32e17633a68903ecffbd1f</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Gijselhart</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -17927,17 +17927,17 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>5f32e17633a68903ecffbd1f</t>
+          <t>5f4e59209209ce03d8236b09</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Fran García</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -17954,17 +17954,17 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>5f4e59209209ce03d8236b09</t>
+          <t>5f6fae0738429649dbf263d6</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Fran García</t>
+          <t>Boyomo</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -17981,22 +17981,22 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>5f6fae0738429649dbf263d6</t>
+          <t>5f70efc9b69ba04a25453f2c</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Boyomo</t>
+          <t>Jofre</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -18008,17 +18008,17 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>5f70efc9b69ba04a25453f2c</t>
+          <t>602833759c7d2b6c2de127f5</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Ilaix Moriba</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -18035,17 +18035,17 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>602833759c7d2b6c2de127f5</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Ilaix Moriba</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -18062,22 +18062,22 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -18089,22 +18089,22 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>61228f14bee4ec08574d99bf</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Haitam</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -18116,22 +18116,22 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>61228f14bee4ec08574d99bf</t>
+          <t>614cc15d3916210732959cc3</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Haitam</t>
+          <t>Robert Navarro</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -18143,22 +18143,22 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>614cc15d3916210732959cc3</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Robert Navarro</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -18170,17 +18170,17 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>62ab326f996d511b380d0d7a</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Álex Pastor</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -18197,22 +18197,22 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>62ab326f996d511b380d0d7a</t>
+          <t>62ab326f996d511b380d0d7f</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Álex Pastor</t>
+          <t>Marc Aguado</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -18224,17 +18224,17 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>62ab326f996d511b380d0d7f</t>
+          <t>63fd2d48e13c195af1f7112f</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Marc Aguado</t>
+          <t>Terrats</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -18251,22 +18251,22 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>63fd2d48e13c195af1f7112f</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Terrats</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -18278,22 +18278,22 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>657cccb79a154503e6fa2fa8</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Rodri Mendoza</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -18305,17 +18305,17 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>657cccb79a154503e6fa2fa8</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Rodri Mendoza</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -18332,22 +18332,22 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -18359,22 +18359,22 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>6643e149974fb0361c6a6e9b</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Mario Martín</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -18386,22 +18386,22 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6643e149974fb0361c6a6e9b</t>
+          <t>668020900ab8ba417f327199</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Mario Martín</t>
+          <t>Vertrouwd</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -18413,22 +18413,22 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>668020900ab8ba417f327199</t>
+          <t>66ade7b9702b9203b99a16eb</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Vertrouwd</t>
+          <t>Luka Sucic</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -18440,17 +18440,17 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>66ade7b9702b9203b99a16eb</t>
+          <t>66b69fb39e452303b3fc0b77</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Luka Sucic</t>
+          <t>Dani Olmo</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -18467,17 +18467,17 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>66b69fb39e452303b3fc0b77</t>
+          <t>66c11ee4b5741f1a24b14824</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Dani Olmo</t>
+          <t>Otorbi</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -18494,22 +18494,22 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>66c11ee4b5741f1a24b14824</t>
+          <t>66c7c242f119260402e25f8f</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Otorbi</t>
+          <t>Logan Costa</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -18521,22 +18521,22 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>66c7c242f119260402e25f8f</t>
+          <t>679542c43f683203b32f39d0</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Logan Costa</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -18548,22 +18548,22 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>679542c43f683203b32f39d0</t>
+          <t>68a234d9a9a91a0415a3788b</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Rego</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -18575,22 +18575,22 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>68a234d9a9a91a0415a3788b</t>
+          <t>68adbb77d1d08d1c1f1228ce</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Rego</t>
+          <t>Hinojo</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -18602,17 +18602,17 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>68adbb77d1d08d1c1f1228ce</t>
+          <t>697e90b3ff715b03c5df8278</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Hinojo</t>
+          <t>Koski</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -18629,17 +18629,17 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>697e90b3ff715b03c5df8278</t>
+          <t>521465c2dbf8b74f020000b8</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Koski</t>
+          <t>Yuri</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -18656,22 +18656,22 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>521465c2dbf8b74f020000b8</t>
+          <t>578a39f79572c04c06eb3daf</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Yuri</t>
+          <t>Comesaña</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -18683,17 +18683,17 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>578a39f79572c04c06eb3daf</t>
+          <t>5b34a882447188471d9677fc</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Comesaña</t>
+          <t>Óscar Valentín</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -18710,12 +18710,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>5b34a882447188471d9677fc</t>
+          <t>5cdf2e37121b5404171c6fad</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Óscar Valentín</t>
+          <t>Pedro Díaz</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -18737,22 +18737,22 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>5cdf2e37121b5404171c6fad</t>
+          <t>5d51a593fbc39d3fa25f7eb0</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Pedro Díaz</t>
+          <t>Sergio Gómez</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -18764,17 +18764,17 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>5d51a593fbc39d3fa25f7eb0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Sergio Gómez</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -18791,22 +18791,22 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>5f7c91e784180b4fc44cd0ee</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Raphinha</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -18818,22 +18818,22 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>5f7c91e784180b4fc44cd0ee</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Raphinha</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -18845,17 +18845,17 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>61c0ff53122e933e3d15a643</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Iranzo</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -18872,17 +18872,17 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>61c0ff53122e933e3d15a643</t>
+          <t>665368343bd1d1040fffb355</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Iranzo</t>
+          <t>Yoel Lago</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -18899,22 +18899,22 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>665368343bd1d1040fffb355</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Yoel Lago</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -18926,22 +18926,22 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -18953,22 +18953,22 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>66802dd799f9bf415ff4350c</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Diego Villares</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -18980,17 +18980,17 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>66802dd799f9bf415ff4350c</t>
+          <t>66bb83844942001a16eafbb8</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Diego Villares</t>
+          <t>Javi Hernández</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -19007,22 +19007,22 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>66bb83844942001a16eafbb8</t>
+          <t>66bfad063bdc581a0f65ead1</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Javi Hernández</t>
+          <t>Javi Rodríguez</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
@@ -19034,22 +19034,22 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>66bfad063bdc581a0f65ead1</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Javi Rodríguez</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -19061,22 +19061,22 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -19088,22 +19088,22 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>680529fb802b9e0450bb226a</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>Eyong</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -19115,17 +19115,17 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>680529fb802b9e0450bb226a</t>
+          <t>6861cd7eca97b13338e6c16d</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Eyong</t>
+          <t>Marcos Fernández</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -19142,22 +19142,22 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6861cd7eca97b13338e6c16d</t>
+          <t>68c5f54d83815b05817ba3bd</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Marcos Fernández</t>
+          <t>Ángel Recio</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
@@ -19169,22 +19169,22 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>68c5f54d83815b05817ba3bd</t>
+          <t>6977e9c440eaa603f8aa3e87</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Ángel Recio</t>
+          <t>Cepeda</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
@@ -19196,22 +19196,22 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6977e9c440eaa603f8aa3e87</t>
+          <t>51cb698301d64ad4700000bc</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Cepeda</t>
+          <t>Szczesny</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -19223,22 +19223,22 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>51cb698301d64ad4700000bc</t>
+          <t>596fc4490ef6710375cfbc85</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Szczesny</t>
+          <t>Javi Muñoz</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
@@ -19250,17 +19250,17 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>596fc4490ef6710375cfbc85</t>
+          <t>5a639998e2a0fd3424128d06</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Javi Muñoz</t>
+          <t>Brahim Díaz</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -19277,12 +19277,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>5a639998e2a0fd3424128d06</t>
+          <t>5b33408c744d2a591d3e566e</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Brahim Díaz</t>
+          <t>Vinícius</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19292,7 +19292,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -19304,22 +19304,22 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>5b33408c744d2a591d3e566e</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Vinícius</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -19331,12 +19331,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>607325f27b19b30c4fb34081</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Urko González</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -19358,22 +19358,22 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>607325f27b19b30c4fb34081</t>
+          <t>610abc4f328e98602847897f</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Urko González</t>
+          <t>Ratiu</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
@@ -19385,22 +19385,22 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>610abc4f328e98602847897f</t>
+          <t>612bc20d8f3edc07a4a81def</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Ratiu</t>
+          <t>Gavi</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
@@ -19412,17 +19412,17 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>612bc20d8f3edc07a4a81def</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Gavi</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -19439,17 +19439,17 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>62c3721bc057ca2d85a00512</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Giuliano Simeone</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -19466,22 +19466,22 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>62c3721bc057ca2d85a00512</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Giuliano Simeone</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
@@ -19493,22 +19493,22 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>643c697b471fc403f43359d6</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Javi Guerra</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -19520,22 +19520,22 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>643c697b471fc403f43359d6</t>
+          <t>644d90d4479a44042784eb9f</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Javi Guerra</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
@@ -19547,22 +19547,22 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>644d90d4479a44042784eb9f</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -19574,22 +19574,22 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -19601,22 +19601,22 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>66c72a0476de1f03e6d2b55a</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -19628,17 +19628,17 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>66c72a0476de1f03e6d2b55a</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -19655,17 +19655,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>682920fc77ba5003ca4869ce</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Deossa</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -19682,17 +19682,17 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>682920fc77ba5003ca4869ce</t>
+          <t>6866a56fca97b13338e6cd0b</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Deossa</t>
+          <t>Goti</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -19709,22 +19709,22 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6866a56fca97b13338e6cd0b</t>
+          <t>687aa8cb00ed89046c1f7e6e</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Goti</t>
+          <t>Gonzalo Petit</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
@@ -19736,22 +19736,22 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>687aa8cb00ed89046c1f7e6e</t>
+          <t>68b5ed22026ac303d72e012e</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Gonzalo Petit</t>
+          <t>Puerta</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -19763,22 +19763,22 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>68b5ed22026ac303d72e012e</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Puerta</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -19790,22 +19790,22 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>69a5ddd7cd2bdb03fcc07f8a</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Thiago Pitarch</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -19817,17 +19817,17 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>69a5ddd7cd2bdb03fcc07f8a</t>
+          <t>5c3a22fd2eb0f60409307e95</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Thiago Pitarch</t>
+          <t>Kang-in Lee</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -19844,22 +19844,22 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>5c3a22fd2eb0f60409307e95</t>
+          <t>5f79bdeb02358a040ca3ed7c</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Kang-in Lee</t>
+          <t>Miguel Rodríguez</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -19871,22 +19871,22 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>5f79bdeb02358a040ca3ed7c</t>
+          <t>62d7299dfbbaa82d7199978f</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Miguel Rodríguez</t>
+          <t>Dubasin</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -19898,22 +19898,22 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>62d7299dfbbaa82d7199978f</t>
+          <t>69a37b194f0be803ae3e49e7</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Dubasin</t>
+          <t>Julio Díaz</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -19925,22 +19925,22 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>69a37b194f0be803ae3e49e7</t>
+          <t>5e2c95e681b4f252c1de887c</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Julio Díaz</t>
+          <t>Fer Niño</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -19952,17 +19952,17 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>5e2c95e681b4f252c1de887c</t>
+          <t>6a6b5de91c339705c4749fdc</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Fer Niño</t>
+          <t>Zabiri</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -19979,22 +19979,22 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a6b5de91c339705c4749fdc</t>
+          <t>55ad2871332f681702ac1350</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Zabiri</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
@@ -20006,12 +20006,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>55ad2871332f681702ac1350</t>
+          <t>6a6f41d86767b305a9938268</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Musuayi</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
@@ -20033,22 +20033,22 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a6f41d86767b305a9938268</t>
+          <t>51d14b1478d9b68505000018</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Musuayi</t>
+          <t>Abdoulaye Faye</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -20060,22 +20060,22 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>51d14b1478d9b68505000018</t>
+          <t>5774b5ed27ae4bd9135ae2ec</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Abdoulaye Faye</t>
+          <t>Gulácsi</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
@@ -20087,22 +20087,22 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>5774b5ed27ae4bd9135ae2ec</t>
+          <t>64f094c1e6bb420409b10378</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Gulácsi</t>
+          <t>Sazonov</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -20114,22 +20114,22 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>64f094c1e6bb420409b10378</t>
+          <t>6a7363a8db5fee059d38f030</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Sazonov</t>
+          <t>Macià</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
@@ -20141,22 +20141,22 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a7363a8db5fee059d38f030</t>
+          <t>698127b6163f5f03fb3b4153</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Macià</t>
+          <t>Pedro Felipe</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
@@ -20168,22 +20168,22 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>698127b6163f5f03fb3b4153</t>
+          <t>69d1843021ab3804095dc5d2</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Pedro Felipe</t>
+          <t>Morcillo</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
@@ -20195,22 +20195,22 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>69d1843021ab3804095dc5d2</t>
+          <t>67f44ff6e3c6fe0422013801</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Morcillo</t>
+          <t>Diomande</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
@@ -20222,22 +20222,22 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>67f44ff6e3c6fe0422013801</t>
+          <t>6a73c52ac6d839058e96579c</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Diomande</t>
+          <t>Hugo González</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
@@ -20249,22 +20249,22 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a73c52ac6d839058e96579c</t>
+          <t>66a3cb8550535003acfadaa1</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Hugo González</t>
+          <t>Valentini</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -20276,17 +20276,17 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>66a3cb8550535003acfadaa1</t>
+          <t>58637d1af4f101eb55c2efda</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Valentini</t>
+          <t>Angeliño</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -20303,22 +20303,22 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>58637d1af4f101eb55c2efda</t>
+          <t>64f1b064dd41fe03d19c02e0</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Angeliño</t>
+          <t>Bayindir</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
@@ -20330,22 +20330,22 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>64f1b064dd41fe03d19c02e0</t>
+          <t>593aca21c298fc0e06f5a8c4</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Bayindir</t>
+          <t>Mangala</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -20357,22 +20357,22 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>593aca21c298fc0e06f5a8c4</t>
+          <t>5d63a31035a3437797dab04d</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Mangala</t>
+          <t>Kumbulla</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -20384,22 +20384,22 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>5d63a31035a3437797dab04d</t>
+          <t>63b1dee65cda2d03f841722e</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Kumbulla</t>
+          <t>Buonanotte</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -20411,17 +20411,17 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>63b1dee65cda2d03f841722e</t>
+          <t>6a7817791d7836057d9e19a6</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Buonanotte</t>
+          <t>Guillén</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -20438,12 +20438,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a7817791d7836057d9e19a6</t>
+          <t>6a781745af66ad05af1c1054</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Guillén</t>
+          <t>Miguel Sierra</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -20465,12 +20465,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a781745af66ad05af1c1054</t>
+          <t>6a7b13cb1c484e03ecee7773</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Miguel Sierra</t>
+          <t>Ure</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -20492,17 +20492,17 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a7b13cb1c484e03ecee7773</t>
+          <t>66a38f96a3a4d703c605ac2e</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Ure</t>
+          <t>Tsitaishvili</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -20519,22 +20519,22 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>66a38f96a3a4d703c605ac2e</t>
+          <t>53b108ea1933f2de6f000907</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Tsitaishvili</t>
+          <t>Diego Rico</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -20546,17 +20546,17 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>53b108ea1933f2de6f000907</t>
+          <t>51d70ed7a7178a7654000012</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Diego Rico</t>
+          <t>Mojica</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -20573,12 +20573,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>51d70ed7a7178a7654000012</t>
+          <t>5936875d7fc1fb070672b7f2</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Mojica</t>
+          <t>Enes Ünal</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -20600,22 +20600,22 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>5936875d7fc1fb070672b7f2</t>
+          <t>6a7eecdb4cdb8203d4a7ba99</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Enes Ünal</t>
+          <t>Yeboah</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -20627,22 +20627,22 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a7eecdb4cdb8203d4a7ba99</t>
+          <t>6a801172c839e903bae6f799</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Yeboah</t>
+          <t>Arnau Ortiz</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -20654,17 +20654,17 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a801172c839e903bae6f799</t>
+          <t>55e5a38a1275df3d029c0884</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Arnau Ortiz</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -20681,22 +20681,22 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>55e5a38a1275df3d029c0884</t>
+          <t>5bcb8327fe292a5a6d05b684</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -20708,22 +20708,22 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>5bcb8327fe292a5a6d05b684</t>
+          <t>6a81e2c1581eca03c0b29b4d</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Abdelkarim</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
@@ -20735,22 +20735,22 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a81e2c1581eca03c0b29b4d</t>
+          <t>6a81bd34c440bf0402377009</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Abdelkarim</t>
+          <t>Drkusic</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
@@ -20762,17 +20762,17 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a81bd34c440bf0402377009</t>
+          <t>6a821227ebfdd00400dfc231</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Drkusic</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -20789,22 +20789,22 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a821227ebfdd00400dfc231</t>
+          <t>6a81ef11c7d7a603e238021c</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Diego Díaz</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -20816,22 +20816,22 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a81ef11c7d7a603e238021c</t>
+          <t>6a83834bebfdd00400dfc8bf</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Diego Díaz</t>
+          <t>Konaré</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
@@ -20843,22 +20843,22 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a83834bebfdd00400dfc8bf</t>
+          <t>5713d1176563c888592d5a3b</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Konaré</t>
+          <t>Rodri</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
@@ -20870,17 +20870,17 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>5713d1176563c888592d5a3b</t>
+          <t>5f9ef33f619ad62ce8c12f13</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Rodri</t>
+          <t>Francho Serrano</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -20897,22 +20897,22 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>5f9ef33f619ad62ce8c12f13</t>
+          <t>6a8615031ca6d904085d6953</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Francho Serrano</t>
+          <t>Dani Martínez</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -20924,12 +20924,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a8615031ca6d904085d6953</t>
+          <t>6a8614c2a6943303dcc51179</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Dani Martínez</t>
+          <t>Domínguez</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -20951,25 +20951,52 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a8614c2a6943303dcc51179</t>
+          <t>6a8775d3cb5d6303c77f0425</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Domínguez</t>
+          <t>Parrott</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>5f36db010b759303ff680104</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iván Martín </t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>520e4ee4a776cc826b00004b</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E776"/>
+  <dimension ref="A1:E777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7316,22 +7316,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>68a21b2501a094041b51ad5b</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Bekhoucha</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -7343,17 +7343,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7370,22 +7370,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7397,22 +7397,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5591624ea1736b3a42844561</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Villalibre</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7424,22 +7424,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>52017ff1cf55e01b3400002e</t>
+          <t>5591624ea1736b3a42844561</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Villalibre</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -7451,17 +7451,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>52017ff1cf55e01b3400002e</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7478,22 +7478,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -7505,17 +7505,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5202890bd7a595bd3700007b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán </t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7532,17 +7532,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>5202890bd7a595bd3700007b</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t xml:space="preserve">Germán </t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7559,12 +7559,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7586,22 +7586,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7640,17 +7640,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7667,17 +7667,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005a6</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Ximo Navarro</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7694,17 +7694,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>504f65024d8bec9a670005a6</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Ximo Navarro</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7721,22 +7721,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7748,22 +7748,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7775,22 +7775,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7802,22 +7802,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -7829,17 +7829,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7856,22 +7856,22 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -7883,22 +7883,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7910,22 +7910,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7937,17 +7937,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7964,22 +7964,22 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>520d0d314386b4816b000029</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Alfonso Herrero</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -7991,22 +7991,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>520d0d314386b4816b000029</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Alfonso Herrero</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -8018,17 +8018,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8045,22 +8045,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -8072,22 +8072,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,12 +8126,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8153,22 +8153,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8180,22 +8180,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8234,22 +8234,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>51d71d02a7178a7654000017</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Aubameyang</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>51d71d02a7178a7654000017</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Aubameyang</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,22 +8315,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8369,22 +8369,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,22 +8504,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -8531,22 +8531,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>52167e295d086a6726000238</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Jurado</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8558,22 +8558,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>52167e295d086a6726000238</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Jurado</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,12 +8585,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,22 +8612,22 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8639,17 +8639,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8666,22 +8666,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8693,22 +8693,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8720,22 +8720,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,22 +8774,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8801,22 +8801,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8828,22 +8828,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,22 +8855,22 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,17 +8936,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>53a01453b33bed3b010002b1</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Denis Suárez</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8963,22 +8963,22 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>53a01453b33bed3b010002b1</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Denis Suárez</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -8990,22 +8990,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -9017,22 +9017,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -9044,17 +9044,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9071,22 +9071,22 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -9098,22 +9098,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,12 +9125,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -9152,22 +9152,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,17 +9206,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9233,22 +9233,22 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -9260,22 +9260,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>57e816de3c438763749abb90</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Álvaro Fernández</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,22 +9287,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>57e816de3c438763749abb90</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Álvaro Fernández</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -9314,17 +9314,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9341,12 +9341,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -9368,22 +9368,22 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,22 +9395,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9449,17 +9449,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9476,22 +9476,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,22 +9530,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,22 +9611,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,22 +9665,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9692,17 +9692,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9719,22 +9719,22 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,17 +9773,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>64c039a313c6a63ccc321929</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Luismi Cruz</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9800,22 +9800,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>64c039a313c6a63ccc321929</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Luismi Cruz</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,17 +9854,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9881,22 +9881,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>66802f240c14414136e408c3</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Mella</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -9908,22 +9908,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>66802f240c14414136e408c3</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Mella</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -9935,17 +9935,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9962,22 +9962,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -9989,22 +9989,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10016,22 +10016,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,22 +10070,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10097,22 +10097,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10124,22 +10124,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,17 +10232,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10259,17 +10259,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6a4d1bfcae633549bd0f0744</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10286,17 +10286,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>65b23452ad8bc354111e6659</t>
+          <t>6a4d1bfcae633549bd0f0744</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Adama Boiro</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10313,22 +10313,22 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>65b23452ad8bc354111e6659</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Adama Boiro</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>66cfa0f08be9a7041ad309f9</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Jon Martín</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>66cfa0f08be9a7041ad309f9</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Jon Martín</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,22 +10421,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10448,22 +10448,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>69ab5b84a3657e03f770ab51</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Manuel Ángel</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>69ab5b84a3657e03f770ab51</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>Manuel Ángel</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,17 +10502,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10529,22 +10529,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6a621c32c6d839058e965748</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>6a621c32c6d839058e965748</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,22 +10583,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -10610,22 +10610,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -10637,17 +10637,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -10664,12 +10664,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -10691,22 +10691,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,22 +10745,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -10772,22 +10772,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5f78e79033215d0412a634a7</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Larrubia</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,17 +10826,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5f78e79033215d0412a634a7</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Larrubia</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10853,22 +10853,22 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -10880,17 +10880,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10907,22 +10907,22 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10934,17 +10934,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10961,17 +10961,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10988,22 +10988,22 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -11015,17 +11015,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11042,17 +11042,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>62e0f3d5fbbaa82d719997a2</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Quagliata</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11069,17 +11069,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>62e0f3d5fbbaa82d719997a2</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Quagliata</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11096,22 +11096,22 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>José Salinas</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -11123,17 +11123,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>630f3695b0b3fe076438ce57</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Yvan Neyou</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11150,17 +11150,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>630d3c68b640225ddc5861c9</t>
+          <t>630f3695b0b3fe076438ce57</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Fran Pérez</t>
+          <t>Yvan Neyou</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11177,17 +11177,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>630d3c68b640225ddc5861c9</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Fran Pérez</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11204,22 +11204,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>64d2b9156167273d0ccc5c4f</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Facundo González</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -11231,22 +11231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d2b9156167273d0ccc5c4f</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Facundo González</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11258,22 +11258,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -11285,22 +11285,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -11312,22 +11312,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,22 +11420,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -11447,22 +11447,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -11474,17 +11474,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11501,17 +11501,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11528,22 +11528,22 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>66ba79564942001a16eafbb7</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Dani Martín</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -11555,22 +11555,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>66802cdbfd03ab41756b1dc9</t>
+          <t>66ba79564942001a16eafbb7</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Dani Barcia</t>
+          <t>Dani Martín</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -11582,17 +11582,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>66802cdbfd03ab41756b1dc9</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Dani Barcia</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11609,22 +11609,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -11636,22 +11636,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -11663,22 +11663,22 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -11690,22 +11690,22 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6865a9767775a433449e9c85</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Noubi</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -11744,22 +11744,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>6865a9767775a433449e9c85</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Noubi</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -11771,22 +11771,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -11798,17 +11798,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -11825,22 +11825,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>679d3d34fdee6403d89449fe</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Eddahchouri</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -11852,22 +11852,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>68ebfeadaff4d55004ae1572</t>
+          <t>679d3d34fdee6403d89449fe</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Rafita</t>
+          <t>Eddahchouri</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11879,22 +11879,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>68ebfeadaff4d55004ae1572</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Rafita</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -11906,12 +11906,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6935bcd342796103f7ed41db</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,22 +11933,22 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>68c735dbd4204b55b4125678</t>
+          <t>6935bcd342796103f7ed41db</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Roony</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -11960,22 +11960,22 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>697bdf4c8d994403fc68fa11</t>
+          <t>68c735dbd4204b55b4125678</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Roony</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -11987,22 +11987,22 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4d1b4e2ae0d649eac3a152</t>
+          <t>697bdf4c8d994403fc68fa11</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Bernal</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -12014,17 +12014,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>594d11088a928dbb0555e5a6</t>
+          <t>6a4d1b4e2ae0d649eac3a152</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Fede Valverde</t>
+          <t>Bernal</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -12041,17 +12041,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>5a2d6f2fd168259b3ede4aef</t>
+          <t>594d11088a928dbb0555e5a6</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Fede Valverde</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -12068,22 +12068,22 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5c03bd490f4a903b890cd3da</t>
+          <t>5a2d6f2fd168259b3ede4aef</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Le Normand</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -12095,17 +12095,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>5989a4391f9fb9af4ba1b806</t>
+          <t>5c03bd490f4a903b890cd3da</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Calero</t>
+          <t>Le Normand</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>5e499be66e12ab0422cc40fb</t>
+          <t>5989a4391f9fb9af4ba1b806</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Unai Vencedor</t>
+          <t>Calero</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12149,22 +12149,22 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>5f8b0f52406daa4fc599cfa0</t>
+          <t>5e499be66e12ab0422cc40fb</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Carreira</t>
+          <t>Unai Vencedor</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12176,17 +12176,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>60b416c715f5654650f8e413</t>
+          <t>5f8b0f52406daa4fc599cfa0</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Sergi Cardona</t>
+          <t>Carreira</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -12203,22 +12203,22 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>5a23f0b68a9f96c2332504ab</t>
+          <t>60b416c715f5654650f8e413</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Raba</t>
+          <t>Sergi Cardona</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12230,22 +12230,22 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>60dec77388c3b1602f5b3ae6</t>
+          <t>5a23f0b68a9f96c2332504ab</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Konaté</t>
+          <t>Raba</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12257,22 +12257,22 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5ac29d32c8bf976d1c180107</t>
+          <t>60dec77388c3b1602f5b3ae6</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Hugo Duro</t>
+          <t>Konaté</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12284,17 +12284,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>61122ac42806395bcad477f0</t>
+          <t>5ac29d32c8bf976d1c180107</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Brugué</t>
+          <t>Hugo Duro</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -12311,22 +12311,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>5d0220e0167d9e5eb611db94</t>
+          <t>61122ac42806395bcad477f0</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Brugué</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12338,17 +12338,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>612e5dd7c44d9506f10f8fed</t>
+          <t>5d0220e0167d9e5eb611db94</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Camavinga</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -12365,22 +12365,22 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>5d430c1e2099e47b0f3d7650</t>
+          <t>612e5dd7c44d9506f10f8fed</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Camavinga</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -12392,12 +12392,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>614f52757bf8f60892e55d4a</t>
+          <t>5d430c1e2099e47b0f3d7650</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Jesús Vázquez</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -12419,22 +12419,22 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>61b51da6d1dcc206d030bacc</t>
+          <t>614f52757bf8f60892e55d4a</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Dani Lorenzo</t>
+          <t>Jesús Vázquez</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -12446,22 +12446,22 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6089b8ace0c69806f612a3d4</t>
+          <t>61b51da6d1dcc206d030bacc</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Nico Williams</t>
+          <t>Dani Lorenzo</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -12473,22 +12473,22 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>62b30b7011f4242dbd7252b0</t>
+          <t>6089b8ace0c69806f612a3d4</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Mantilla</t>
+          <t>Nico Williams</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -12500,22 +12500,22 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>610174c4bc32266071ced17a</t>
+          <t>62b30b7011f4242dbd7252b0</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Oriol Rey</t>
+          <t>Mantilla</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -12527,22 +12527,22 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>62f826f93355b0168987308d</t>
+          <t>610174c4bc32266071ced17a</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Oriol Rey</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -12554,22 +12554,22 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>61122a78c7c51f5b9a6ca7c4</t>
+          <t>62f826f93355b0168987308d</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Pepelu</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -12581,12 +12581,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>630d3bceb4ad355e01bea95f</t>
+          <t>61122a78c7c51f5b9a6ca7c4</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Diego López</t>
+          <t>Pepelu</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -12608,22 +12608,22 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>61184f3ad8a84f5bb9a7fe9d</t>
+          <t>630d3bceb4ad355e01bea95f</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Dumfries</t>
+          <t>Diego López</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -12635,17 +12635,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>63375e14c376ff465d2a5af7</t>
+          <t>61184f3ad8a84f5bb9a7fe9d</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Aitor Paredes</t>
+          <t>Dumfries</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -12662,17 +12662,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>614204ec48f6a015444ac7df</t>
+          <t>63375e14c376ff465d2a5af7</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Balde</t>
+          <t>Aitor Paredes</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -12689,17 +12689,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>64516ff73917190401517dfb</t>
+          <t>614204ec48f6a015444ac7df</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Balde</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -12716,22 +12716,22 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6461127d49e91a03fb017cda</t>
+          <t>64516ff73917190401517dfb</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Carlos Martín</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -12743,22 +12743,22 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>62adceb2b2a1132d77c95779</t>
+          <t>6461127d49e91a03fb017cda</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Swedberg</t>
+          <t>Carlos Martín</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -12770,22 +12770,22 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>64a6fcb014cd337373737ba9</t>
+          <t>62adceb2b2a1132d77c95779</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Güler</t>
+          <t>Swedberg</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -12797,17 +12797,17 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>62ae4ce2c057ca2d85a004e2</t>
+          <t>64a6fcb014cd337373737ba9</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Hjulmand</t>
+          <t>Güler</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12824,22 +12824,22 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>655be3da0cc5192b1a75785c</t>
+          <t>62ae4ce2c057ca2d85a004e2</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Xavi Grande</t>
+          <t>Hjulmand</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -12851,22 +12851,22 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>630e1e745328c70716999d1d</t>
+          <t>655be3da0cc5192b1a75785c</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Xavi Grande</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -12878,22 +12878,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>631ca92becf9a206fe07abea</t>
+          <t>630e1e745328c70716999d1d</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Kike Salas</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -12905,22 +12905,22 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>63a8cd87bfb65a271f11db10</t>
+          <t>631ca92becf9a206fe07abea</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Carlos Álvarez</t>
+          <t>Kike Salas</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -12932,22 +12932,22 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>65ad5e596519630480ca1cf7</t>
+          <t>63a8cd87bfb65a271f11db10</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Cubarsí</t>
+          <t>Carlos Álvarez</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -12959,22 +12959,22 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>666741233b1ffd0457e2b565</t>
+          <t>65ad5e596519630480ca1cf7</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Djaló</t>
+          <t>Cubarsí</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -12986,22 +12986,22 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>65ba7f36d859840e31ca03fe</t>
+          <t>666741233b1ffd0457e2b565</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Djaló</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13013,22 +13013,22 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>666890c0ac5cca0443fd54dd</t>
+          <t>65ba7f36d859840e31ca03fe</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Endrick</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -13040,12 +13040,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>66659f6d36df000455d656bf</t>
+          <t>666890c0ac5cca0443fd54dd</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Mbappé</t>
+          <t>Endrick</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13067,22 +13067,22 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>66802e7e654982413588730f</t>
+          <t>66659f6d36df000455d656bf</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Rubén López</t>
+          <t>Mbappé</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -13094,22 +13094,22 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>668015b50ab8ba417f327194</t>
+          <t>66802e7e654982413588730f</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Roberto Fernández</t>
+          <t>Rubén López</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -13121,12 +13121,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>66905806702b9203b99a1357</t>
+          <t>668015b50ab8ba417f327194</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Álex Calatrava</t>
+          <t>Roberto Fernández</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -13148,17 +13148,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>66802dd799f9bf415ff4350c</t>
+          <t>66905806702b9203b99a1357</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Diego Villares</t>
+          <t>Álex Calatrava</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -13175,12 +13175,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>66802fd539012a413c5d995f</t>
+          <t>66802dd799f9bf415ff4350c</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Yeremay Hernández</t>
+          <t>Diego Villares</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -13202,22 +13202,22 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>66f98191043342085bbcc7ce</t>
+          <t>66802fd539012a413c5d995f</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Peio Canales</t>
+          <t>Yeremay Hernández</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -13229,22 +13229,22 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>66a3d3797fc6ff03fb06facf</t>
+          <t>66f98191043342085bbcc7ce</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Boselli</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -13256,17 +13256,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6865791adf31913331fecaf7</t>
+          <t>66a3d3797fc6ff03fb06facf</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Hartman</t>
+          <t>Boselli</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -13283,22 +13283,22 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>66c72a0476de1f03e6d2b55a</t>
+          <t>6865791adf31913331fecaf7</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Gueye</t>
+          <t>Hartman</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -13310,22 +13310,22 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>688318293777f6041274556c</t>
+          <t>66c72a0476de1f03e6d2b55a</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Hancko</t>
+          <t>Gueye</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -13337,22 +13337,22 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6861bef57775a433449e9581</t>
+          <t>688318293777f6041274556c</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Jutglà</t>
+          <t>Hancko</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -13364,22 +13364,22 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>68a21b2501a094041b51ad5b</t>
+          <t>6861bef57775a433449e9581</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Bekhoucha</t>
+          <t>Jutglà</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Jorge Salinas</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -21375,6 +21375,33 @@
         </is>
       </c>
       <c r="E776" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>68b61e2fbab84b03bb80ed2a</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Livakovic</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000c7</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>portero</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -7343,22 +7343,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5767a067e854a6271e7ff173</t>
+          <t>6935bcd342796103f7ed41db</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Toni Martínez</t>
+          <t>Oso</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -7370,17 +7370,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5634f6a0268e529b04ff8c45</t>
+          <t>5767a067e854a6271e7ff173</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Borja Mayoral</t>
+          <t>Toni Martínez</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7397,22 +7397,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>52079128fa700fba29000016</t>
+          <t>5634f6a0268e529b04ff8c45</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Pere Milla</t>
+          <t>Borja Mayoral</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7424,22 +7424,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5591624ea1736b3a42844561</t>
+          <t>52079128fa700fba29000016</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Villalibre</t>
+          <t>Pere Milla</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -7451,22 +7451,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>52017ff1cf55e01b3400002e</t>
+          <t>5591624ea1736b3a42844561</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Mandi</t>
+          <t>Villalibre</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -7478,17 +7478,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>57363a66ad212396073bce9f</t>
+          <t>52017ff1cf55e01b3400002e</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Zubeldia</t>
+          <t>Mandi</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7505,22 +7505,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5201061f19cbe478070000c6</t>
+          <t>57363a66ad212396073bce9f</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Sergio Herrera</t>
+          <t>Zubeldia</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7532,17 +7532,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5202890bd7a595bd3700007b</t>
+          <t>5201061f19cbe478070000c6</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germán </t>
+          <t>Sergio Herrera</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7559,17 +7559,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5214d165dbf8b74f020000e3</t>
+          <t>5202890bd7a595bd3700007b</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Aitor Fernández</t>
+          <t xml:space="preserve">Germán </t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7586,12 +7586,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>574dc94bb9278bf5518b1e7b</t>
+          <t>5214d165dbf8b74f020000e3</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Budimir</t>
+          <t>Aitor Fernández</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7613,22 +7613,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5402cba8e8a4c9292a000287</t>
+          <t>574dc94bb9278bf5518b1e7b</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Christensen</t>
+          <t>Budimir</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -7640,17 +7640,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>50d2514b099731b00e02ee94</t>
+          <t>5402cba8e8a4c9292a000287</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Laporte</t>
+          <t>Christensen</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7667,17 +7667,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>51b89bd5e401a15f2c000140</t>
+          <t>50d2514b099731b00e02ee94</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Laporte</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7694,17 +7694,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005a6</t>
+          <t>51b89bd5e401a15f2c000140</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Ximo Navarro</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7721,17 +7721,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>523473325a4ad28f01000014</t>
+          <t>504f65024d8bec9a670005a6</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Giménez</t>
+          <t>Ximo Navarro</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7748,22 +7748,22 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>55b66bc6fe0ded1c22ebbd6d</t>
+          <t>523473325a4ad28f01000014</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Dmitrovic</t>
+          <t>Giménez</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7775,22 +7775,22 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>520d1ce5a776cc826b000026</t>
+          <t>55b66bc6fe0ded1c22ebbd6d</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Lucas Torró</t>
+          <t>Dmitrovic</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7802,22 +7802,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>525d4f895231f4d645000795</t>
+          <t>520d1ce5a776cc826b000026</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Iván Villar</t>
+          <t>Lucas Torró</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -7829,22 +7829,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5442eeb84e1f41e97e000261</t>
+          <t>525d4f895231f4d645000795</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Bellerin</t>
+          <t>Iván Villar</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -7856,17 +7856,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>544dfb9b322ce8ed010002bf</t>
+          <t>5442eeb84e1f41e97e000261</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Djené</t>
+          <t>Bellerin</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7883,22 +7883,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>56787538d0e498cf3e24cda6</t>
+          <t>544dfb9b322ce8ed010002bf</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Guruzeta</t>
+          <t>Djené</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7910,22 +7910,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>522f8e353ce1ab673f00000b</t>
+          <t>56787538d0e498cf3e24cda6</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Bartra</t>
+          <t>Guruzeta</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7937,22 +7937,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>522ccdebe10a44087f0000ec</t>
+          <t>522f8e353ce1ab673f00000b</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Unai López</t>
+          <t>Bartra</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -7964,17 +7964,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>504e58594d8bec9a67000106</t>
+          <t>522ccdebe10a44087f0000ec</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Galarreta</t>
+          <t>Unai López</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7991,22 +7991,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>520d0d314386b4816b000029</t>
+          <t>504e58594d8bec9a67000106</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Alfonso Herrero</t>
+          <t>Galarreta</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -8018,22 +8018,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>51b895eae401a15f2c00012d</t>
+          <t>520d0d314386b4816b000029</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Alfonso Herrero</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -8045,17 +8045,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>504e58bb4d8bec9a67000187</t>
+          <t>51b895eae401a15f2c00012d</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Koke</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8072,22 +8072,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>53df365ce5c94c6a08000203</t>
+          <t>504e58bb4d8bec9a67000187</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Koke</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -8099,22 +8099,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>520243d0d7a595bd3700001f</t>
+          <t>53df365ce5c94c6a08000203</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Oblak</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -8126,22 +8126,22 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5676df0e008eb5c93e62f205</t>
+          <t>520243d0d7a595bd3700001f</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Sadiq Umar</t>
+          <t>Oblak</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -8153,12 +8153,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>520d201ca776cc826b000029</t>
+          <t>5676df0e008eb5c93e62f205</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Luis Rioja</t>
+          <t>Sadiq Umar</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -8180,22 +8180,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>521a999b5865e5687000001c</t>
+          <t>520d201ca776cc826b000029</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Soria </t>
+          <t>Luis Rioja</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -8207,22 +8207,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5738fcf88179bfa8526e19ce</t>
+          <t>521a999b5865e5687000001c</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Sergi Canós</t>
+          <t xml:space="preserve">David Soria </t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8234,22 +8234,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>51b9e593e401a15f2c00019f</t>
+          <t>5738fcf88179bfa8526e19ce</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Toljan</t>
+          <t>Sergi Canós</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -8261,22 +8261,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>51d71d02a7178a7654000017</t>
+          <t>51b9e593e401a15f2c00019f</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Aubameyang</t>
+          <t>Toljan</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8288,22 +8288,22 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5203972e2e80d2950b00016f</t>
+          <t>51d71d02a7178a7654000017</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>J. Musso</t>
+          <t>Aubameyang</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8315,22 +8315,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>520d29408091fd886b000049</t>
+          <t>5203972e2e80d2950b00016f</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Mariano</t>
+          <t>J. Musso</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8342,22 +8342,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5590e248b804493642903cdc</t>
+          <t>520d29408091fd886b000049</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Remiro</t>
+          <t>Mariano</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8369,22 +8369,22 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>53c61e5c3554a2ca66000014</t>
+          <t>5590e248b804493642903cdc</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Lejeune</t>
+          <t>Remiro</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8396,22 +8396,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>52175e9470a79164260001a4</t>
+          <t>53c61e5c3554a2ca66000014</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Lejeune</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5590e613b804493642903d44</t>
+          <t>52175e9470a79164260001a4</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Yeray</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8450,22 +8450,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>504f50c54d8bec9a670003d1</t>
+          <t>5590e613b804493642903d44</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Yeray</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8477,22 +8477,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>505d8a247e438909310001c5</t>
+          <t>504f50c54d8bec9a670003d1</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Rubén García</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8504,22 +8504,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>53df321ae5c94c6a08000200</t>
+          <t>505d8a247e438909310001c5</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Marcos Llorente</t>
+          <t>Rubén García</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -8531,22 +8531,22 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>521464ea0c36b84d02000024</t>
+          <t>53df321ae5c94c6a08000200</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Raúl de Tomás</t>
+          <t>Marcos Llorente</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8558,22 +8558,22 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>52167e295d086a6726000238</t>
+          <t>521464ea0c36b84d02000024</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Jurado</t>
+          <t>Raúl de Tomás</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8585,22 +8585,22 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>52017ff55430e20e34000036</t>
+          <t>52167e295d086a6726000238</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Foulquier</t>
+          <t>Jurado</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8612,12 +8612,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5218979184abda6d26000258</t>
+          <t>52017ff55430e20e34000036</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Dimitrievski</t>
+          <t>Foulquier</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8639,22 +8639,22 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>50f47dd1dbbab36d0e0042e3</t>
+          <t>5218979184abda6d26000258</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Jonny</t>
+          <t>Dimitrievski</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -8666,17 +8666,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5255d8008e3e4c1352000369</t>
+          <t>50f47dd1dbbab36d0e0042e3</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Odriozola</t>
+          <t>Jonny</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8693,22 +8693,22 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>56ff01f1f4bbe2a5799eb126</t>
+          <t>5255d8008e3e4c1352000369</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Odriozola</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8720,22 +8720,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>54b25febc9360f7e58002e7c</t>
+          <t>56ff01f1f4bbe2a5799eb126</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Berenguer</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8747,22 +8747,22 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>504f50d44d8bec9a6700040e</t>
+          <t>54b25febc9360f7e58002e7c</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Ayoze Pérez</t>
+          <t>Berenguer</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8774,22 +8774,22 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>55916197c498293442727262</t>
+          <t>504f50d44d8bec9a6700040e</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Ayoze Pérez</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8801,22 +8801,22 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>52013ee178b20d7f07000351</t>
+          <t>55916197c498293442727262</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Josan</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8828,22 +8828,22 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>575c2bacaf91c7b04d8c2513</t>
+          <t>52013ee178b20d7f07000351</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Boyé</t>
+          <t>Josan</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8855,22 +8855,22 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>535d291c74bf632c030004d2</t>
+          <t>575c2bacaf91c7b04d8c2513</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Gayá</t>
+          <t>Boyé</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8882,22 +8882,22 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>504f65184d8bec9a670005f7</t>
+          <t>535d291c74bf632c030004d2</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Isco</t>
+          <t>Gayá</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8909,22 +8909,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5659df7ca6379cbb070b8d84</t>
+          <t>504f65184d8bec9a670005f7</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Oyarzabal</t>
+          <t>Isco</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8936,22 +8936,22 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5218a3a884abda6d26000265</t>
+          <t>5659df7ca6379cbb070b8d84</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Álvaro García</t>
+          <t>Oyarzabal</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -8963,17 +8963,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>53a01453b33bed3b010002b1</t>
+          <t>5218a3a884abda6d26000265</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Denis Suárez</t>
+          <t>Álvaro García</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8990,22 +8990,22 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>504f65024d8bec9a670005aa</t>
+          <t>53a01453b33bed3b010002b1</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Bigas</t>
+          <t>Denis Suárez</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -9017,22 +9017,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>57c09dd1f40c42594caa2956</t>
+          <t>504f65024d8bec9a670005aa</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Marc Roca</t>
+          <t>Bigas</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -9044,22 +9044,22 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>51c1ca53c7694f5f66000015</t>
+          <t>57c09dd1f40c42594caa2956</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Rüdiger</t>
+          <t>Marc Roca</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -9071,17 +9071,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>51bcc43bb9eca82e1a000011</t>
+          <t>51c1ca53c7694f5f66000015</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Marcos Alonso</t>
+          <t>Rüdiger</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9098,22 +9098,22 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>51b897a5e401a15f2c000139</t>
+          <t>51bcc43bb9eca82e1a000011</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Gerard Moreno</t>
+          <t>Marcos Alonso</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9125,22 +9125,22 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5606c6f48ec803b3053e1b04</t>
+          <t>51b897a5e401a15f2c000139</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Fornals</t>
+          <t>Gerard Moreno</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -9152,12 +9152,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>51aa7cb4a56ca45802050abe</t>
+          <t>5606c6f48ec803b3053e1b04</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Diego Llorente</t>
+          <t>Fornals</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -9179,22 +9179,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>548336cc78a053bf06000ce5</t>
+          <t>51aa7cb4a56ca45802050abe</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Iñaki Williams</t>
+          <t>Diego Llorente</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -9206,22 +9206,22 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>598b2b3e96ef719d4b46b147</t>
+          <t>548336cc78a053bf06000ce5</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Barja</t>
+          <t>Iñaki Williams</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5962a95af5056e652d290af9</t>
+          <t>598b2b3e96ef719d4b46b147</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Tete Morente</t>
+          <t>Barja</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,22 +9260,22 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>592c5d96e0882ebf0514d517</t>
+          <t>5962a95af5056e652d290af9</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Gabriel Suazo</t>
+          <t>Tete Morente</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9287,22 +9287,22 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>57e816de3c438763749abb90</t>
+          <t>592c5d96e0882ebf0514d517</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Álvaro Fernández</t>
+          <t>Gabriel Suazo</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -9314,22 +9314,22 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5b33dff53200b74d1d72171e</t>
+          <t>57e816de3c438763749abb90</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Catena</t>
+          <t>Álvaro Fernández</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -9341,17 +9341,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5b35434b6268503b1d665ec1</t>
+          <t>5b33dff53200b74d1d72171e</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Diakhaby</t>
+          <t>Catena</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9368,12 +9368,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5a00fee9772e5c4f5827fbeb</t>
+          <t>5b35434b6268503b1d665ec1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Guido Rodríguez</t>
+          <t>Diakhaby</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -9395,22 +9395,22 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5d51a911d191dc3feef552c0</t>
+          <t>5a00fee9772e5c4f5827fbeb</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Balliu</t>
+          <t>Guido Rodríguez</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9422,22 +9422,22 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5b89b1161c0c9f16f9678cba</t>
+          <t>5d51a911d191dc3feef552c0</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Lo Celso</t>
+          <t>Balliu</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9449,17 +9449,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5d6d88ad1ad6ea0475d2ea30</t>
+          <t>5b89b1161c0c9f16f9678cba</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Ciss</t>
+          <t>Lo Celso</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9476,17 +9476,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5d01a0892111645ef81548f8</t>
+          <t>5d6d88ad1ad6ea0475d2ea30</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>De Jong</t>
+          <t>Ciss</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9503,22 +9503,22 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>60b40cb9d2d7f04662cc9c19</t>
+          <t>5d01a0892111645ef81548f8</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>De Jong</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -9530,22 +9530,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5d4bf0557474677ad684915a</t>
+          <t>60b40cb9d2d7f04662cc9c19</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9557,22 +9557,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>60d6578de348bc03e95ba4b2</t>
+          <t>5d4bf0557474677ad684915a</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Copete</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9584,22 +9584,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>612183f216ab17088eaf36b1</t>
+          <t>60d6578de348bc03e95ba4b2</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Satriano</t>
+          <t>Copete</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -9611,22 +9611,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>5d5ea4ec12a917530bc3e4b0</t>
+          <t>612183f216ab17088eaf36b1</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Kubo</t>
+          <t>Satriano</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -9638,22 +9638,22 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5d8a75210298d1049e864191</t>
+          <t>5d5ea4ec12a917530bc3e4b0</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Raúl</t>
+          <t>Kubo</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -9665,22 +9665,22 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>61d98435c40342041fe941b4</t>
+          <t>5d8a75210298d1049e864191</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Leo Román</t>
+          <t>Raúl</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9692,22 +9692,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5f45502cae94c503ccbd573f</t>
+          <t>61d98435c40342041fe941b4</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Fidalgo</t>
+          <t>Leo Román</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -9719,17 +9719,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>62d034b9fbbaa82d7199978b</t>
+          <t>5f45502cae94c503ccbd573f</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Beñat Prados</t>
+          <t>Fidalgo</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9746,22 +9746,22 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5f6b104d6a93e44a2fcc725e</t>
+          <t>62d034b9fbbaa82d7199978b</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Cristian Rivero</t>
+          <t>Beñat Prados</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9773,22 +9773,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>6494b8e92ba0ab1e468b7f35</t>
+          <t>5f6b104d6a93e44a2fcc725e</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Cristian Rivero</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9800,17 +9800,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>64c039a313c6a63ccc321929</t>
+          <t>6494b8e92ba0ab1e468b7f35</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Luismi Cruz</t>
+          <t>Bellingham</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9827,22 +9827,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>5fecc9d86ede9207a9f2fcac</t>
+          <t>64c039a313c6a63ccc321929</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Juan Iglesias</t>
+          <t>Luismi Cruz</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9854,22 +9854,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>64e53d084068dc518b94a054</t>
+          <t>5fecc9d86ede9207a9f2fcac</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Zakharyan</t>
+          <t>Juan Iglesias</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -9881,17 +9881,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>6080ace3876c8206f41c4197</t>
+          <t>64e53d084068dc518b94a054</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Blanco</t>
+          <t>Zakharyan</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9908,22 +9908,22 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>66802f240c14414136e408c3</t>
+          <t>6080ace3876c8206f41c4197</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Mella</t>
+          <t>Blanco</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -9935,22 +9935,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6110e7e0c16ee36065aa49bd</t>
+          <t>66802f240c14414136e408c3</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Agirrezabala</t>
+          <t>Mella</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -9962,17 +9962,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>6685186cd766964157307273</t>
+          <t>6110e7e0c16ee36065aa49bd</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Vlachodimos</t>
+          <t>Agirrezabala</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9989,22 +9989,22 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>62a67388de8e9e03e103990b</t>
+          <t>6685186cd766964157307273</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Tchouameni</t>
+          <t>Vlachodimos</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10016,22 +10016,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>6692e7f199e2e504052cb421</t>
+          <t>62a67388de8e9e03e103990b</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Letacek</t>
+          <t>Tchouameni</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10043,22 +10043,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>62c81fc9deea5c2d8c81fe13</t>
+          <t>6692e7f199e2e504052cb421</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Letacek</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10070,22 +10070,22 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>6861a4f450c8fc331b6365a2</t>
+          <t>62c81fc9deea5c2d8c81fe13</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Gerenabarrena</t>
+          <t>Peque</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10097,22 +10097,22 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>64b8620a5595c73cc509b299</t>
+          <t>6861a4f450c8fc331b6365a2</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Alemão</t>
+          <t>Gerenabarrena</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10124,22 +10124,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>68a3a86d3a1cb503e4687030</t>
+          <t>64b8620a5595c73cc509b299</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Martim Neto</t>
+          <t>Alemão</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10151,22 +10151,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>64d156d341f8d73d235026fb</t>
+          <t>68a3a86d3a1cb503e4687030</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Natan</t>
+          <t>Martim Neto</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10178,22 +10178,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>6961830c619f3203bc795c50</t>
+          <t>64d156d341f8d73d235026fb</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Joselu</t>
+          <t>Natan</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10205,22 +10205,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>64e53d94a577ee5151c0b1f4</t>
+          <t>6961830c619f3203bc795c50</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Unai Marrero</t>
+          <t>Joselu</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10232,22 +10232,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>6599dd40a4082870148ee34a</t>
+          <t>64e53d94a577ee5151c0b1f4</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Huijsen</t>
+          <t>Unai Marrero</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10259,17 +10259,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>65aac8411342fe045bb822e2</t>
+          <t>6599dd40a4082870148ee34a</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tárrega</t>
+          <t>Huijsen</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10286,17 +10286,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>6a4d1bfcae633549bd0f0744</t>
+          <t>65aac8411342fe045bb822e2</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Tárrega</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10313,17 +10313,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>65b23452ad8bc354111e6659</t>
+          <t>6a4d1bfcae633549bd0f0744</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Adama Boiro</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10340,22 +10340,22 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>6653899c36df000455d63bf7</t>
+          <t>65b23452ad8bc354111e6659</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Espí</t>
+          <t>Adama Boiro</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10367,22 +10367,22 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>66b78ac399e2e504052cbe93</t>
+          <t>6653899c36df000455d63bf7</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Espí</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10394,22 +10394,22 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>66cfa0f08be9a7041ad309f9</t>
+          <t>66b78ac399e2e504052cbe93</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Jon Martín</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10421,22 +10421,22 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>6823c91b81f9dd0429e625ac</t>
+          <t>66cfa0f08be9a7041ad309f9</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Redondo</t>
+          <t>Jon Martín</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10448,22 +10448,22 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>68a1066311d65103ec0070ef</t>
+          <t>6823c91b81f9dd0429e625ac</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>El-Abdellaoui</t>
+          <t>Redondo</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10475,22 +10475,22 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>69ab5b84a3657e03f770ab51</t>
+          <t>68a1066311d65103ec0070ef</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Manuel Ángel</t>
+          <t>El-Abdellaoui</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10502,22 +10502,22 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>69b6fc4a1c66b403a1223d3d</t>
+          <t>69ab5b84a3657e03f770ab51</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Espart</t>
+          <t>Manuel Ángel</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -10529,17 +10529,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6a43e860e284b949d26e1c3c</t>
+          <t>69b6fc4a1c66b403a1223d3d</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grimaldo </t>
+          <t>Espart</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10556,22 +10556,22 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>6a621c32c6d839058e965748</t>
+          <t>6a43e860e284b949d26e1c3c</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t xml:space="preserve">Grimaldo </t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -10583,22 +10583,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>58cd754bafa5feac0520edda</t>
+          <t>6a621c32c6d839058e965748</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Guridi</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -10610,22 +10610,22 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>59c7ab546c064c993bc73462</t>
+          <t>58cd754bafa5feac0520edda</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Guridi</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -10637,22 +10637,22 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>594ad95d4ba3892d2226454c</t>
+          <t>59c7ab546c064c993bc73462</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Bernardo Silva</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -10664,17 +10664,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5cb344adaa68df0442669528</t>
+          <t>594ad95d4ba3892d2226454c</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Barrenetxea</t>
+          <t>Bernardo Silva</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10691,12 +10691,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>59a9a9027d26b96314916033</t>
+          <t>5cb344adaa68df0442669528</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Guedes</t>
+          <t>Barrenetxea</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10718,22 +10718,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5e2b73e8a7992b52c0641b93</t>
+          <t>59a9a9027d26b96314916033</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Manu Hernando</t>
+          <t>Guedes</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -10745,22 +10745,22 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>5b7864b259b3992b14aa4bc0</t>
+          <t>5e2b73e8a7992b52c0641b93</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Puado</t>
+          <t>Manu Hernando</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -10772,22 +10772,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5f14b970f8e4ae03c1f96475</t>
+          <t>5b7864b259b3992b14aa4bc0</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Puado</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10799,22 +10799,22 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5f75f6ff5efb030404be8b77</t>
+          <t>5f14b970f8e4ae03c1f96475</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Lookman</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10826,22 +10826,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>5f78e79033215d0412a634a7</t>
+          <t>5f75f6ff5efb030404be8b77</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Larrubia</t>
+          <t>Lookman</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -10853,17 +10853,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>601869861554ce07d665766f</t>
+          <t>5f78e79033215d0412a634a7</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Germán Valera</t>
+          <t>Larrubia</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10880,22 +10880,22 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>60ed485214bb466048d3a5db</t>
+          <t>601869861554ce07d665766f</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Areso</t>
+          <t>Germán Valera</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -10907,17 +10907,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>607b5df9e292620d106cbb8e</t>
+          <t>60ed485214bb466048d3a5db</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Chust</t>
+          <t>Areso</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10934,22 +10934,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>610ab7f51a405a604ca8c374</t>
+          <t>607b5df9e292620d106cbb8e</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Moleiro</t>
+          <t>Chust</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10961,17 +10961,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>611e6d65c6657008542a1453</t>
+          <t>610ab7f51a405a604ca8c374</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Raúl Moro</t>
+          <t>Moleiro</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10988,17 +10988,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>61996290d61a5d094f43a4bd</t>
+          <t>611e6d65c6657008542a1453</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Ilias Akhomach</t>
+          <t>Raúl Moro</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11015,22 +11015,22 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>61c0eb88278f443e1e5d6a71</t>
+          <t>61996290d61a5d094f43a4bd</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Pubill</t>
+          <t>Ilias Akhomach</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -11042,17 +11042,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>62b31101deea5c2d8c81fdf5</t>
+          <t>61c0eb88278f443e1e5d6a71</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Dela</t>
+          <t>Pubill</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11069,17 +11069,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>62e0f3d5fbbaa82d719997a2</t>
+          <t>62b31101deea5c2d8c81fdf5</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Quagliata</t>
+          <t>Dela</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11096,17 +11096,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>62e58d3e11f4242dbd72531a</t>
+          <t>62e0f3d5fbbaa82d719997a2</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>José Salinas</t>
+          <t>Quagliata</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11123,22 +11123,22 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>62ee482f2f093467dc60108e</t>
+          <t>62e58d3e11f4242dbd72531a</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Pablo Ibáñez</t>
+          <t>José Salinas</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -11150,17 +11150,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>630f3695b0b3fe076438ce57</t>
+          <t>62ee482f2f093467dc60108e</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Yvan Neyou</t>
+          <t>Pablo Ibáñez</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11177,17 +11177,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>630d3c68b640225ddc5861c9</t>
+          <t>630f3695b0b3fe076438ce57</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Fran Pérez</t>
+          <t>Yvan Neyou</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11204,17 +11204,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>635d5731fab08a089c78801c</t>
+          <t>630d3c68b640225ddc5861c9</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Fran Pérez</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11231,22 +11231,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>64d2b9156167273d0ccc5c4f</t>
+          <t>635d5731fab08a089c78801c</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Facundo González</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11258,22 +11258,22 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6595c864840719702ac42c2a</t>
+          <t>64d2b9156167273d0ccc5c4f</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Hugo Álvarez</t>
+          <t>Facundo González</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -11285,22 +11285,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>65ac4fa5fa23880455a78f95</t>
+          <t>6595c864840719702ac42c2a</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Aramburu</t>
+          <t>Hugo Álvarez</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -11312,22 +11312,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>65988cd903b798703d8cc061</t>
+          <t>65ac4fa5fa23880455a78f95</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Buchanan</t>
+          <t>Aramburu</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -11339,22 +11339,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>65db9c727da3ff03e6654f00</t>
+          <t>65988cd903b798703d8cc061</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Arguibide</t>
+          <t>Buchanan</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11366,22 +11366,22 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>65a14cffd9c62803f70f8509</t>
+          <t>65db9c727da3ff03e6654f00</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Arguibide</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11393,22 +11393,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6623fd0e5d937903d96ecca1</t>
+          <t>65a14cffd9c62803f70f8509</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Cabello</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -11420,22 +11420,22 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>66453408943e1536068fa651</t>
+          <t>6623fd0e5d937903d96ecca1</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Risco</t>
+          <t>Cabello</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -11447,22 +11447,22 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>66a3cafd9e452303b3fc0b5e</t>
+          <t>66453408943e1536068fa651</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>A. Osorio</t>
+          <t>Risco</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -11474,22 +11474,22 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>665ced2c03b5e9046aff4b19</t>
+          <t>66a3cafd9e452303b3fc0b5e</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Bauza</t>
+          <t>A. Osorio</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -11501,17 +11501,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>66b6a02fe0157a03f87fcb94</t>
+          <t>665ced2c03b5e9046aff4b19</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Gorrotxategi</t>
+          <t>Bauza</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11528,17 +11528,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>666b0e4336df000455d656d4</t>
+          <t>66b6a02fe0157a03f87fcb94</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Gorrotxategi</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11555,22 +11555,22 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>66ba79564942001a16eafbb7</t>
+          <t>666b0e4336df000455d656d4</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Dani Martín</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -11582,22 +11582,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>66802cdbfd03ab41756b1dc9</t>
+          <t>66ba79564942001a16eafbb7</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Dani Barcia</t>
+          <t>Dani Martín</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -11609,17 +11609,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>66d0a0d48be9a7041ad30d08</t>
+          <t>66802cdbfd03ab41756b1dc9</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Egiluz</t>
+          <t>Dani Barcia</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -11636,22 +11636,22 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6780ea6d98d6a37581d90469</t>
+          <t>66d0a0d48be9a7041ad30d08</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Egiluz</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -11663,22 +11663,22 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>66a9874cce303803d6f77525</t>
+          <t>6780ea6d98d6a37581d90469</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>centrocampista</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -11690,22 +11690,22 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>682893686f9b99317afd9034</t>
+          <t>66a9874cce303803d6f77525</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>F. Cardoso</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>centrocampista</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -11717,22 +11717,22 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>66c5102b8be9a7041ad2df88</t>
+          <t>682893686f9b99317afd9034</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Luiz Junior</t>
+          <t>F. Cardoso</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -11744,22 +11744,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6865a9767775a433449e9c85</t>
+          <t>66c5102b8be9a7041ad2df88</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Noubi</t>
+          <t>Luiz Junior</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -11771,22 +11771,22 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>66d2486c099be403f1da8033</t>
+          <t>6865a9767775a433449e9c85</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Óskarsson</t>
+          <t>Noubi</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -11798,22 +11798,22 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>66d63535f2cbb10b235f78c3</t>
+          <t>66d2486c099be403f1da8033</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Affengruber</t>
+          <t>Óskarsson</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -11825,17 +11825,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6884c2ae19c279041887fa84</t>
+          <t>66d63535f2cbb10b235f78c3</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Valentín Gómez</t>
+          <t>Affengruber</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -11852,22 +11852,22 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>679d3d34fdee6403d89449fe</t>
+          <t>6884c2ae19c279041887fa84</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Eddahchouri</t>
+          <t>Valentín Gómez</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>delantero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11879,22 +11879,22 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>68ebfeadaff4d55004ae1572</t>
+          <t>679d3d34fdee6403d89449fe</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Rafita</t>
+          <t>Eddahchouri</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>delantero</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -11906,22 +11906,22 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>67eeb84cb5d12f043f14e638</t>
+          <t>68ebfeadaff4d55004ae1572</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Fran González</t>
+          <t>Rafita</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>portero</t>
+          <t>defensa</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11933,12 +11933,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6935bcd342796103f7ed41db</t>
+          <t>67eeb84cb5d12f043f14e638</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Oso</t>
+          <t>Fran González</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>defensa</t>
+          <t>portero</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">

--- a/datos/maestros/md_jugadores.xlsx
+++ b/datos/maestros/md_jugadores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E797"/>
+  <dimension ref="A1:E798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +21947,33 @@
         </is>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>6a9a057eb9defe052095ff9a</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Antañón</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>centrocampista</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
